--- a/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
+++ b/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D28B47-ECD5-45F7-AF7B-3A5AE83342A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E9FF6-1926-4762-ADE6-73692AC2E649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="132">
   <si>
     <t>VALOR UNITARIO</t>
   </si>
@@ -172,21 +172,6 @@
     <t># ITEM</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Todos los pagos se realizan en dólares. </t>
-  </si>
-  <si>
-    <t>3. No somos responsables de retraso del proveedor para entregar la carga.</t>
-  </si>
-  <si>
-    <t>5.Los pagos realizados fuera de fecha están sujetos a un recargo de S/.30 por día.</t>
-  </si>
-  <si>
-    <t>9.No hay opción de reembolso.</t>
-  </si>
-  <si>
-    <t>6.Se procederá a cobrar S/.30 x día de almacenaje si el cliente no recoge su pedido en el plazo acordado.</t>
-  </si>
-  <si>
     <t>se procederá a realizar las acciones legales del caso.</t>
   </si>
   <si>
@@ -196,70 +181,15 @@
     <t xml:space="preserve"> No se aceptan marcas con medidas  de frontera. </t>
   </si>
   <si>
-    <t>2.Todas las marcas de los productos deben ser verificadas por el cliente,</t>
-  </si>
-  <si>
     <t>En caso contrario, asumirá el costo de  almacenaje $30 y será embarcado en la próxima salida.</t>
   </si>
   <si>
-    <t>4. La carga deberá llegar al almacén –Yiwu en el rango de fecha indicado por su asesor.</t>
-  </si>
-  <si>
-    <t>7.Los envíos a provincia se realizan a través de la agencia Marvisur o Shalom, con previo pago de flete interno.</t>
-  </si>
-  <si>
     <t>Costo: desde s/20.00</t>
   </si>
   <si>
     <t>coordinador  logístico la tarifa.</t>
   </si>
   <si>
-    <t>8. Las cargas mayores a 200 kg x bulto tendrán un costo adicional por manipuleo, consultar con el</t>
-  </si>
-  <si>
-    <t>11. El costo por metro cubico incluye: Flete – Ag. Aduana – Costos en destino.</t>
-  </si>
-  <si>
-    <r>
-      <t>13.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color theme="1"/>
-        <rFont val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Los documentos de importación deber ser entregados a tiempo, de lo contrario, el participante no tendrá opción</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">14.En caso el cliente esté importando una carga que no sea legal y la empresa Pro Business se vea perjudicada, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.El cliente estará sujeto a pagar mayor el ad- valorem en caso aduanas aplique cambios de partida. </t>
-  </si>
-  <si>
-    <t>16.Si el cliente no paga los tributos o gastos administrativos de su cotización, Pro Business será dueño total de la carga.</t>
-  </si>
-  <si>
-    <t>17.Los ajustes de valor que aplique la aduana serán asumidos por el cliente.</t>
-  </si>
-  <si>
-    <t>18.No somos responsable de las mermas o faltante de la carga (entregamos su pedido tal cual el proveedor envío).</t>
-  </si>
-  <si>
     <t>VALOR ZAPATILLAS</t>
   </si>
   <si>
@@ -291,12 +221,6 @@
   </si>
   <si>
     <t>NUEVO</t>
-  </si>
-  <si>
-    <t>20.Las mercancías son declaradas a nombre de la empresa Grupo Pro Business.</t>
-  </si>
-  <si>
-    <t>21.Se emitirá comprobante (boleta o Factura) de su importación en base a la estrategia de declaración realizada.</t>
   </si>
   <si>
     <t>TOTAL CBM</t>
@@ -580,27 +504,9 @@
     <t>RESUMEN DE COSTOS UNITARIOS</t>
   </si>
   <si>
-    <t>12.No se aceptan productos restringido que no cuenten con permiso.</t>
-  </si>
-  <si>
     <t>de acogerse a un beneficio arancelario (C.O) o pueda tener perdida en aduanas por informacion incompleta.</t>
   </si>
   <si>
-    <t>19.La fecha de entrega es aproximada, está sujeto a variaciones de linea naviera o aduanas.</t>
-  </si>
-  <si>
-    <t>10. Si el cliente quiere cambiar la salida de su carga debera informar 4 día antes de la fecha de cierre.</t>
-  </si>
-  <si>
-    <t>22. El cliente tendra un plazo de 24 horas despues de la entrega para presentar algun tipo de reclamo.</t>
-  </si>
-  <si>
-    <t>23. La factura o boleta se emitirá con base al valor CIF de la cotización final.</t>
-  </si>
-  <si>
-    <t>24. Concepto no facturable: Advalorem, Percepción, Anti-Dumping o Gestión de Compra</t>
-  </si>
-  <si>
     <t>N PROVEEDOR</t>
   </si>
   <si>
@@ -647,6 +553,103 @@
   </si>
   <si>
     <t>Deposito a nuestra cuenta bancaria para pagar impuestos ante Aduanas antes de llegar a puerto (Callao)</t>
+  </si>
+  <si>
+    <t>2.Los productos que tengan un peso mayor o igual a 100 kgs se le realizará el recargo por el uso de montacarga.</t>
+  </si>
+  <si>
+    <t>3.Todas las marcas de los productos deben ser verificadas por el cliente,</t>
+  </si>
+  <si>
+    <t>4. No somos responsables de retraso del proveedor para entregar la carga.</t>
+  </si>
+  <si>
+    <t>5. La carga deberá llegar al almacén –Yiwu en el rango de fecha indicado por su asesor.</t>
+  </si>
+  <si>
+    <t>6.Los pagos realizados fuera de fecha están sujetos a un recargo de S/.30 por día.</t>
+  </si>
+  <si>
+    <t>7.Se procederá a cobrar S/.30 x día de almacenaje si el cliente no recoge su pedido en el plazo acordado.</t>
+  </si>
+  <si>
+    <t>8.Los envíos a provincia se realizan a través de la agencia Marvisur o Shalom, con previo pago de flete interno.</t>
+  </si>
+  <si>
+    <t>10.No hay opción de reembolso.</t>
+  </si>
+  <si>
+    <t>11. Si el cliente quiere cambiar la salida de su carga debera informar 4 día antes de la fecha de cierre.</t>
+  </si>
+  <si>
+    <t>1. La cotización tiene una vida útil de 48 horas hábiles</t>
+  </si>
+  <si>
+    <t>9. Las cargas mayores a 100 kg x bulto tendrán un costo adicional por manipuleo, consultar con el</t>
+  </si>
+  <si>
+    <t>12. El costo por metro cubico incluye: Flete – Ag. Aduana – Costos en destino.</t>
+  </si>
+  <si>
+    <t>13.No se aceptan productos restringido que no cuenten con permiso.</t>
+  </si>
+  <si>
+    <r>
+      <t>14.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Los documentos de importación deber ser entregados a tiempo, de lo contrario, el participante no tendrá opción</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">15.En caso el cliente esté importando una carga que no sea legal y la empresa Pro Business se vea perjudicada, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.El cliente estará sujeto a pagar mayor el ad- valorem en caso aduanas aplique cambios de partida. </t>
+  </si>
+  <si>
+    <t>17.Si el cliente no paga los tributos o gastos administrativos de su cotización, Pro Business será dueño total de la carga.</t>
+  </si>
+  <si>
+    <t>18.Los ajustes de valor que aplique la aduana serán asumidos por el cliente.</t>
+  </si>
+  <si>
+    <t>19.No somos responsable de las mermas o faltante de la carga (entregamos su pedido tal cual el proveedor envío).</t>
+  </si>
+  <si>
+    <t>20.La fecha de entrega es aproximada, está sujeto a variaciones de linea naviera o aduanas.</t>
+  </si>
+  <si>
+    <t>21.Las mercancías son declaradas a nombre de la empresa Grupo Pro Business.</t>
+  </si>
+  <si>
+    <t>22.Se emitirá comprobante (boleta o Factura) de su importación en base a la estrategia de declaración realizada.</t>
+  </si>
+  <si>
+    <t>23. El cliente tendra un plazo de 24 horas despues de la entrega para presentar algun tipo de reclamo.</t>
+  </si>
+  <si>
+    <t>24. La factura o boleta se emitirá con base al valor CIF de la cotización final.</t>
+  </si>
+  <si>
+    <t>25. Concepto no facturable: Advalorem, Percepción, Anti-Dumping o Gestión de Compra</t>
   </si>
 </sst>
 </file>
@@ -1636,6 +1639,86 @@
     <xf numFmtId="2" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1666,71 +1749,20 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1752,35 +1784,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -2571,15 +2574,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>79078</xdr:rowOff>
+      <xdr:colOff>89648</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>45463</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>239621</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>33834</xdr:rowOff>
+      <xdr:colOff>329269</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>219</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2608,8 +2611,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="18776300"/>
-          <a:ext cx="7639885" cy="6276534"/>
+          <a:off x="89648" y="11654757"/>
+          <a:ext cx="6716621" cy="6050756"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2958,40 +2961,40 @@
     <row r="1" spans="1:11" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:11" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:11">
-      <c r="C3" s="125" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
+      <c r="C3" s="120" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
     </row>
     <row r="5" spans="1:11" ht="26.25">
-      <c r="C5" s="126" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
+      <c r="C5" s="121" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="D7" s="141" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
+      <c r="D7" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="33" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B8" s="47"/>
       <c r="D8" s="64" t="s">
@@ -3005,40 +3008,40 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="143">
+      <c r="I8" s="139">
         <f>+'2'!D5</f>
         <v>1</v>
       </c>
-      <c r="J8" s="143"/>
-      <c r="K8" s="143"/>
+      <c r="J8" s="139"/>
+      <c r="K8" s="139"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="33" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="B9" s="47"/>
       <c r="D9" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="127">
+        <v>76</v>
+      </c>
+      <c r="E9" s="122">
         <f ca="1">+TODAY()</f>
-        <v>46062</v>
-      </c>
-      <c r="F9" s="128"/>
+        <v>46094</v>
+      </c>
+      <c r="F9" s="123"/>
       <c r="G9" s="31"/>
       <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="144">
+      <c r="I9" s="140">
         <f>+'2'!D6</f>
         <v>23.2</v>
       </c>
-      <c r="J9" s="144"/>
-      <c r="K9" s="144"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="33" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="B10" s="47"/>
       <c r="D10" s="74" t="s">
@@ -3050,7 +3053,7 @@
       <c r="F10" s="73"/>
       <c r="G10" s="31"/>
       <c r="H10" s="1" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I10" s="80">
         <v>0</v>
@@ -3071,27 +3074,27 @@
         <v>22</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="F11" s="69"/>
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="142">
+      <c r="I11" s="137">
         <f>+'2'!D8</f>
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="60"/>
@@ -3104,11 +3107,11 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
+      <c r="B14" s="143"/>
+      <c r="C14" s="143"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -3122,11 +3125,11 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
+      <c r="B15" s="142"/>
+      <c r="C15" s="142"/>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
       <c r="F15" s="38"/>
@@ -3188,13 +3191,13 @@
       <c r="K18" s="31"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="123" t="s">
-        <v>92</v>
-      </c>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
+      <c r="A19" s="138" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="138"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
       <c r="H19" s="58"/>
@@ -3343,7 +3346,7 @@
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
       <c r="I26" s="62" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="J26" s="46" t="e">
         <f>'2'!D37</f>
@@ -3373,13 +3376,13 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75">
-      <c r="A29" s="122" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="122"/>
-      <c r="C29" s="122"/>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
+      <c r="A29" s="150" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="150"/>
+      <c r="C29" s="150"/>
+      <c r="D29" s="150"/>
+      <c r="E29" s="150"/>
       <c r="F29" s="78"/>
       <c r="G29" s="78"/>
       <c r="H29" s="79"/>
@@ -3393,7 +3396,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="31" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
@@ -3413,7 +3416,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="31" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
@@ -3432,7 +3435,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="104" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
@@ -3473,7 +3476,7 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" s="33" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
@@ -3490,13 +3493,13 @@
       <c r="K34" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M34" s="131" t="s">
-        <v>107</v>
-      </c>
-      <c r="N34" s="131"/>
-      <c r="O34" s="131"/>
-      <c r="P34" s="131"/>
-      <c r="Q34" s="131"/>
+      <c r="M34" s="126" t="s">
+        <v>89</v>
+      </c>
+      <c r="N34" s="126"/>
+      <c r="O34" s="126"/>
+      <c r="P34" s="126"/>
+      <c r="Q34" s="126"/>
     </row>
     <row r="35" spans="1:19" ht="20.25" customHeight="1">
       <c r="A35" s="33"/>
@@ -3510,73 +3513,73 @@
       <c r="I35" s="37"/>
       <c r="J35" s="37"/>
       <c r="K35" s="34"/>
-      <c r="M35" s="132"/>
-      <c r="N35" s="132"/>
-      <c r="O35" s="132"/>
-      <c r="P35" s="132"/>
-      <c r="Q35" s="132"/>
+      <c r="M35" s="127"/>
+      <c r="N35" s="127"/>
+      <c r="O35" s="127"/>
+      <c r="P35" s="127"/>
+      <c r="Q35" s="127"/>
     </row>
     <row r="36" spans="1:19" ht="15" customHeight="1">
-      <c r="A36" s="118" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="119"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
-      <c r="K36" s="120"/>
-      <c r="M36" s="139" t="s">
+      <c r="A36" s="146" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="147"/>
+      <c r="C36" s="147"/>
+      <c r="D36" s="147"/>
+      <c r="E36" s="147"/>
+      <c r="F36" s="147"/>
+      <c r="G36" s="147"/>
+      <c r="H36" s="147"/>
+      <c r="I36" s="147"/>
+      <c r="J36" s="147"/>
+      <c r="K36" s="148"/>
+      <c r="M36" s="134" t="s">
         <v>46</v>
       </c>
-      <c r="N36" s="137" t="s">
-        <v>76</v>
-      </c>
-      <c r="O36" s="133" t="s">
-        <v>103</v>
-      </c>
-      <c r="P36" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q36" s="129" t="s">
-        <v>105</v>
+      <c r="N36" s="132" t="s">
+        <v>60</v>
+      </c>
+      <c r="O36" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="P36" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q36" s="124" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="17.25" customHeight="1">
       <c r="A37" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="116" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="121"/>
-      <c r="D37" s="117"/>
+      <c r="B37" s="144" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="149"/>
+      <c r="D37" s="145"/>
       <c r="E37" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F37" s="116" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37" s="117"/>
+      <c r="F37" s="144" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="145"/>
       <c r="H37" s="5" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="I37" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="124" t="s">
-        <v>75</v>
-      </c>
-      <c r="K37" s="124"/>
-      <c r="M37" s="140"/>
-      <c r="N37" s="138"/>
-      <c r="O37" s="134"/>
-      <c r="P37" s="136"/>
-      <c r="Q37" s="130"/>
+      <c r="J37" s="151" t="s">
+        <v>59</v>
+      </c>
+      <c r="K37" s="151"/>
+      <c r="M37" s="135"/>
+      <c r="N37" s="133"/>
+      <c r="O37" s="129"/>
+      <c r="P37" s="131"/>
+      <c r="Q37" s="125"/>
     </row>
     <row r="38" spans="1:19" s="109" customFormat="1" ht="15.75">
       <c r="A38" s="106" t="s">
@@ -3610,19 +3613,19 @@
       <c r="I39" s="83"/>
       <c r="J39" s="71"/>
       <c r="K39" s="72"/>
-      <c r="M39" s="152" t="s">
-        <v>106</v>
-      </c>
-      <c r="N39" s="152"/>
-      <c r="O39" s="152"/>
-      <c r="P39" s="152"/>
-      <c r="Q39" s="152"/>
-      <c r="R39" s="152"/>
-      <c r="S39" s="152"/>
+      <c r="M39" s="153" t="s">
+        <v>88</v>
+      </c>
+      <c r="N39" s="153"/>
+      <c r="O39" s="153"/>
+      <c r="P39" s="153"/>
+      <c r="Q39" s="153"/>
+      <c r="R39" s="153"/>
+      <c r="S39" s="153"/>
     </row>
     <row r="40" spans="1:19" ht="18.75" customHeight="1">
       <c r="A40" s="81" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
@@ -3633,17 +3636,17 @@
       <c r="H40" s="31"/>
       <c r="I40" s="31"/>
       <c r="J40" s="31"/>
-      <c r="M40" s="152"/>
-      <c r="N40" s="152"/>
-      <c r="O40" s="152"/>
-      <c r="P40" s="152"/>
-      <c r="Q40" s="152"/>
-      <c r="R40" s="152"/>
-      <c r="S40" s="152"/>
+      <c r="M40" s="153"/>
+      <c r="N40" s="153"/>
+      <c r="O40" s="153"/>
+      <c r="P40" s="153"/>
+      <c r="Q40" s="153"/>
+      <c r="R40" s="153"/>
+      <c r="S40" s="153"/>
     </row>
     <row r="41" spans="1:19" ht="18.75">
       <c r="A41" s="82" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
@@ -3657,7 +3660,7 @@
     </row>
     <row r="42" spans="1:19" ht="18.75">
       <c r="A42" s="82" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
@@ -3668,19 +3671,19 @@
       <c r="H42" s="31"/>
       <c r="I42" s="31"/>
       <c r="J42" s="31"/>
-      <c r="M42" s="153" t="s">
-        <v>123</v>
-      </c>
-      <c r="O42" s="153" t="s">
+      <c r="M42" s="113" t="s">
+        <v>99</v>
+      </c>
+      <c r="O42" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="R42" s="153" t="s">
-        <v>124</v>
+      <c r="R42" s="113" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="18.75">
       <c r="A43" s="82" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -3691,13 +3694,13 @@
       <c r="H43" s="31"/>
       <c r="I43" s="31"/>
       <c r="J43" s="31"/>
-      <c r="N43" s="154"/>
-      <c r="O43" s="154"/>
-      <c r="P43" s="154"/>
+      <c r="N43" s="114"/>
+      <c r="O43" s="114"/>
+      <c r="P43" s="114"/>
     </row>
     <row r="44" spans="1:19" ht="18.75" customHeight="1">
       <c r="A44" s="82" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
@@ -3708,24 +3711,24 @@
       <c r="H44" s="31"/>
       <c r="I44" s="31"/>
       <c r="J44" s="31"/>
-      <c r="M44" s="155" t="s">
-        <v>125</v>
+      <c r="M44" s="154" t="s">
+        <v>101</v>
       </c>
       <c r="N44" s="31"/>
-      <c r="O44" s="156">
+      <c r="O44" s="152">
         <f>J14</f>
         <v>1220</v>
       </c>
       <c r="P44" s="31"/>
-      <c r="Q44" s="157" t="s">
-        <v>126</v>
-      </c>
-      <c r="R44" s="157"/>
-      <c r="S44" s="157"/>
+      <c r="Q44" s="119" t="s">
+        <v>102</v>
+      </c>
+      <c r="R44" s="119"/>
+      <c r="S44" s="119"/>
     </row>
     <row r="45" spans="1:19" ht="18.75" customHeight="1">
       <c r="A45" s="82" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
@@ -3736,17 +3739,17 @@
       <c r="H45" s="31"/>
       <c r="I45" s="31"/>
       <c r="J45" s="31"/>
-      <c r="M45" s="155"/>
-      <c r="N45" s="158"/>
-      <c r="O45" s="156"/>
+      <c r="M45" s="154"/>
+      <c r="N45" s="115"/>
+      <c r="O45" s="152"/>
       <c r="P45" s="31"/>
-      <c r="Q45" s="157"/>
-      <c r="R45" s="157"/>
-      <c r="S45" s="157"/>
+      <c r="Q45" s="119"/>
+      <c r="R45" s="119"/>
+      <c r="S45" s="119"/>
     </row>
     <row r="46" spans="1:19" ht="18.75" customHeight="1">
       <c r="A46" s="82" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
@@ -3766,7 +3769,7 @@
     </row>
     <row r="47" spans="1:19" ht="18.75">
       <c r="A47" s="82" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
@@ -3777,24 +3780,24 @@
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
       <c r="J47" s="31"/>
-      <c r="M47" s="155" t="s">
-        <v>127</v>
+      <c r="M47" s="154" t="s">
+        <v>103</v>
       </c>
       <c r="N47" s="31"/>
-      <c r="O47" s="156" t="e">
+      <c r="O47" s="152" t="e">
         <f>J30+J31-J32</f>
         <v>#REF!</v>
       </c>
       <c r="P47" s="31"/>
-      <c r="Q47" s="157" t="s">
-        <v>128</v>
-      </c>
-      <c r="R47" s="157"/>
-      <c r="S47" s="157"/>
+      <c r="Q47" s="119" t="s">
+        <v>104</v>
+      </c>
+      <c r="R47" s="119"/>
+      <c r="S47" s="119"/>
     </row>
     <row r="48" spans="1:19" ht="18.75">
       <c r="A48" s="82" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
@@ -3805,13 +3808,13 @@
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
       <c r="J48" s="31"/>
-      <c r="M48" s="155"/>
-      <c r="N48" s="158"/>
-      <c r="O48" s="159"/>
+      <c r="M48" s="154"/>
+      <c r="N48" s="115"/>
+      <c r="O48" s="155"/>
       <c r="P48" s="31"/>
-      <c r="Q48" s="157"/>
-      <c r="R48" s="157"/>
-      <c r="S48" s="157"/>
+      <c r="Q48" s="119"/>
+      <c r="R48" s="119"/>
+      <c r="S48" s="119"/>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" s="31"/>
@@ -3832,29 +3835,29 @@
       <c r="S49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="M50" s="160" t="s">
-        <v>129</v>
-      </c>
-      <c r="O50" s="161" t="e">
+      <c r="M50" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="O50" s="117" t="e">
         <f>J33</f>
         <v>#REF!</v>
       </c>
-      <c r="Q50" s="157" t="s">
-        <v>130</v>
-      </c>
-      <c r="R50" s="157"/>
-      <c r="S50" s="157"/>
+      <c r="Q50" s="119" t="s">
+        <v>106</v>
+      </c>
+      <c r="R50" s="119"/>
+      <c r="S50" s="119"/>
     </row>
     <row r="51" spans="1:19" ht="18.75">
       <c r="H51" s="32"/>
       <c r="I51" s="32"/>
       <c r="J51" s="32"/>
       <c r="K51" s="31"/>
-      <c r="M51" s="160"/>
-      <c r="O51" s="162"/>
-      <c r="Q51" s="157"/>
-      <c r="R51" s="157"/>
-      <c r="S51" s="157"/>
+      <c r="M51" s="116"/>
+      <c r="O51" s="118"/>
+      <c r="Q51" s="119"/>
+      <c r="R51" s="119"/>
+      <c r="S51" s="119"/>
     </row>
     <row r="52" spans="1:19" ht="18.75">
       <c r="H52" s="32"/>
@@ -3868,23 +3871,28 @@
       <c r="J54" s="40"/>
     </row>
     <row r="56" spans="1:19" ht="21">
-      <c r="A56" s="113" t="s">
+      <c r="A56" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="B56" s="113"/>
-      <c r="C56" s="113"/>
-      <c r="D56" s="113"/>
-      <c r="E56" s="113"/>
-      <c r="F56" s="113"/>
-      <c r="G56" s="113"/>
-      <c r="H56" s="113"/>
-      <c r="I56" s="113"/>
-      <c r="J56" s="113"/>
-      <c r="K56" s="113"/>
+      <c r="B56" s="141"/>
+      <c r="C56" s="141"/>
+      <c r="D56" s="141"/>
+      <c r="E56" s="141"/>
+      <c r="F56" s="141"/>
+      <c r="G56" s="141"/>
+      <c r="H56" s="141"/>
+      <c r="I56" s="141"/>
+      <c r="J56" s="141"/>
+      <c r="K56" s="141"/>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="A59" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="60" spans="1:19">
       <c r="A60" s="49" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
@@ -3892,7 +3900,7 @@
     </row>
     <row r="61" spans="1:19">
       <c r="A61" s="49" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -3900,14 +3908,14 @@
     </row>
     <row r="62" spans="1:19">
       <c r="A62" s="31" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C62" s="31"/>
       <c r="D62" s="31"/>
     </row>
     <row r="63" spans="1:19">
       <c r="A63" s="49" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="B63" s="31"/>
       <c r="C63" s="31"/>
@@ -3915,7 +3923,7 @@
     </row>
     <row r="64" spans="1:19">
       <c r="A64" s="49" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
@@ -3923,14 +3931,14 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="31" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C65" s="31"/>
       <c r="D65" s="31"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="49" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="B66" s="31"/>
       <c r="C66" s="31"/>
@@ -3938,7 +3946,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="49" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -3946,7 +3954,7 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="49" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
@@ -3954,7 +3962,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="49" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
@@ -3962,7 +3970,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="49" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -3970,7 +3978,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="49" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B71" s="31"/>
       <c r="C71" s="31"/>
@@ -3978,7 +3986,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="49" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
@@ -3986,7 +3994,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="49" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
@@ -3994,7 +4002,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="49" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
@@ -4008,7 +4016,7 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="90" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B78" s="31"/>
       <c r="C78" s="31"/>
@@ -4022,7 +4030,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="49" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
@@ -4036,7 +4044,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="89" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
@@ -4049,7 +4057,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="49" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="B81" s="31"/>
       <c r="C81" s="31"/>
@@ -4063,7 +4071,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="35" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C82" s="31"/>
       <c r="D82" s="31"/>
@@ -4076,7 +4084,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="49" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
@@ -4090,7 +4098,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="49" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="B84" s="31"/>
       <c r="C84" s="31"/>
@@ -4104,7 +4112,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="49" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="B85" s="31"/>
       <c r="C85" s="31"/>
@@ -4118,7 +4126,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="49" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="B86" s="31"/>
       <c r="C86" s="31"/>
@@ -4132,7 +4140,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="49" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B87" s="31"/>
       <c r="C87" s="31"/>
@@ -4146,7 +4154,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="49" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="B91" s="31"/>
       <c r="C91" s="31"/>
@@ -4154,7 +4162,7 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="49" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="B92" s="31"/>
       <c r="C92" s="31"/>
@@ -4162,7 +4170,7 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="41" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B93" s="31"/>
       <c r="C93" s="31"/>
@@ -4170,12 +4178,12 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="41" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="41" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="2:10">
@@ -4211,6 +4219,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="33">
+    <mergeCell ref="O44:O45"/>
+    <mergeCell ref="M39:S40"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="Q44:S45"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="Q47:S48"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="J37:K37"/>
     <mergeCell ref="M50:M51"/>
     <mergeCell ref="O50:O51"/>
     <mergeCell ref="Q50:S51"/>
@@ -4227,23 +4252,6 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="O44:O45"/>
-    <mergeCell ref="M39:S40"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="Q44:S45"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="Q47:S48"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="COMPROBAR CANTIDAD DE CAJAS" error="Se debe ingresar la cantidad de cajas" sqref="I11" xr:uid="{3C2F8455-5D0D-41B0-BE98-F91BBC4383D3}">
@@ -4290,19 +4298,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:47" ht="15.75" thickBot="1">
-      <c r="B1" s="145" t="s">
+      <c r="B1" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="147"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="158"/>
     </row>
     <row r="2" spans="2:47" s="1" customFormat="1" ht="35.1" customHeight="1">
       <c r="B2" s="43"/>
@@ -4321,7 +4329,7 @@
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
       <c r="D3" s="93" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="E3" s="43"/>
       <c r="F3" s="43"/>
@@ -4334,7 +4342,7 @@
     </row>
     <row r="4" spans="2:47">
       <c r="B4" s="91" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C4" s="103">
         <v>1</v>
@@ -4366,7 +4374,7 @@
     </row>
     <row r="6" spans="2:47">
       <c r="B6" s="91" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C6" s="103">
         <v>23.2</v>
@@ -4378,13 +4386,13 @@
     </row>
     <row r="7" spans="2:47">
       <c r="B7" s="91" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C7" s="103"/>
     </row>
     <row r="8" spans="2:47">
       <c r="B8" s="91" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C8" s="103">
         <v>8.4000000000000005E-2</v>
@@ -4414,10 +4422,10 @@
     </row>
     <row r="11" spans="2:47" ht="15" customHeight="1">
       <c r="B11" s="87" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="D11" s="99" t="s">
         <v>8</v>
@@ -4433,7 +4441,7 @@
     </row>
     <row r="12" spans="2:47" ht="15" hidden="1" customHeight="1">
       <c r="B12" s="5" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="100">
@@ -4451,7 +4459,7 @@
     </row>
     <row r="13" spans="2:47" ht="15" hidden="1" customHeight="1">
       <c r="B13" s="5" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C13" s="86"/>
       <c r="D13" s="101">
@@ -4469,7 +4477,7 @@
     </row>
     <row r="14" spans="2:47" ht="15" hidden="1" customHeight="1">
       <c r="B14" s="5" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C14" s="85"/>
       <c r="D14" s="102">
@@ -4532,7 +4540,7 @@
     </row>
     <row r="16" spans="2:47" ht="15" hidden="1" customHeight="1">
       <c r="B16" s="54" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C16" s="55"/>
       <c r="D16" s="1"/>
@@ -4702,7 +4710,7 @@
         <v>#REF!</v>
       </c>
       <c r="E21" s="77"/>
-      <c r="F21" s="149"/>
+      <c r="F21" s="160"/>
       <c r="G21" s="48"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -4736,7 +4744,7 @@
         <v>#REF!</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="149"/>
+      <c r="F22" s="160"/>
       <c r="G22" s="48"/>
       <c r="H22" s="1"/>
       <c r="I22" s="76"/>
@@ -4761,7 +4769,7 @@
     </row>
     <row r="23" spans="2:48" ht="14.25" hidden="1" customHeight="1">
       <c r="B23" s="56" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C23" s="57" t="e">
         <f>C19+C21</f>
@@ -4855,7 +4863,7 @@
     </row>
     <row r="26" spans="2:48" ht="18.75" hidden="1" customHeight="1">
       <c r="B26" s="56" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C26" s="57" t="e">
         <f>C23+C24</f>
@@ -4871,19 +4879,19 @@
       <c r="G27" s="48"/>
     </row>
     <row r="28" spans="2:48">
-      <c r="B28" s="151" t="s">
+      <c r="B28" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="151"/>
-      <c r="D28" s="151"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
-      <c r="H28" s="151"/>
-      <c r="I28" s="151"/>
-      <c r="J28" s="151"/>
-      <c r="K28" s="151"/>
-      <c r="L28" s="151"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="162"/>
+      <c r="H28" s="162"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="162"/>
+      <c r="K28" s="162"/>
+      <c r="L28" s="162"/>
     </row>
     <row r="30" spans="2:48">
       <c r="C30" s="50"/>
@@ -4918,8 +4926,8 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="150"/>
-      <c r="I33" s="150"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -4947,8 +4955,8 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="150"/>
-      <c r="I34" s="150"/>
+      <c r="H34" s="161"/>
+      <c r="I34" s="161"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -5154,19 +5162,19 @@
       </c>
     </row>
     <row r="42" spans="1:47">
-      <c r="B42" s="148" t="s">
+      <c r="B42" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="148"/>
-      <c r="D42" s="148"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="148"/>
-      <c r="G42" s="148"/>
-      <c r="H42" s="148"/>
-      <c r="I42" s="148"/>
-      <c r="J42" s="148"/>
-      <c r="K42" s="148"/>
-      <c r="L42" s="148"/>
+      <c r="C42" s="159"/>
+      <c r="D42" s="159"/>
+      <c r="E42" s="159"/>
+      <c r="F42" s="159"/>
+      <c r="G42" s="159"/>
+      <c r="H42" s="159"/>
+      <c r="I42" s="159"/>
+      <c r="J42" s="159"/>
+      <c r="K42" s="159"/>
+      <c r="L42" s="159"/>
     </row>
     <row r="44" spans="1:47">
       <c r="C44" s="21">

--- a/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
+++ b/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E9FF6-1926-4762-ADE6-73692AC2E649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9606CE-98A0-4EB4-833B-D95D925F4CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -24,12 +24,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="131">
   <si>
     <t>VALOR UNITARIO</t>
   </si>
@@ -218,9 +227,6 @@
   </si>
   <si>
     <t>NOMBRE:</t>
-  </si>
-  <si>
-    <t>NUEVO</t>
   </si>
   <si>
     <t>TOTAL CBM</t>
@@ -671,7 +677,7 @@
     <numFmt numFmtId="174" formatCode="0.00\ &quot;x UC&quot;"/>
     <numFmt numFmtId="175" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -956,6 +962,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
@@ -1377,7 +1391,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1644,6 +1658,60 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1653,9 +1721,6 @@
     <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1710,59 +1775,8 @@
     <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1785,6 +1799,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2933,64 +2948,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:S109"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="4" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="10.85546875" style="1"/>
+    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.88671875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.44140625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:11" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:11">
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="137" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+    </row>
+    <row r="5" spans="1:11" ht="25.8">
+      <c r="C5" s="138" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-    </row>
-    <row r="5" spans="1:11" ht="26.25">
-      <c r="C5" s="121" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="D7" s="136" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
+      <c r="D7" s="153" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="33" t="s">
@@ -3008,40 +3023,40 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="139">
+      <c r="I8" s="155">
         <f>+'2'!D5</f>
         <v>1</v>
       </c>
-      <c r="J8" s="139"/>
-      <c r="K8" s="139"/>
+      <c r="J8" s="155"/>
+      <c r="K8" s="155"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="47"/>
       <c r="D9" s="67" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="122">
+        <v>75</v>
+      </c>
+      <c r="E9" s="139">
         <f ca="1">+TODAY()</f>
-        <v>46094</v>
-      </c>
-      <c r="F9" s="123"/>
+        <v>46120</v>
+      </c>
+      <c r="F9" s="140"/>
       <c r="G9" s="31"/>
       <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="140">
+      <c r="I9" s="121">
         <f>+'2'!D6</f>
         <v>23.2</v>
       </c>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" s="47"/>
       <c r="D10" s="74" t="s">
@@ -3073,28 +3088,26 @@
       <c r="D11" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="38" t="s">
-        <v>63</v>
-      </c>
+      <c r="E11" s="38"/>
       <c r="F11" s="69"/>
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="137">
+      <c r="I11" s="154">
         <f>+'2'!D8</f>
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="154"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="138" t="s">
+      <c r="A13" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="138"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
+      <c r="B13" s="132"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="60"/>
@@ -3107,11 +3120,11 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="143" t="s">
+      <c r="A14" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="143"/>
-      <c r="C14" s="143"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -3125,11 +3138,11 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="142" t="s">
+      <c r="A15" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="142"/>
-      <c r="C15" s="142"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="123"/>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
       <c r="F15" s="38"/>
@@ -3152,7 +3165,7 @@
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
+      <c r="F16" s="163"/>
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
@@ -3191,13 +3204,13 @@
       <c r="K18" s="31"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="138" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="138"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
+      <c r="A19" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="132"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
       <c r="H19" s="58"/>
@@ -3375,14 +3388,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.75">
-      <c r="A29" s="150" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="150"/>
-      <c r="C29" s="150"/>
-      <c r="D29" s="150"/>
-      <c r="E29" s="150"/>
+    <row r="29" spans="1:12" ht="15.6">
+      <c r="A29" s="131" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="131"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
       <c r="F29" s="78"/>
       <c r="G29" s="78"/>
       <c r="H29" s="79"/>
@@ -3396,7 +3409,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
@@ -3416,7 +3429,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
@@ -3435,7 +3448,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="104" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
@@ -3476,7 +3489,7 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
@@ -3493,13 +3506,13 @@
       <c r="K34" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M34" s="126" t="s">
-        <v>89</v>
-      </c>
-      <c r="N34" s="126"/>
-      <c r="O34" s="126"/>
-      <c r="P34" s="126"/>
-      <c r="Q34" s="126"/>
+      <c r="M34" s="143" t="s">
+        <v>88</v>
+      </c>
+      <c r="N34" s="143"/>
+      <c r="O34" s="143"/>
+      <c r="P34" s="143"/>
+      <c r="Q34" s="143"/>
     </row>
     <row r="35" spans="1:19" ht="20.25" customHeight="1">
       <c r="A35" s="33"/>
@@ -3513,75 +3526,75 @@
       <c r="I35" s="37"/>
       <c r="J35" s="37"/>
       <c r="K35" s="34"/>
-      <c r="M35" s="127"/>
-      <c r="N35" s="127"/>
-      <c r="O35" s="127"/>
-      <c r="P35" s="127"/>
-      <c r="Q35" s="127"/>
+      <c r="M35" s="144"/>
+      <c r="N35" s="144"/>
+      <c r="O35" s="144"/>
+      <c r="P35" s="144"/>
+      <c r="Q35" s="144"/>
     </row>
     <row r="36" spans="1:19" ht="15" customHeight="1">
-      <c r="A36" s="146" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="147"/>
-      <c r="C36" s="147"/>
-      <c r="D36" s="147"/>
-      <c r="E36" s="147"/>
-      <c r="F36" s="147"/>
-      <c r="G36" s="147"/>
-      <c r="H36" s="147"/>
-      <c r="I36" s="147"/>
-      <c r="J36" s="147"/>
-      <c r="K36" s="148"/>
-      <c r="M36" s="134" t="s">
+      <c r="A36" s="127" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="128"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
+      <c r="I36" s="128"/>
+      <c r="J36" s="128"/>
+      <c r="K36" s="129"/>
+      <c r="M36" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="N36" s="132" t="s">
+      <c r="N36" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="O36" s="128" t="s">
+      <c r="O36" s="145" t="s">
+        <v>84</v>
+      </c>
+      <c r="P36" s="147" t="s">
         <v>85</v>
       </c>
-      <c r="P36" s="130" t="s">
+      <c r="Q36" s="141" t="s">
         <v>86</v>
-      </c>
-      <c r="Q36" s="124" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="17.25" customHeight="1">
       <c r="A37" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="144" t="s">
+      <c r="B37" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="149"/>
-      <c r="D37" s="145"/>
+      <c r="C37" s="130"/>
+      <c r="D37" s="126"/>
       <c r="E37" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F37" s="144" t="s">
+      <c r="F37" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="145"/>
+      <c r="G37" s="126"/>
       <c r="H37" s="5" t="s">
         <v>58</v>
       </c>
       <c r="I37" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="151" t="s">
+      <c r="J37" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="K37" s="151"/>
-      <c r="M37" s="135"/>
-      <c r="N37" s="133"/>
-      <c r="O37" s="129"/>
-      <c r="P37" s="131"/>
-      <c r="Q37" s="125"/>
-    </row>
-    <row r="38" spans="1:19" s="109" customFormat="1" ht="15.75">
+      <c r="K37" s="133"/>
+      <c r="M37" s="152"/>
+      <c r="N37" s="150"/>
+      <c r="O37" s="146"/>
+      <c r="P37" s="148"/>
+      <c r="Q37" s="142"/>
+    </row>
+    <row r="38" spans="1:19" s="109" customFormat="1" ht="15.6">
       <c r="A38" s="106" t="s">
         <v>8</v>
       </c>
@@ -3613,15 +3626,15 @@
       <c r="I39" s="83"/>
       <c r="J39" s="71"/>
       <c r="K39" s="72"/>
-      <c r="M39" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="N39" s="153"/>
-      <c r="O39" s="153"/>
-      <c r="P39" s="153"/>
-      <c r="Q39" s="153"/>
-      <c r="R39" s="153"/>
-      <c r="S39" s="153"/>
+      <c r="M39" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="N39" s="117"/>
+      <c r="O39" s="117"/>
+      <c r="P39" s="117"/>
+      <c r="Q39" s="117"/>
+      <c r="R39" s="117"/>
+      <c r="S39" s="117"/>
     </row>
     <row r="40" spans="1:19" ht="18.75" customHeight="1">
       <c r="A40" s="81" t="s">
@@ -3636,17 +3649,17 @@
       <c r="H40" s="31"/>
       <c r="I40" s="31"/>
       <c r="J40" s="31"/>
-      <c r="M40" s="153"/>
-      <c r="N40" s="153"/>
-      <c r="O40" s="153"/>
-      <c r="P40" s="153"/>
-      <c r="Q40" s="153"/>
-      <c r="R40" s="153"/>
-      <c r="S40" s="153"/>
-    </row>
-    <row r="41" spans="1:19" ht="18.75">
+      <c r="M40" s="117"/>
+      <c r="N40" s="117"/>
+      <c r="O40" s="117"/>
+      <c r="P40" s="117"/>
+      <c r="Q40" s="117"/>
+      <c r="R40" s="117"/>
+      <c r="S40" s="117"/>
+    </row>
+    <row r="41" spans="1:19" ht="18">
       <c r="A41" s="82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
@@ -3658,9 +3671,9 @@
       <c r="I41" s="31"/>
       <c r="J41" s="31"/>
     </row>
-    <row r="42" spans="1:19" ht="18.75">
+    <row r="42" spans="1:19" ht="18">
       <c r="A42" s="82" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
@@ -3672,18 +3685,18 @@
       <c r="I42" s="31"/>
       <c r="J42" s="31"/>
       <c r="M42" s="113" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O42" s="113" t="s">
         <v>34</v>
       </c>
       <c r="R42" s="113" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="18.75">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="18">
       <c r="A43" s="82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -3700,7 +3713,7 @@
     </row>
     <row r="44" spans="1:19" ht="18.75" customHeight="1">
       <c r="A44" s="82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
@@ -3711,24 +3724,24 @@
       <c r="H44" s="31"/>
       <c r="I44" s="31"/>
       <c r="J44" s="31"/>
-      <c r="M44" s="154" t="s">
-        <v>101</v>
+      <c r="M44" s="118" t="s">
+        <v>100</v>
       </c>
       <c r="N44" s="31"/>
-      <c r="O44" s="152">
+      <c r="O44" s="116">
         <f>J14</f>
         <v>1220</v>
       </c>
       <c r="P44" s="31"/>
       <c r="Q44" s="119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R44" s="119"/>
       <c r="S44" s="119"/>
     </row>
     <row r="45" spans="1:19" ht="18.75" customHeight="1">
       <c r="A45" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
@@ -3739,9 +3752,9 @@
       <c r="H45" s="31"/>
       <c r="I45" s="31"/>
       <c r="J45" s="31"/>
-      <c r="M45" s="154"/>
+      <c r="M45" s="118"/>
       <c r="N45" s="115"/>
-      <c r="O45" s="152"/>
+      <c r="O45" s="116"/>
       <c r="P45" s="31"/>
       <c r="Q45" s="119"/>
       <c r="R45" s="119"/>
@@ -3749,7 +3762,7 @@
     </row>
     <row r="46" spans="1:19" ht="18.75" customHeight="1">
       <c r="A46" s="82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
@@ -3767,9 +3780,9 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
     </row>
-    <row r="47" spans="1:19" ht="18.75">
+    <row r="47" spans="1:19" ht="18">
       <c r="A47" s="82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
@@ -3780,24 +3793,24 @@
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
       <c r="J47" s="31"/>
-      <c r="M47" s="154" t="s">
-        <v>103</v>
+      <c r="M47" s="118" t="s">
+        <v>102</v>
       </c>
       <c r="N47" s="31"/>
-      <c r="O47" s="152" t="e">
+      <c r="O47" s="116" t="e">
         <f>J30+J31-J32</f>
         <v>#REF!</v>
       </c>
       <c r="P47" s="31"/>
       <c r="Q47" s="119" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R47" s="119"/>
       <c r="S47" s="119"/>
     </row>
-    <row r="48" spans="1:19" ht="18.75">
+    <row r="48" spans="1:19" ht="18">
       <c r="A48" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
@@ -3808,9 +3821,9 @@
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
       <c r="J48" s="31"/>
-      <c r="M48" s="154"/>
+      <c r="M48" s="118"/>
       <c r="N48" s="115"/>
-      <c r="O48" s="155"/>
+      <c r="O48" s="120"/>
       <c r="P48" s="31"/>
       <c r="Q48" s="119"/>
       <c r="R48" s="119"/>
@@ -3835,31 +3848,31 @@
       <c r="S49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="M50" s="116" t="s">
-        <v>105</v>
-      </c>
-      <c r="O50" s="117" t="e">
+      <c r="M50" s="134" t="s">
+        <v>104</v>
+      </c>
+      <c r="O50" s="135" t="e">
         <f>J33</f>
         <v>#REF!</v>
       </c>
       <c r="Q50" s="119" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R50" s="119"/>
       <c r="S50" s="119"/>
     </row>
-    <row r="51" spans="1:19" ht="18.75">
+    <row r="51" spans="1:19" ht="18">
       <c r="H51" s="32"/>
       <c r="I51" s="32"/>
       <c r="J51" s="32"/>
       <c r="K51" s="31"/>
-      <c r="M51" s="116"/>
-      <c r="O51" s="118"/>
+      <c r="M51" s="134"/>
+      <c r="O51" s="136"/>
       <c r="Q51" s="119"/>
       <c r="R51" s="119"/>
       <c r="S51" s="119"/>
     </row>
-    <row r="52" spans="1:19" ht="18.75">
+    <row r="52" spans="1:19" ht="18">
       <c r="H52" s="32"/>
       <c r="I52" s="32"/>
       <c r="J52" s="32"/>
@@ -3871,28 +3884,28 @@
       <c r="J54" s="40"/>
     </row>
     <row r="56" spans="1:19" ht="21">
-      <c r="A56" s="141" t="s">
+      <c r="A56" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="B56" s="141"/>
-      <c r="C56" s="141"/>
-      <c r="D56" s="141"/>
-      <c r="E56" s="141"/>
-      <c r="F56" s="141"/>
-      <c r="G56" s="141"/>
-      <c r="H56" s="141"/>
-      <c r="I56" s="141"/>
-      <c r="J56" s="141"/>
-      <c r="K56" s="141"/>
+      <c r="B56" s="122"/>
+      <c r="C56" s="122"/>
+      <c r="D56" s="122"/>
+      <c r="E56" s="122"/>
+      <c r="F56" s="122"/>
+      <c r="G56" s="122"/>
+      <c r="H56" s="122"/>
+      <c r="I56" s="122"/>
+      <c r="J56" s="122"/>
+      <c r="K56" s="122"/>
     </row>
     <row r="59" spans="1:19">
       <c r="A59" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:19">
       <c r="A60" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
@@ -3900,7 +3913,7 @@
     </row>
     <row r="61" spans="1:19">
       <c r="A61" s="49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -3915,7 +3928,7 @@
     </row>
     <row r="63" spans="1:19">
       <c r="A63" s="49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B63" s="31"/>
       <c r="C63" s="31"/>
@@ -3923,7 +3936,7 @@
     </row>
     <row r="64" spans="1:19">
       <c r="A64" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
@@ -3938,7 +3951,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B66" s="31"/>
       <c r="C66" s="31"/>
@@ -3946,7 +3959,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="49" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -3954,7 +3967,7 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
@@ -3970,7 +3983,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -3986,7 +3999,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
@@ -3994,7 +4007,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
@@ -4002,7 +4015,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
@@ -4016,7 +4029,7 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="90" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B78" s="31"/>
       <c r="C78" s="31"/>
@@ -4030,7 +4043,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
@@ -4044,7 +4057,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
@@ -4057,7 +4070,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="49" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B81" s="31"/>
       <c r="C81" s="31"/>
@@ -4084,7 +4097,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
@@ -4098,7 +4111,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B84" s="31"/>
       <c r="C84" s="31"/>
@@ -4112,7 +4125,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B85" s="31"/>
       <c r="C85" s="31"/>
@@ -4126,7 +4139,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B86" s="31"/>
       <c r="C86" s="31"/>
@@ -4140,7 +4153,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B87" s="31"/>
       <c r="C87" s="31"/>
@@ -4154,7 +4167,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B91" s="31"/>
       <c r="C91" s="31"/>
@@ -4162,7 +4175,7 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="49" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B92" s="31"/>
       <c r="C92" s="31"/>
@@ -4170,7 +4183,7 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B93" s="31"/>
       <c r="C93" s="31"/>
@@ -4178,21 +4191,21 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="2:10">
       <c r="B100" s="41"/>
     </row>
-    <row r="101" spans="2:10" ht="15.75">
+    <row r="101" spans="2:10" ht="15.6">
       <c r="B101" s="42"/>
     </row>
-    <row r="102" spans="2:10" ht="15.75">
+    <row r="102" spans="2:10" ht="15.6">
       <c r="B102" s="42"/>
     </row>
     <row r="104" spans="2:10">
@@ -4213,29 +4226,12 @@
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
     </row>
-    <row r="109" spans="2:10" ht="15.75">
+    <row r="109" spans="2:10" ht="15.6">
       <c r="B109" s="44"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="33">
-    <mergeCell ref="O44:O45"/>
-    <mergeCell ref="M39:S40"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="Q44:S45"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="Q47:S48"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="J37:K37"/>
     <mergeCell ref="M50:M51"/>
     <mergeCell ref="O50:O51"/>
     <mergeCell ref="Q50:S51"/>
@@ -4252,13 +4248,27 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="O44:O45"/>
+    <mergeCell ref="M39:S40"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="Q44:S45"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="Q47:S48"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="1">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="COMPROBAR CANTIDAD DE CAJAS" error="Se debe ingresar la cantidad de cajas" sqref="I11" xr:uid="{3C2F8455-5D0D-41B0-BE98-F91BBC4383D3}">
       <formula1>I8&gt;0</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11" xr:uid="{543061A4-B74B-4C59-A4B0-2AF20D851021}">
-      <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -4281,23 +4291,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AV54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="2"/>
-    <col min="6" max="6" width="11.28515625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="2"/>
-    <col min="9" max="9" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="2"/>
+    <col min="6" max="6" width="11.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" style="2"/>
+    <col min="9" max="9" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="47" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="47" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:47" ht="15.75" thickBot="1">
+    <row r="1" spans="2:47" ht="15" thickBot="1">
       <c r="B1" s="156" t="s">
         <v>12</v>
       </c>
@@ -4329,7 +4339,7 @@
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
       <c r="D3" s="93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E3" s="43"/>
       <c r="F3" s="43"/>
@@ -4342,7 +4352,7 @@
     </row>
     <row r="4" spans="2:47">
       <c r="B4" s="91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="103">
         <v>1</v>
@@ -4374,7 +4384,7 @@
     </row>
     <row r="6" spans="2:47">
       <c r="B6" s="91" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="103">
         <v>23.2</v>
@@ -4392,7 +4402,7 @@
     </row>
     <row r="8" spans="2:47">
       <c r="B8" s="91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="103">
         <v>8.4000000000000005E-2</v>
@@ -4422,10 +4432,10 @@
     </row>
     <row r="11" spans="2:47" ht="15" customHeight="1">
       <c r="B11" s="87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="99" t="s">
         <v>8</v>
@@ -4441,7 +4451,7 @@
     </row>
     <row r="12" spans="2:47" ht="15" hidden="1" customHeight="1">
       <c r="B12" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="100">
@@ -4459,7 +4469,7 @@
     </row>
     <row r="13" spans="2:47" ht="15" hidden="1" customHeight="1">
       <c r="B13" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" s="86"/>
       <c r="D13" s="101">
@@ -4477,7 +4487,7 @@
     </row>
     <row r="14" spans="2:47" ht="15" hidden="1" customHeight="1">
       <c r="B14" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="85"/>
       <c r="D14" s="102">
@@ -4545,9 +4555,9 @@
       <c r="C16" s="55"/>
       <c r="D16" s="1"/>
       <c r="E16" s="3"/>
-      <c r="G16" s="2" t="str">
+      <c r="G16" s="2">
         <f>'1'!E11</f>
-        <v>NUEVO</v>
+        <v>0</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>

--- a/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
+++ b/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9606CE-98A0-4EB4-833B-D95D925F4CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA268BBC-95BD-493B-AE8E-73390473A86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="2" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$K$109</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$K$118</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="139">
   <si>
     <t>VALOR UNITARIO</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>MONTO TOTAL</t>
-  </si>
-  <si>
-    <t>SERVICIO DE IMPORTACIÓN  (ORIGEN -FLETE - DESTINO)</t>
   </si>
   <si>
     <t>CALCULO DE TRIBUTOS</t>
@@ -525,9 +522,6 @@
     <t>BASE DE LAMPARA LED</t>
   </si>
   <si>
-    <t xml:space="preserve">CARGOS EXTRAS (QTY PROVEEDORES O QTY ITEMS) </t>
-  </si>
-  <si>
     <t>DESCUENTO APLICABLE</t>
   </si>
   <si>
@@ -657,6 +651,36 @@
   <si>
     <t>25. Concepto no facturable: Advalorem, Percepción, Anti-Dumping o Gestión de Compra</t>
   </si>
+  <si>
+    <t>COSTOS FOB</t>
+  </si>
+  <si>
+    <t>ISC</t>
+  </si>
+  <si>
+    <t>CALCULO DE SERVICIO DE IMPORTACIÓN</t>
+  </si>
+  <si>
+    <t>Gravado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLETE INTERNACIONAL </t>
+  </si>
+  <si>
+    <t>No gravado</t>
+  </si>
+  <si>
+    <t>COSTOS EN DESTINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECARGOS OPERATIVOS ( QTY PROVEEDORES Y/O ITEMS) </t>
+  </si>
+  <si>
+    <t>SERVICIO DE IMPORTACIÓN</t>
+  </si>
+  <si>
+    <t>VALOR EXW</t>
+  </si>
 </sst>
 </file>
 
@@ -677,7 +701,7 @@
     <numFmt numFmtId="174" formatCode="0.00\ &quot;x UC&quot;"/>
     <numFmt numFmtId="175" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -892,13 +916,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="12"/>
@@ -974,8 +991,63 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1048,8 +1120,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FF009999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1356,6 +1458,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1391,7 +1552,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1600,7 +1761,6 @@
     <xf numFmtId="0" fontId="24" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1632,8 +1792,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1642,29 +1801,133 @@
     <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="31" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="30" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="39" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="39" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="43" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="44" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="44" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="43" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="46" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1703,7 +1966,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1712,7 +1975,13 @@
     <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1721,10 +1990,10 @@
     <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1799,7 +2068,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1846,13 +2114,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>147864</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>299357</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1914,13 +2182,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>7258</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>139247</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>503464</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>40822</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1998,13 +2266,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>51938</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>147864</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161126</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2066,13 +2334,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>20865</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>139247</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>258536</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>108857</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2135,13 +2403,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>68035</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>147864</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>629124</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2203,13 +2471,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>48080</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>139248</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>462643</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2399,13 +2667,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>607219</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>59531</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>218434</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>94305</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2488,13 +2756,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>813593</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>119066</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>130195</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2590,13 +2858,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>89648</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>45463</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>329269</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>219</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2640,13 +2908,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>809977</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>166510</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>280511</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>120</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2947,7 +3215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:S109"/>
+  <dimension ref="A1:S118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.88671875" style="1" customWidth="1"/>
@@ -2973,41 +3241,41 @@
     <col min="21" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1"/>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1"/>
-    <row r="3" spans="1:11">
-      <c r="C3" s="137" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-    </row>
-    <row r="5" spans="1:11" ht="25.8">
-      <c r="C5" s="138" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="138"/>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="D7" s="153" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-    </row>
-    <row r="8" spans="1:11">
+    <row r="1" spans="1:17" ht="18.75" customHeight="1"/>
+    <row r="2" spans="1:17" ht="18.75" customHeight="1"/>
+    <row r="3" spans="1:17">
+      <c r="C3" s="185" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="C4" s="185"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
+    </row>
+    <row r="5" spans="1:17" ht="25.8">
+      <c r="C5" s="186" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="D7" s="201" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="33" t="s">
         <v>62</v>
       </c>
@@ -3023,40 +3291,40 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="155">
+      <c r="I8" s="203">
         <f>+'2'!D5</f>
         <v>1</v>
       </c>
-      <c r="J8" s="155"/>
-      <c r="K8" s="155"/>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="J8" s="203"/>
+      <c r="K8" s="203"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="47"/>
       <c r="D9" s="67" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="139">
+        <v>74</v>
+      </c>
+      <c r="E9" s="187">
         <f ca="1">+TODAY()</f>
-        <v>46120</v>
-      </c>
-      <c r="F9" s="140"/>
+        <v>46121</v>
+      </c>
+      <c r="F9" s="188"/>
       <c r="G9" s="31"/>
       <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="121">
+      <c r="I9" s="165">
         <f>+'2'!D6</f>
         <v>23.2</v>
       </c>
-      <c r="J9" s="121"/>
-      <c r="K9" s="121"/>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" s="47"/>
       <c r="D10" s="74" t="s">
@@ -3080,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:17">
       <c r="A11" s="33" t="s">
         <v>23</v>
       </c>
@@ -3093,21 +3361,21 @@
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="154">
+      <c r="I11" s="202">
         <f>+'2'!D8</f>
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J11" s="154"/>
-      <c r="K11" s="154"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="132" t="s">
+      <c r="J11" s="202"/>
+      <c r="K11" s="202"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="176" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
+      <c r="B13" s="176"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="60"/>
@@ -3119,12 +3387,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="124" t="s">
+    <row r="14" spans="1:17">
+      <c r="A14" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
+      <c r="B14" s="168"/>
+      <c r="C14" s="168"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -3137,60 +3405,71 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="123" t="s">
+    <row r="15" spans="1:17" customFormat="1">
+      <c r="A15" s="115" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="118">
+        <v>0</v>
+      </c>
+      <c r="K15" s="119" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="167" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="123"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="46" t="e">
-        <f>IF(I11&lt;1,'2'!D21+'2'!D24,60%*(#REF!*I11)+'2'!D24)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K15" s="39" t="s">
+      <c r="B16" s="167"/>
+      <c r="C16" s="167"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="46">
+        <v>0</v>
+      </c>
+      <c r="K16" s="39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="33" t="s">
+    <row r="17" spans="1:17">
+      <c r="A17" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="163"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="45" t="e">
-        <f>SUM(J14:J15)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K16" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="31"/>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
+      <c r="F17" s="114"/>
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="J17" s="45">
+        <f>SUM(J14:J16)</f>
+        <v>1220</v>
+      </c>
+      <c r="K17" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="31"/>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
@@ -3203,14 +3482,14 @@
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
     </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="132" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="132"/>
-      <c r="C19" s="132"/>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
+    <row r="19" spans="1:17">
+      <c r="A19" s="176" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="176"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="176"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
       <c r="H19" s="58"/>
@@ -3224,7 +3503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:17">
       <c r="A20" s="31" t="s">
         <v>37</v>
       </c>
@@ -3236,42 +3515,47 @@
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="61">
-        <f>MAX('2'!C33:C33)</f>
+        <f>MAX('2'!C34:C34)</f>
         <v>0</v>
       </c>
       <c r="J20" s="45" t="e">
-        <f>'2'!D34</f>
+        <f>'2'!D35</f>
         <v>#REF!</v>
       </c>
       <c r="K20" s="34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="31" t="s">
+    <row r="21" spans="1:17" customFormat="1">
+      <c r="A21" s="116" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="116"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="120">
+        <v>0</v>
+      </c>
+      <c r="J21" s="118">
+        <v>0</v>
+      </c>
+      <c r="K21" s="119" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21" s="117"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="117"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="31" t="s">
         <v>38</v>
-      </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="61">
-        <v>0.16</v>
-      </c>
-      <c r="J21" s="45" t="e">
-        <f>'2'!D35</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K21" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="31" t="s">
-        <v>39</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
@@ -3281,61 +3565,65 @@
       <c r="G22" s="31"/>
       <c r="H22" s="31"/>
       <c r="I22" s="61">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="J22" s="45" t="e">
-        <f>'2'!D36</f>
+        <f>'2'!D38</f>
         <v>#REF!</v>
       </c>
       <c r="K22" s="34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="38" t="s">
+    <row r="23" spans="1:17">
+      <c r="A23" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="J23" s="45" t="e">
+        <f>'2'!D39</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K23" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="75">
-        <f>MAX('2'!C30:C30)</f>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="75">
+        <f>MAX('2'!C31:C31)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="46">
-        <f>'2'!D31</f>
+      <c r="J24" s="46">
+        <f>'2'!D32</f>
         <v>0</v>
       </c>
-      <c r="K23" s="39" t="s">
+      <c r="K24" s="39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="33" t="s">
+    <row r="25" spans="1:17">
+      <c r="A25" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="45" t="e">
-        <f>SUM(J20:J23)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K24" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="31"/>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
@@ -3343,323 +3631,313 @@
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="34"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="38" t="s">
+      <c r="I25" s="34"/>
+      <c r="J25" s="45" t="e">
+        <f>SUM(J20:J24)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="31"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="34"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="62" t="s">
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="J26" s="46" t="e">
-        <f>'2'!D37</f>
+      <c r="J27" s="46" t="e">
+        <f>'2'!D40</f>
         <v>#REF!</v>
       </c>
-      <c r="K26" s="39" t="s">
+      <c r="K27" s="39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="33" t="s">
+    <row r="28" spans="1:17">
+      <c r="A28" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="J27" s="45" t="e">
-        <f>J24+J26</f>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="J28" s="45" t="e">
+        <f>J25+J27</f>
         <v>#REF!</v>
       </c>
-      <c r="K27" s="34" t="s">
+      <c r="K28" s="34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.6">
-      <c r="A29" s="131" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="131"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79" t="s">
+    <row r="30" spans="1:17">
+      <c r="A30" s="178" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="179"/>
+      <c r="C30" s="179"/>
+      <c r="D30" s="179"/>
+      <c r="E30" s="179"/>
+      <c r="F30" s="122"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="123"/>
+      <c r="I30" s="124" t="s">
+        <v>38</v>
+      </c>
+      <c r="J30" s="124" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="79" t="s">
+      <c r="K30" s="124" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45" t="e">
-        <f>+'2'!D45+'2'!D21</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K30" s="34" t="s">
+    <row r="31" spans="1:17" customFormat="1">
+      <c r="A31" s="116" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="125"/>
+      <c r="C31" s="125"/>
+      <c r="D31" s="125"/>
+      <c r="E31" s="125"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="125"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="119" t="s">
+        <v>132</v>
+      </c>
+      <c r="J31" s="118">
+        <v>0</v>
+      </c>
+      <c r="K31" s="119" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45">
-        <v>50</v>
-      </c>
-      <c r="K31" s="34" t="s">
+      <c r="L31" s="117"/>
+      <c r="M31" s="117"/>
+      <c r="N31" s="117"/>
+      <c r="O31" s="117"/>
+      <c r="P31" s="117"/>
+      <c r="Q31" s="117"/>
+    </row>
+    <row r="32" spans="1:17" customFormat="1">
+      <c r="A32" s="125" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="125"/>
+      <c r="C32" s="125"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="125"/>
+      <c r="I32" s="119" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="118">
+        <v>0</v>
+      </c>
+      <c r="K32" s="119" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="104" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="105">
-        <v>100</v>
-      </c>
-      <c r="K32" s="34" t="s">
+      <c r="L32" s="117"/>
+      <c r="M32" s="117"/>
+      <c r="N32" s="117"/>
+      <c r="O32" s="117"/>
+      <c r="P32" s="117"/>
+      <c r="Q32" s="117"/>
+    </row>
+    <row r="33" spans="1:19" customFormat="1">
+      <c r="A33" s="128" t="s">
+        <v>135</v>
+      </c>
+      <c r="B33" s="128"/>
+      <c r="C33" s="128"/>
+      <c r="D33" s="128"/>
+      <c r="E33" s="128"/>
+      <c r="F33" s="128"/>
+      <c r="G33" s="128"/>
+      <c r="H33" s="128"/>
+      <c r="I33" s="129" t="s">
+        <v>132</v>
+      </c>
+      <c r="J33" s="130">
+        <v>0</v>
+      </c>
+      <c r="K33" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="L32" s="92"/>
-    </row>
-    <row r="33" spans="1:19">
-      <c r="A33" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46" t="e">
-        <f>J27</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K33" s="39" t="s">
+      <c r="L33" s="117"/>
+      <c r="M33" s="117"/>
+      <c r="N33" s="117"/>
+      <c r="O33" s="117"/>
+      <c r="P33" s="117"/>
+      <c r="Q33" s="117"/>
+    </row>
+    <row r="34" spans="1:19" customFormat="1">
+      <c r="A34" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="125"/>
+      <c r="C34" s="125"/>
+      <c r="D34" s="125"/>
+      <c r="E34" s="125"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="118">
+        <v>0</v>
+      </c>
+      <c r="K34" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" spans="1:19">
-      <c r="A34" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45" t="e">
-        <f>(J30+J31+J33)-J32</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K34" s="34" t="s">
+      <c r="L34" s="117"/>
+      <c r="M34" s="117"/>
+      <c r="N34" s="117"/>
+      <c r="O34" s="117"/>
+      <c r="P34" s="117"/>
+      <c r="Q34" s="117"/>
+    </row>
+    <row r="36" spans="1:19" customFormat="1">
+      <c r="A36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="132"/>
+      <c r="C36" s="132"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="132"/>
+      <c r="G36" s="132"/>
+      <c r="H36" s="132"/>
+      <c r="I36" s="133"/>
+      <c r="J36" s="134">
+        <v>0</v>
+      </c>
+      <c r="K36" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="M34" s="143" t="s">
-        <v>88</v>
-      </c>
-      <c r="N34" s="143"/>
-      <c r="O34" s="143"/>
-      <c r="P34" s="143"/>
-      <c r="Q34" s="143"/>
-    </row>
-    <row r="35" spans="1:19" ht="20.25" customHeight="1">
-      <c r="A35" s="33"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="34"/>
-      <c r="M35" s="144"/>
-      <c r="N35" s="144"/>
-      <c r="O35" s="144"/>
-      <c r="P35" s="144"/>
-      <c r="Q35" s="144"/>
-    </row>
-    <row r="36" spans="1:19" ht="15" customHeight="1">
-      <c r="A36" s="127" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="128"/>
-      <c r="C36" s="128"/>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="128"/>
-      <c r="H36" s="128"/>
-      <c r="I36" s="128"/>
-      <c r="J36" s="128"/>
-      <c r="K36" s="129"/>
-      <c r="M36" s="151" t="s">
-        <v>46</v>
-      </c>
-      <c r="N36" s="149" t="s">
-        <v>60</v>
-      </c>
-      <c r="O36" s="145" t="s">
-        <v>84</v>
-      </c>
-      <c r="P36" s="147" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q36" s="141" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="17.25" customHeight="1">
-      <c r="A37" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="125" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="130"/>
-      <c r="D37" s="126"/>
-      <c r="E37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="125" t="s">
-        <v>61</v>
-      </c>
-      <c r="G37" s="126"/>
-      <c r="H37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I37" s="70" t="s">
+      <c r="L36" s="117"/>
+      <c r="M36" s="117"/>
+      <c r="N36" s="117"/>
+      <c r="O36" s="117"/>
+      <c r="P36" s="117"/>
+      <c r="Q36" s="117"/>
+    </row>
+    <row r="37" spans="1:19" customFormat="1">
+      <c r="A37" s="136" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="137"/>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="137"/>
+      <c r="H37" s="137"/>
+      <c r="I37" s="138"/>
+      <c r="J37" s="139">
+        <v>0</v>
+      </c>
+      <c r="K37" s="140" t="s">
+        <v>35</v>
+      </c>
+      <c r="L37" s="117"/>
+      <c r="M37" s="117"/>
+      <c r="N37" s="117"/>
+      <c r="O37" s="117"/>
+      <c r="P37" s="117"/>
+      <c r="Q37" s="117"/>
+    </row>
+    <row r="38" spans="1:19" customFormat="1">
+      <c r="A38" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="133" t="s">
-        <v>59</v>
-      </c>
-      <c r="K37" s="133"/>
-      <c r="M37" s="152"/>
-      <c r="N37" s="150"/>
-      <c r="O37" s="146"/>
-      <c r="P37" s="148"/>
-      <c r="Q37" s="142"/>
-    </row>
-    <row r="38" spans="1:19" s="109" customFormat="1" ht="15.6">
-      <c r="A38" s="106" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="107"/>
-      <c r="C38" s="107"/>
-      <c r="D38" s="107"/>
-      <c r="E38" s="108" t="e">
-        <f>+SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F38" s="107"/>
-      <c r="G38" s="107"/>
-      <c r="I38" s="110" t="e">
-        <f>+SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J38" s="111"/>
-      <c r="K38" s="112"/>
-      <c r="L38" s="107"/>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A39" s="63"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="72"/>
-      <c r="M39" s="117" t="s">
-        <v>87</v>
-      </c>
+      <c r="B38" s="181"/>
+      <c r="C38" s="181"/>
+      <c r="D38" s="181"/>
+      <c r="E38" s="181"/>
+      <c r="F38" s="181"/>
+      <c r="G38" s="181"/>
+      <c r="H38" s="181"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="147">
+        <f>SUM(J34+J36)-J37</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="148" t="s">
+        <v>35</v>
+      </c>
+      <c r="L38" s="117"/>
+      <c r="M38" s="117"/>
+      <c r="N38" s="117"/>
+      <c r="O38" s="117"/>
+      <c r="P38" s="117"/>
+      <c r="Q38" s="117"/>
+    </row>
+    <row r="39" spans="1:19" customFormat="1">
+      <c r="A39" s="141"/>
+      <c r="B39" s="142"/>
+      <c r="C39" s="142"/>
+      <c r="D39" s="142"/>
+      <c r="E39" s="142"/>
+      <c r="F39" s="142"/>
+      <c r="G39" s="142"/>
+      <c r="H39" s="142"/>
+      <c r="I39" s="143"/>
+      <c r="J39" s="144"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="117"/>
+      <c r="M39" s="117"/>
       <c r="N39" s="117"/>
       <c r="O39" s="117"/>
       <c r="P39" s="117"/>
       <c r="Q39" s="117"/>
-      <c r="R39" s="117"/>
-      <c r="S39" s="117"/>
-    </row>
-    <row r="40" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A40" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="M40" s="117"/>
-      <c r="N40" s="117"/>
-      <c r="O40" s="117"/>
-      <c r="P40" s="117"/>
-      <c r="Q40" s="117"/>
-      <c r="R40" s="117"/>
-      <c r="S40" s="117"/>
-    </row>
-    <row r="41" spans="1:19" ht="18">
-      <c r="A41" s="82" t="s">
-        <v>65</v>
+    </row>
+    <row r="40" spans="1:19" ht="15.6">
+      <c r="A40" s="175" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="175"/>
+      <c r="C40" s="175"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="175"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="79" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="31" t="s">
+        <v>137</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
@@ -3667,36 +3945,40 @@
       <c r="E41" s="31"/>
       <c r="F41" s="31"/>
       <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-    </row>
-    <row r="42" spans="1:19" ht="18">
-      <c r="A42" s="82" t="s">
-        <v>66</v>
-      </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="M42" s="113" t="s">
-        <v>98</v>
-      </c>
-      <c r="O42" s="113" t="s">
-        <v>34</v>
-      </c>
-      <c r="R42" s="113" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="18">
-      <c r="A43" s="82" t="s">
-        <v>77</v>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="45" t="e">
+        <f>+'2'!D48+'2'!D22</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K41" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46" t="e">
+        <f>J28</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K42" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="N42" s="2"/>
+    </row>
+    <row r="43" spans="1:19">
+      <c r="A43" s="33" t="s">
+        <v>71</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -3704,133 +3986,149 @@
       <c r="E43" s="31"/>
       <c r="F43" s="31"/>
       <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="N43" s="114"/>
-      <c r="O43" s="114"/>
-      <c r="P43" s="114"/>
-    </row>
-    <row r="44" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A44" s="82" t="s">
-        <v>67</v>
-      </c>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45" t="e">
+        <f>SUM(J41:J42)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K43" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="M43" s="191" t="s">
+        <v>87</v>
+      </c>
+      <c r="N43" s="191"/>
+      <c r="O43" s="191"/>
+      <c r="P43" s="191"/>
+      <c r="Q43" s="191"/>
+    </row>
+    <row r="44" spans="1:19" ht="20.25" customHeight="1">
+      <c r="A44" s="33"/>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
       <c r="E44" s="31"/>
       <c r="F44" s="31"/>
       <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="M44" s="118" t="s">
-        <v>100</v>
-      </c>
-      <c r="N44" s="31"/>
-      <c r="O44" s="116">
-        <f>J14</f>
-        <v>1220</v>
-      </c>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="119" t="s">
-        <v>101</v>
-      </c>
-      <c r="R44" s="119"/>
-      <c r="S44" s="119"/>
-    </row>
-    <row r="45" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A45" s="82" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="M45" s="118"/>
-      <c r="N45" s="115"/>
-      <c r="O45" s="116"/>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="119"/>
-      <c r="R45" s="119"/>
-      <c r="S45" s="119"/>
-    </row>
-    <row r="46" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A46" s="82" t="s">
-        <v>79</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-    </row>
-    <row r="47" spans="1:19" ht="18">
-      <c r="A47" s="82" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="M47" s="118" t="s">
-        <v>102</v>
-      </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="116" t="e">
-        <f>J30+J31-J32</f>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="34"/>
+      <c r="M44" s="192"/>
+      <c r="N44" s="192"/>
+      <c r="O44" s="192"/>
+      <c r="P44" s="192"/>
+      <c r="Q44" s="192"/>
+    </row>
+    <row r="45" spans="1:19" ht="15" customHeight="1">
+      <c r="A45" s="171" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
+      <c r="D45" s="172"/>
+      <c r="E45" s="172"/>
+      <c r="F45" s="172"/>
+      <c r="G45" s="172"/>
+      <c r="H45" s="172"/>
+      <c r="I45" s="172"/>
+      <c r="J45" s="172"/>
+      <c r="K45" s="173"/>
+      <c r="M45" s="199" t="s">
+        <v>46</v>
+      </c>
+      <c r="N45" s="197" t="s">
+        <v>60</v>
+      </c>
+      <c r="O45" s="193" t="s">
+        <v>83</v>
+      </c>
+      <c r="P45" s="195" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q45" s="189" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="17.25" customHeight="1">
+      <c r="A46" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="169" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="174"/>
+      <c r="D46" s="170"/>
+      <c r="E46" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="169" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" s="170"/>
+      <c r="H46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I46" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="177" t="s">
+        <v>59</v>
+      </c>
+      <c r="K46" s="177"/>
+      <c r="M46" s="200"/>
+      <c r="N46" s="198"/>
+      <c r="O46" s="194"/>
+      <c r="P46" s="196"/>
+      <c r="Q46" s="190"/>
+    </row>
+    <row r="47" spans="1:19" s="106" customFormat="1" ht="15.6">
+      <c r="A47" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="105" t="e">
+        <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="119" t="s">
-        <v>103</v>
-      </c>
-      <c r="R47" s="119"/>
-      <c r="S47" s="119"/>
-    </row>
-    <row r="48" spans="1:19" ht="18">
-      <c r="A48" s="82" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="M48" s="118"/>
-      <c r="N48" s="115"/>
-      <c r="O48" s="120"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="119"/>
-      <c r="R48" s="119"/>
-      <c r="S48" s="119"/>
-    </row>
-    <row r="49" spans="1:19">
-      <c r="A49" s="31"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="I47" s="107" t="e">
+        <f>+SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J47" s="108"/>
+      <c r="K47" s="109"/>
+      <c r="L47" s="104"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A48" s="63"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="I48" s="83"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="72"/>
+      <c r="M48" s="161" t="s">
+        <v>86</v>
+      </c>
+      <c r="N48" s="161"/>
+      <c r="O48" s="161"/>
+      <c r="P48" s="161"/>
+      <c r="Q48" s="161"/>
+      <c r="R48" s="161"/>
+      <c r="S48" s="161"/>
+    </row>
+    <row r="49" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A49" s="81" t="s">
+        <v>48</v>
+      </c>
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="31"/>
@@ -3840,306 +4138,373 @@
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
       <c r="J49" s="31"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="31"/>
-      <c r="P49" s="31"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
-    </row>
-    <row r="50" spans="1:19">
-      <c r="M50" s="134" t="s">
+      <c r="M49" s="161"/>
+      <c r="N49" s="161"/>
+      <c r="O49" s="161"/>
+      <c r="P49" s="161"/>
+      <c r="Q49" s="161"/>
+      <c r="R49" s="161"/>
+      <c r="S49" s="161"/>
+    </row>
+    <row r="50" spans="1:19" ht="18">
+      <c r="A50" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="31"/>
+    </row>
+    <row r="51" spans="1:19" ht="18">
+      <c r="A51" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="M51" s="110" t="s">
+        <v>96</v>
+      </c>
+      <c r="O51" s="110" t="s">
+        <v>34</v>
+      </c>
+      <c r="R51" s="110" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="18">
+      <c r="A52" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="N52" s="111"/>
+      <c r="O52" s="111"/>
+      <c r="P52" s="111"/>
+    </row>
+    <row r="53" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A53" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
+      <c r="M53" s="162" t="s">
+        <v>98</v>
+      </c>
+      <c r="N53" s="31"/>
+      <c r="O53" s="160">
+        <f>J14</f>
+        <v>1220</v>
+      </c>
+      <c r="P53" s="31"/>
+      <c r="Q53" s="163" t="s">
+        <v>99</v>
+      </c>
+      <c r="R53" s="163"/>
+      <c r="S53" s="163"/>
+    </row>
+    <row r="54" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A54" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
+      <c r="M54" s="162"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="160"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="163"/>
+      <c r="R54" s="163"/>
+      <c r="S54" s="163"/>
+    </row>
+    <row r="55" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A55" s="82" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+    </row>
+    <row r="56" spans="1:19" ht="18">
+      <c r="A56" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="31"/>
+      <c r="M56" s="162" t="s">
+        <v>100</v>
+      </c>
+      <c r="N56" s="31"/>
+      <c r="O56" s="160" t="e">
+        <f>J41+#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P56" s="31"/>
+      <c r="Q56" s="163" t="s">
+        <v>101</v>
+      </c>
+      <c r="R56" s="163"/>
+      <c r="S56" s="163"/>
+    </row>
+    <row r="57" spans="1:19" ht="18">
+      <c r="A57" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
+      <c r="M57" s="162"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="164"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="163"/>
+      <c r="R57" s="163"/>
+      <c r="S57" s="163"/>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="A58" s="31"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="M59" s="182" t="s">
+        <v>102</v>
+      </c>
+      <c r="O59" s="183" t="e">
+        <f>J42</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q59" s="163" t="s">
+        <v>103</v>
+      </c>
+      <c r="R59" s="163"/>
+      <c r="S59" s="163"/>
+    </row>
+    <row r="60" spans="1:19" ht="18">
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="31"/>
+      <c r="M60" s="182"/>
+      <c r="O60" s="184"/>
+      <c r="Q60" s="163"/>
+      <c r="R60" s="163"/>
+      <c r="S60" s="163"/>
+    </row>
+    <row r="61" spans="1:19" ht="18">
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="31"/>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="H63" s="40"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="40"/>
+    </row>
+    <row r="65" spans="1:11" ht="21">
+      <c r="A65" s="166" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="166"/>
+      <c r="C65" s="166"/>
+      <c r="D65" s="166"/>
+      <c r="E65" s="166"/>
+      <c r="F65" s="166"/>
+      <c r="G65" s="166"/>
+      <c r="H65" s="166"/>
+      <c r="I65" s="166"/>
+      <c r="J65" s="166"/>
+      <c r="K65" s="166"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="49" t="s">
         <v>104</v>
-      </c>
-      <c r="O50" s="135" t="e">
-        <f>J33</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q50" s="119" t="s">
-        <v>105</v>
-      </c>
-      <c r="R50" s="119"/>
-      <c r="S50" s="119"/>
-    </row>
-    <row r="51" spans="1:19" ht="18">
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="31"/>
-      <c r="M51" s="134"/>
-      <c r="O51" s="136"/>
-      <c r="Q51" s="119"/>
-      <c r="R51" s="119"/>
-      <c r="S51" s="119"/>
-    </row>
-    <row r="52" spans="1:19" ht="18">
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="31"/>
-    </row>
-    <row r="54" spans="1:19">
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-    </row>
-    <row r="56" spans="1:19" ht="21">
-      <c r="A56" s="122" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="122"/>
-      <c r="C56" s="122"/>
-      <c r="D56" s="122"/>
-      <c r="E56" s="122"/>
-      <c r="F56" s="122"/>
-      <c r="G56" s="122"/>
-      <c r="H56" s="122"/>
-      <c r="I56" s="122"/>
-      <c r="J56" s="122"/>
-      <c r="K56" s="122"/>
-    </row>
-    <row r="59" spans="1:19">
-      <c r="A59" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19">
-      <c r="A60" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-    </row>
-    <row r="61" spans="1:19">
-      <c r="A61" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-    </row>
-    <row r="62" spans="1:19">
-      <c r="A62" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-    </row>
-    <row r="63" spans="1:19">
-      <c r="A63" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="B63" s="31"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-    </row>
-    <row r="64" spans="1:19">
-      <c r="A64" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="B66" s="31"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="49" t="s">
-        <v>51</v>
       </c>
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
       <c r="D69" s="31"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:11">
       <c r="A70" s="49" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
       <c r="D70" s="31"/>
     </row>
-    <row r="71" spans="1:10">
-      <c r="A71" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B71" s="31"/>
+    <row r="71" spans="1:11">
+      <c r="A71" s="31" t="s">
+        <v>49</v>
+      </c>
       <c r="C71" s="31"/>
       <c r="D71" s="31"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:11">
       <c r="A72" s="49" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
       <c r="D72" s="31"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:11">
       <c r="A73" s="49" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
       <c r="D73" s="31"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="74" spans="1:11">
+      <c r="A74" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="B76" s="31"/>
+      <c r="C76" s="31"/>
+      <c r="D76" s="31"/>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="49" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
       <c r="D77" s="31"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="31"/>
-    </row>
-    <row r="78" spans="1:10">
-      <c r="A78" s="90" t="s">
-        <v>118</v>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="49" t="s">
+        <v>51</v>
       </c>
       <c r="B78" s="31"/>
       <c r="C78" s="31"/>
       <c r="D78" s="31"/>
-      <c r="E78" s="31"/>
-      <c r="F78" s="31"/>
-      <c r="G78" s="31"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="31"/>
-      <c r="J78" s="31"/>
-    </row>
-    <row r="79" spans="1:10">
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="49" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
       <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="31"/>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="89" t="s">
-        <v>89</v>
-      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" s="31"/>
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
-      <c r="E80" s="31"/>
-      <c r="F80" s="31"/>
-      <c r="G80" s="31"/>
-      <c r="H80" s="31"/>
-      <c r="I80" s="31"/>
-      <c r="J80" s="31"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="49" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B81" s="31"/>
       <c r="C81" s="31"/>
       <c r="D81" s="31"/>
-      <c r="E81" s="31"/>
-      <c r="F81" s="31"/>
-      <c r="G81" s="31"/>
-      <c r="H81" s="31"/>
-      <c r="I81" s="31"/>
-      <c r="J81" s="31"/>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="35" t="s">
-        <v>47</v>
-      </c>
+      <c r="A82" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B82" s="31"/>
       <c r="C82" s="31"/>
       <c r="D82" s="31"/>
-      <c r="E82" s="31"/>
-      <c r="F82" s="31"/>
-      <c r="G82" s="31"/>
-      <c r="H82" s="31"/>
-      <c r="I82" s="31"/>
-      <c r="J82" s="31"/>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B83" s="31"/>
-      <c r="C83" s="31"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="31"/>
-      <c r="H83" s="31"/>
-      <c r="I83" s="31"/>
-      <c r="J83" s="31"/>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="B84" s="31"/>
-      <c r="C84" s="31"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="31"/>
-      <c r="F84" s="31"/>
-      <c r="G84" s="31"/>
-      <c r="H84" s="31"/>
-      <c r="I84" s="31"/>
-      <c r="J84" s="31"/>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="31"/>
-      <c r="F85" s="31"/>
-      <c r="G85" s="31"/>
-      <c r="H85" s="31"/>
-      <c r="I85" s="31"/>
-      <c r="J85" s="31"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="49" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B86" s="31"/>
       <c r="C86" s="31"/>
@@ -4152,8 +4517,8 @@
       <c r="J86" s="31"/>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="49" t="s">
-        <v>125</v>
+      <c r="A87" s="90" t="s">
+        <v>116</v>
       </c>
       <c r="B87" s="31"/>
       <c r="C87" s="31"/>
@@ -4165,108 +4530,234 @@
       <c r="I87" s="31"/>
       <c r="J87" s="31"/>
     </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B88" s="31"/>
+      <c r="C88" s="31"/>
+      <c r="D88" s="31"/>
+      <c r="E88" s="31"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="31"/>
+      <c r="H88" s="31"/>
+      <c r="I88" s="31"/>
+      <c r="J88" s="31"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="89" t="s">
+        <v>88</v>
+      </c>
+      <c r="C89" s="31"/>
+      <c r="D89" s="31"/>
+      <c r="E89" s="31"/>
+      <c r="F89" s="31"/>
+      <c r="G89" s="31"/>
+      <c r="H89" s="31"/>
+      <c r="I89" s="31"/>
+      <c r="J89" s="31"/>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B90" s="31"/>
+      <c r="C90" s="31"/>
+      <c r="D90" s="31"/>
+      <c r="E90" s="31"/>
+      <c r="F90" s="31"/>
+      <c r="G90" s="31"/>
+      <c r="H90" s="31"/>
+      <c r="I90" s="31"/>
+      <c r="J90" s="31"/>
+    </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="B91" s="31"/>
+      <c r="A91" s="35" t="s">
+        <v>47</v>
+      </c>
       <c r="C91" s="31"/>
       <c r="D91" s="31"/>
+      <c r="E91" s="31"/>
+      <c r="F91" s="31"/>
+      <c r="G91" s="31"/>
+      <c r="H91" s="31"/>
+      <c r="I91" s="31"/>
+      <c r="J91" s="31"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="49" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B92" s="31"/>
       <c r="C92" s="31"/>
       <c r="D92" s="31"/>
+      <c r="E92" s="31"/>
+      <c r="F92" s="31"/>
+      <c r="G92" s="31"/>
+      <c r="H92" s="31"/>
+      <c r="I92" s="31"/>
+      <c r="J92" s="31"/>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="41" t="s">
-        <v>128</v>
+      <c r="A93" s="49" t="s">
+        <v>120</v>
       </c>
       <c r="B93" s="31"/>
       <c r="C93" s="31"/>
       <c r="D93" s="31"/>
+      <c r="E93" s="31"/>
+      <c r="F93" s="31"/>
+      <c r="G93" s="31"/>
+      <c r="H93" s="31"/>
+      <c r="I93" s="31"/>
+      <c r="J93" s="31"/>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="41" t="s">
-        <v>129</v>
-      </c>
+      <c r="A94" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B94" s="31"/>
+      <c r="C94" s="31"/>
+      <c r="D94" s="31"/>
+      <c r="E94" s="31"/>
+      <c r="F94" s="31"/>
+      <c r="G94" s="31"/>
+      <c r="H94" s="31"/>
+      <c r="I94" s="31"/>
+      <c r="J94" s="31"/>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="41" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10">
-      <c r="B100" s="41"/>
-    </row>
-    <row r="101" spans="2:10" ht="15.6">
-      <c r="B101" s="42"/>
-    </row>
-    <row r="102" spans="2:10" ht="15.6">
-      <c r="B102" s="42"/>
-    </row>
-    <row r="104" spans="2:10">
-      <c r="C104" s="43"/>
-      <c r="H104" s="43"/>
-      <c r="I104" s="43"/>
-      <c r="J104" s="43"/>
-    </row>
-    <row r="105" spans="2:10">
-      <c r="C105" s="43"/>
-      <c r="H105" s="43"/>
-      <c r="I105" s="43"/>
-      <c r="J105" s="43"/>
-    </row>
-    <row r="107" spans="2:10">
-      <c r="C107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-    </row>
-    <row r="109" spans="2:10" ht="15.6">
-      <c r="B109" s="44"/>
+      <c r="A95" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="B95" s="31"/>
+      <c r="C95" s="31"/>
+      <c r="D95" s="31"/>
+      <c r="E95" s="31"/>
+      <c r="F95" s="31"/>
+      <c r="G95" s="31"/>
+      <c r="H95" s="31"/>
+      <c r="I95" s="31"/>
+      <c r="J95" s="31"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" s="31"/>
+      <c r="C96" s="31"/>
+      <c r="D96" s="31"/>
+      <c r="E96" s="31"/>
+      <c r="F96" s="31"/>
+      <c r="G96" s="31"/>
+      <c r="H96" s="31"/>
+      <c r="I96" s="31"/>
+      <c r="J96" s="31"/>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B101" s="31"/>
+      <c r="C101" s="31"/>
+      <c r="D101" s="31"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="B102" s="31"/>
+      <c r="C102" s="31"/>
+      <c r="D102" s="31"/>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="B109" s="41"/>
+    </row>
+    <row r="110" spans="1:4" ht="15.6">
+      <c r="B110" s="42"/>
+    </row>
+    <row r="111" spans="1:4" ht="15.6">
+      <c r="B111" s="42"/>
+    </row>
+    <row r="113" spans="2:10">
+      <c r="C113" s="43"/>
+      <c r="H113" s="43"/>
+      <c r="I113" s="43"/>
+      <c r="J113" s="43"/>
+    </row>
+    <row r="114" spans="2:10">
+      <c r="C114" s="43"/>
+      <c r="H114" s="43"/>
+      <c r="I114" s="43"/>
+      <c r="J114" s="43"/>
+    </row>
+    <row r="116" spans="2:10">
+      <c r="C116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+    </row>
+    <row r="118" spans="2:10" ht="15.6">
+      <c r="B118" s="44"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="33">
-    <mergeCell ref="M50:M51"/>
-    <mergeCell ref="O50:O51"/>
-    <mergeCell ref="Q50:S51"/>
+  <mergeCells count="35">
+    <mergeCell ref="M59:M60"/>
+    <mergeCell ref="O59:O60"/>
+    <mergeCell ref="Q59:S60"/>
     <mergeCell ref="C3:G4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="Q36:Q37"/>
-    <mergeCell ref="M34:Q35"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="M43:Q44"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="M45:M46"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="O44:O45"/>
-    <mergeCell ref="M39:S40"/>
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="Q44:S45"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="Q47:S48"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="M48:S49"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="Q53:S54"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="Q56:S57"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="COMPROBAR CANTIDAD DE CAJAS" error="Se debe ingresar la cantidad de cajas" sqref="I11" xr:uid="{3C2F8455-5D0D-41B0-BE98-F91BBC4383D3}">
       <formula1>I8&gt;0</formula1>
     </dataValidation>
@@ -4275,13 +4766,13 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="62" fitToWidth="2" fitToHeight="2" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="49" max="10" man="1"/>
+    <brk id="58" max="10" man="1"/>
   </rowBreaks>
   <cellWatches>
-    <cellWatch r="J16"/>
+    <cellWatch r="J17"/>
   </cellWatches>
   <ignoredErrors>
-    <ignoredError sqref="I26" numberStoredAsText="1"/>
+    <ignoredError sqref="I27" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -4290,7 +4781,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AV54"/>
+  <dimension ref="A1:AV57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
@@ -4308,19 +4799,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:47" ht="15" thickBot="1">
-      <c r="B1" s="156" t="s">
+      <c r="B1" s="204" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="158"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="206"/>
     </row>
     <row r="2" spans="2:47" s="1" customFormat="1" ht="35.1" customHeight="1">
       <c r="B2" s="43"/>
@@ -4338,8 +4829,8 @@
     <row r="3" spans="2:47" s="1" customFormat="1" ht="23.1" customHeight="1">
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
-      <c r="D3" s="93" t="s">
-        <v>92</v>
+      <c r="D3" s="92" t="s">
+        <v>91</v>
       </c>
       <c r="E3" s="43"/>
       <c r="F3" s="43"/>
@@ -4352,12 +4843,12 @@
     </row>
     <row r="4" spans="2:47">
       <c r="B4" s="91" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="103">
+        <v>89</v>
+      </c>
+      <c r="C4" s="102">
         <v>1</v>
       </c>
-      <c r="D4" s="93">
+      <c r="D4" s="92">
         <f>COUNT(C4:C4)</f>
         <v>1</v>
       </c>
@@ -4374,10 +4865,10 @@
       <c r="B5" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="103">
+      <c r="C5" s="102">
         <v>1</v>
       </c>
-      <c r="D5" s="93">
+      <c r="D5" s="92">
         <f>SUM(C5:C5)</f>
         <v>1</v>
       </c>
@@ -4386,10 +4877,10 @@
       <c r="B6" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="103">
+      <c r="C6" s="102">
         <v>23.2</v>
       </c>
-      <c r="D6" s="93">
+      <c r="D6" s="92">
         <f>SUM(C6:C6)</f>
         <v>23.2</v>
       </c>
@@ -4398,24 +4889,24 @@
       <c r="B7" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="102"/>
     </row>
     <row r="8" spans="2:47">
       <c r="B8" s="91" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="103">
+        <v>90</v>
+      </c>
+      <c r="C8" s="102">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="D8" s="93">
+      <c r="D8" s="92">
         <f>SUM(C8:C8)</f>
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
     <row r="9" spans="2:47" s="1" customFormat="1">
-      <c r="B9" s="95"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="96"/>
+      <c r="D9" s="95"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -4426,7 +4917,7 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="2:47">
-      <c r="C10" s="94">
+      <c r="C10" s="93">
         <v>1</v>
       </c>
     </row>
@@ -4435,9 +4926,9 @@
         <v>64</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="99" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="98" t="s">
         <v>8</v>
       </c>
       <c r="J11" s="1"/>
@@ -4454,7 +4945,7 @@
         <v>69</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="100">
+      <c r="D12" s="99">
         <f>SUM(C12:C12)</f>
         <v>0</v>
       </c>
@@ -4472,7 +4963,7 @@
         <v>68</v>
       </c>
       <c r="C13" s="86"/>
-      <c r="D13" s="101">
+      <c r="D13" s="100">
         <f>SUM(C13:C13)</f>
         <v>0</v>
       </c>
@@ -4490,7 +4981,7 @@
         <v>63</v>
       </c>
       <c r="C14" s="85"/>
-      <c r="D14" s="102">
+      <c r="D14" s="101">
         <f>SUM(C14:C14)</f>
         <v>0</v>
       </c>
@@ -4518,7 +5009,7 @@
       <c r="B15" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="98">
+      <c r="C15" s="97">
         <v>12.2</v>
       </c>
       <c r="D15" s="1"/>
@@ -4590,10 +5081,10 @@
       <c r="B17" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="97">
+      <c r="C17" s="96">
         <v>100</v>
       </c>
-      <c r="D17" s="100">
+      <c r="D17" s="99">
         <f>SUM(C17:C17)</f>
         <v>100</v>
       </c>
@@ -4620,7 +5111,7 @@
     </row>
     <row r="18" spans="2:48">
       <c r="B18" s="17" t="s">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="C18" s="18">
         <f>C15*C17</f>
@@ -4707,23 +5198,21 @@
       <c r="AT20"/>
       <c r="AU20"/>
     </row>
-    <row r="21" spans="2:48">
-      <c r="B21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="6" t="e">
-        <f>$D$21*C20</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D21" s="29" t="e">
-        <f>IF(#REF!=0,IF('1'!E11="NUEVO",'2'!#REF!*60%,IF('1'!E11="ANTIGUO",'2'!#REF!*60%,IF('1'!E11="SOCIO",60%*(250*'1'!I11),IF('1'!E11="PILOTO",60%*(250*'1'!I11),IF('2'!#REF!&gt;0,60%*(250*'1'!I11),IF('1'!E11="MANUAL",60%*(IF('1'!#REF!&gt;250,('1'!#REF!*'1'!I11),IF('1'!#REF!&lt;=250,(250*'1'!I11)))))))))),IF(#REF!&lt;=250,(250*'1'!I11)*60%,#REF!*60%))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E21" s="77"/>
-      <c r="F21" s="160"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+    <row r="21" spans="2:48" ht="15" customHeight="1">
+      <c r="B21" s="149" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="150">
+        <v>0</v>
+      </c>
+      <c r="D21" s="150">
+        <v>0</v>
+      </c>
+      <c r="E21" s="30"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -4742,27 +5231,25 @@
       <c r="AU21"/>
     </row>
     <row r="22" spans="2:48">
-      <c r="B22" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="18" t="e">
-        <f>C18+C21</f>
+      <c r="B22" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="6" t="e">
+        <f>$D$22*C20</f>
         <v>#REF!</v>
       </c>
-      <c r="D22" s="18" t="e">
-        <f>SUM(C22:C23)</f>
+      <c r="D22" s="29" t="e">
+        <f>IF(#REF!=0,IF('1'!E11="NUEVO",'2'!#REF!*60%,IF('1'!E11="ANTIGUO",'2'!#REF!*60%,IF('1'!E11="SOCIO",60%*(250*'1'!I11),IF('1'!E11="PILOTO",60%*(250*'1'!I11),IF('2'!#REF!&gt;0,60%*(250*'1'!I11),IF('1'!E11="MANUAL",60%*(IF('1'!#REF!&gt;250,('1'!#REF!*'1'!I11),IF('1'!#REF!&lt;=250,(250*'1'!I11)))))))))),IF(#REF!&lt;=250,(250*'1'!I11)*60%,#REF!*60%))</f>
         <v>#REF!</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="160"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="208"/>
       <c r="G22" s="48"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="76"/>
+      <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="AG22"/>
-      <c r="AH22"/>
       <c r="AI22"/>
       <c r="AJ22"/>
       <c r="AK22"/>
@@ -4777,25 +5264,28 @@
       <c r="AT22"/>
       <c r="AU22"/>
     </row>
-    <row r="23" spans="2:48" ht="14.25" hidden="1" customHeight="1">
-      <c r="B23" s="56" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="57" t="e">
-        <f>C19+C21</f>
+    <row r="23" spans="2:48">
+      <c r="B23" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="18" t="e">
+        <f>C18+C22</f>
         <v>#REF!</v>
       </c>
-      <c r="D23" s="57" t="e">
-        <f>SUM(C23:C23)</f>
+      <c r="D23" s="18" t="e">
+        <f>SUM(C23:C24)</f>
         <v>#REF!</v>
       </c>
       <c r="E23" s="1"/>
+      <c r="F23" s="208"/>
       <c r="G23" s="48"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="30"/>
+      <c r="I23" s="76"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
+      <c r="AG23"/>
+      <c r="AH23"/>
       <c r="AI23"/>
       <c r="AJ23"/>
       <c r="AK23"/>
@@ -4810,22 +5300,22 @@
       <c r="AT23"/>
       <c r="AU23"/>
     </row>
-    <row r="24" spans="2:48" ht="14.25" customHeight="1">
-      <c r="B24" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="6">
-        <f>$D$24*C20</f>
-        <v>50</v>
-      </c>
-      <c r="D24" s="29">
-        <f>IF(D18&lt;5000,50,100)</f>
-        <v>50</v>
+    <row r="24" spans="2:48" ht="14.25" hidden="1" customHeight="1">
+      <c r="B24" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="57" t="e">
+        <f>C19+C22</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D24" s="57" t="e">
+        <f>SUM(C24:C24)</f>
+        <v>#REF!</v>
       </c>
       <c r="E24" s="1"/>
       <c r="G24" s="48"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="I24" s="30"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -4843,17 +5333,17 @@
       <c r="AT24"/>
       <c r="AU24"/>
     </row>
-    <row r="25" spans="2:48">
-      <c r="B25" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="18" t="e">
-        <f t="shared" ref="C25" si="0">C22+C24</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D25" s="18" t="e">
-        <f>SUM(C25:C26)</f>
-        <v>#REF!</v>
+    <row r="25" spans="2:48" ht="14.25" customHeight="1">
+      <c r="B25" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="6">
+        <f>$D$25*C20</f>
+        <v>50</v>
+      </c>
+      <c r="D25" s="29">
+        <f>IF(D18&lt;5000,50,100)</f>
+        <v>50</v>
       </c>
       <c r="E25" s="1"/>
       <c r="G25" s="48"/>
@@ -4862,6 +5352,11 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
+      <c r="AI25"/>
+      <c r="AJ25"/>
+      <c r="AK25"/>
+      <c r="AL25"/>
+      <c r="AM25"/>
       <c r="AN25"/>
       <c r="AO25"/>
       <c r="AP25"/>
@@ -4871,102 +5366,101 @@
       <c r="AT25"/>
       <c r="AU25"/>
     </row>
-    <row r="26" spans="2:48" ht="18.75" hidden="1" customHeight="1">
-      <c r="B26" s="56" t="s">
+    <row r="26" spans="2:48">
+      <c r="B26" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="18" t="e">
+        <f t="shared" ref="C26" si="0">C23+C25</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D26" s="18" t="e">
+        <f>SUM(C26:C27)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="AN26"/>
+      <c r="AO26"/>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+      <c r="AR26"/>
+      <c r="AS26"/>
+      <c r="AT26"/>
+      <c r="AU26"/>
+    </row>
+    <row r="27" spans="2:48" ht="18.75" hidden="1" customHeight="1">
+      <c r="B27" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="57" t="e">
-        <f>C23+C24</f>
+      <c r="C27" s="57" t="e">
+        <f>C24+C25</f>
         <v>#REF!</v>
       </c>
-      <c r="D26" s="57" t="e">
-        <f>SUM(C26:C26)</f>
+      <c r="D27" s="57" t="e">
+        <f>SUM(C27:C27)</f>
         <v>#REF!</v>
       </c>
-      <c r="G26" s="48"/>
-    </row>
-    <row r="27" spans="2:48">
       <c r="G27" s="48"/>
     </row>
     <row r="28" spans="2:48">
-      <c r="B28" s="162" t="s">
+      <c r="G28" s="48"/>
+    </row>
+    <row r="29" spans="2:48">
+      <c r="B29" s="210" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="162"/>
-      <c r="D28" s="162"/>
-      <c r="E28" s="162"/>
-      <c r="F28" s="162"/>
-      <c r="G28" s="162"/>
-      <c r="H28" s="162"/>
-      <c r="I28" s="162"/>
-      <c r="J28" s="162"/>
-      <c r="K28" s="162"/>
-      <c r="L28" s="162"/>
-    </row>
-    <row r="30" spans="2:48">
-      <c r="C30" s="50"/>
-      <c r="M30" s="2"/>
-      <c r="AV30" s="1"/>
+      <c r="C29" s="210"/>
+      <c r="D29" s="210"/>
+      <c r="E29" s="210"/>
+      <c r="F29" s="210"/>
+      <c r="G29" s="210"/>
+      <c r="H29" s="210"/>
+      <c r="I29" s="210"/>
+      <c r="J29" s="210"/>
+      <c r="K29" s="210"/>
+      <c r="L29" s="210"/>
     </row>
     <row r="31" spans="2:48">
-      <c r="B31" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="52">
-        <f>C17*C30</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="52">
-        <f>SUM(C31:C31)</f>
-        <v>0</v>
-      </c>
+      <c r="C31" s="50"/>
       <c r="M31" s="2"/>
       <c r="AV31" s="1"/>
     </row>
     <row r="32" spans="2:48">
-      <c r="G32" s="107"/>
+      <c r="B32" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="52">
+        <f>C17*C31</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="52">
+        <f>SUM(C32:C32)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="AV32" s="1"/>
     </row>
     <row r="33" spans="1:47">
-      <c r="C33" s="11">
+      <c r="G33" s="104"/>
+    </row>
+    <row r="34" spans="1:47">
+      <c r="C34" s="11">
         <v>0</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>8</v>
-      </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="161"/>
-      <c r="I33" s="161"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="AN33"/>
-      <c r="AO33"/>
-      <c r="AP33"/>
-      <c r="AQ33"/>
-      <c r="AR33"/>
-      <c r="AS33"/>
-      <c r="AT33"/>
-      <c r="AU33"/>
-    </row>
-    <row r="34" spans="1:47">
-      <c r="B34" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="6" t="e">
-        <f>MAX(C25:C26)*C33</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D34" s="10" t="e">
-        <f>SUM(C34:C34)</f>
-        <v>#REF!</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="161"/>
-      <c r="I34" s="161"/>
+      <c r="H34" s="209"/>
+      <c r="I34" s="209"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -4979,375 +5473,435 @@
       <c r="AT34"/>
       <c r="AU34"/>
     </row>
-    <row r="35" spans="1:47" s="14" customFormat="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="13" t="e">
-        <f>((MAX(C25:C26))+C34)*16%</f>
+    <row r="35" spans="1:47">
+      <c r="B35" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6" t="e">
+        <f>MAX(C26:C27)*C34</f>
         <v>#REF!</v>
       </c>
       <c r="D35" s="10" t="e">
         <f>SUM(C35:C35)</f>
         <v>#REF!</v>
       </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
-      <c r="X35" s="12"/>
-      <c r="Y35" s="12"/>
-      <c r="Z35" s="12"/>
-      <c r="AA35" s="12"/>
-      <c r="AB35" s="12"/>
-      <c r="AC35" s="12"/>
-      <c r="AD35" s="12"/>
-      <c r="AE35" s="12"/>
-      <c r="AF35" s="12"/>
-      <c r="AG35" s="12"/>
-      <c r="AH35" s="12"/>
-      <c r="AI35" s="12"/>
-      <c r="AJ35" s="12"/>
-      <c r="AK35" s="12"/>
-      <c r="AL35" s="12"/>
-      <c r="AM35" s="12"/>
-    </row>
-    <row r="36" spans="1:47" s="14" customFormat="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="15" t="e">
-        <f t="shared" ref="C36" si="1">((MAX(C25:C26))+C34)*2%</f>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="209"/>
+      <c r="I35" s="209"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="AN35"/>
+      <c r="AO35"/>
+      <c r="AP35"/>
+      <c r="AQ35"/>
+      <c r="AR35"/>
+      <c r="AS35"/>
+      <c r="AT35"/>
+      <c r="AU35"/>
+    </row>
+    <row r="36" spans="1:47">
+      <c r="A36" s="117"/>
+      <c r="B36" s="151"/>
+      <c r="C36" s="152">
+        <v>0</v>
+      </c>
+      <c r="D36" s="152">
+        <v>0</v>
+      </c>
+      <c r="E36" s="156"/>
+      <c r="F36" s="156"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="153"/>
+      <c r="K36" s="153"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="117"/>
+      <c r="N36" s="117"/>
+      <c r="O36" s="117"/>
+      <c r="P36" s="117"/>
+      <c r="Q36" s="117"/>
+      <c r="R36" s="117"/>
+      <c r="S36"/>
+      <c r="T36"/>
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+      <c r="Y36"/>
+      <c r="Z36"/>
+      <c r="AA36"/>
+      <c r="AB36"/>
+      <c r="AC36"/>
+      <c r="AD36"/>
+      <c r="AE36"/>
+      <c r="AF36"/>
+      <c r="AG36"/>
+      <c r="AH36"/>
+      <c r="AI36"/>
+      <c r="AJ36"/>
+      <c r="AK36"/>
+      <c r="AL36"/>
+      <c r="AM36"/>
+      <c r="AN36"/>
+      <c r="AO36"/>
+      <c r="AP36"/>
+      <c r="AQ36"/>
+      <c r="AR36"/>
+      <c r="AS36"/>
+      <c r="AT36"/>
+      <c r="AU36"/>
+    </row>
+    <row r="37" spans="1:47">
+      <c r="A37" s="117"/>
+      <c r="B37" s="154" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" s="155" t="e">
+        <f>ROUND((MAX(C26:C27)+C35)*C36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="D36" s="10" t="e">
-        <f>SUM(C36:C36)</f>
+      <c r="D37" s="159" t="e">
+        <f>ROUND((MAX(D26:D27)+D35)*D36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="12"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="X36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="Z36" s="12"/>
-      <c r="AA36" s="12"/>
-      <c r="AB36" s="12"/>
-      <c r="AC36" s="12"/>
-      <c r="AD36" s="12"/>
-      <c r="AE36" s="12"/>
-      <c r="AF36" s="12"/>
-      <c r="AG36" s="12"/>
-      <c r="AH36" s="12"/>
-      <c r="AI36" s="12"/>
-      <c r="AJ36" s="12"/>
-      <c r="AK36" s="12"/>
-      <c r="AL36" s="12"/>
-      <c r="AM36" s="12"/>
-    </row>
-    <row r="37" spans="1:47" s="14" customFormat="1">
-      <c r="A37" s="12"/>
-      <c r="B37" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="15" t="e">
-        <f t="shared" ref="C37" si="2">(C25+C34+C35+C36)*3.5%</f>
+      <c r="E37" s="157"/>
+      <c r="F37" s="158"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+      <c r="I37" s="117"/>
+      <c r="J37" s="153"/>
+      <c r="K37" s="153"/>
+      <c r="L37" s="117"/>
+      <c r="M37" s="117"/>
+      <c r="N37" s="117"/>
+      <c r="O37" s="117"/>
+      <c r="P37" s="117"/>
+      <c r="Q37" s="117"/>
+      <c r="R37" s="117"/>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37"/>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37"/>
+      <c r="AF37"/>
+      <c r="AG37"/>
+      <c r="AH37"/>
+      <c r="AI37"/>
+      <c r="AJ37"/>
+      <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37"/>
+      <c r="AN37"/>
+      <c r="AO37"/>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+      <c r="AR37"/>
+      <c r="AS37"/>
+      <c r="AT37"/>
+      <c r="AU37"/>
+    </row>
+    <row r="38" spans="1:47" s="14" customFormat="1">
+      <c r="A38" s="12"/>
+      <c r="B38" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="13" t="e">
+        <f>((MAX(C26:C27))+C35)*16%</f>
         <v>#REF!</v>
       </c>
-      <c r="D37" s="10" t="e">
-        <f>SUM(C37:C37)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="12"/>
-      <c r="P37" s="12"/>
-      <c r="Q37" s="12"/>
-      <c r="R37" s="12"/>
-      <c r="S37" s="12"/>
-      <c r="T37" s="12"/>
-      <c r="U37" s="12"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="12"/>
-      <c r="AA37" s="12"/>
-      <c r="AB37" s="12"/>
-      <c r="AC37" s="12"/>
-      <c r="AD37" s="12"/>
-      <c r="AE37" s="12"/>
-      <c r="AF37" s="12"/>
-      <c r="AG37" s="12"/>
-      <c r="AH37" s="12"/>
-      <c r="AI37" s="12"/>
-      <c r="AJ37" s="12"/>
-      <c r="AK37" s="12"/>
-      <c r="AL37" s="12"/>
-      <c r="AM37" s="12"/>
-    </row>
-    <row r="38" spans="1:47">
-      <c r="B38" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="20" t="e">
-        <f t="shared" ref="C38" si="3">SUM(C34:C37)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D38" s="18" t="e">
+      <c r="D38" s="10" t="e">
         <f>SUM(C38:C38)</f>
         <v>#REF!</v>
       </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="AN38"/>
-      <c r="AO38"/>
-      <c r="AP38"/>
-      <c r="AQ38"/>
-      <c r="AR38"/>
-      <c r="AS38"/>
-      <c r="AT38"/>
-      <c r="AU38"/>
-    </row>
-    <row r="39" spans="1:47">
-      <c r="J39" s="1"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="1"/>
-      <c r="AS39"/>
-      <c r="AT39"/>
-      <c r="AU39"/>
-    </row>
-    <row r="40" spans="1:47">
-      <c r="O40" s="24" t="s">
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="12"/>
+      <c r="R38" s="12"/>
+      <c r="S38" s="12"/>
+      <c r="T38" s="12"/>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12"/>
+      <c r="AA38" s="12"/>
+      <c r="AB38" s="12"/>
+      <c r="AC38" s="12"/>
+      <c r="AD38" s="12"/>
+      <c r="AE38" s="12"/>
+      <c r="AF38" s="12"/>
+      <c r="AG38" s="12"/>
+      <c r="AH38" s="12"/>
+      <c r="AI38" s="12"/>
+      <c r="AJ38" s="12"/>
+      <c r="AK38" s="12"/>
+      <c r="AL38" s="12"/>
+      <c r="AM38" s="12"/>
+    </row>
+    <row r="39" spans="1:47" s="14" customFormat="1">
+      <c r="A39" s="12"/>
+      <c r="B39" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="15" t="e">
+        <f t="shared" ref="C39" si="1">((MAX(C26:C27))+C35)*2%</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D39" s="10" t="e">
+        <f>SUM(C39:C39)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="12"/>
+      <c r="P39" s="12"/>
+      <c r="Q39" s="12"/>
+      <c r="R39" s="12"/>
+      <c r="S39" s="12"/>
+      <c r="T39" s="12"/>
+      <c r="U39" s="12"/>
+      <c r="V39" s="12"/>
+      <c r="W39" s="12"/>
+      <c r="X39" s="12"/>
+      <c r="Y39" s="12"/>
+      <c r="Z39" s="12"/>
+      <c r="AA39" s="12"/>
+      <c r="AB39" s="12"/>
+      <c r="AC39" s="12"/>
+      <c r="AD39" s="12"/>
+      <c r="AE39" s="12"/>
+      <c r="AF39" s="12"/>
+      <c r="AG39" s="12"/>
+      <c r="AH39" s="12"/>
+      <c r="AI39" s="12"/>
+      <c r="AJ39" s="12"/>
+      <c r="AK39" s="12"/>
+      <c r="AL39" s="12"/>
+      <c r="AM39" s="12"/>
+    </row>
+    <row r="40" spans="1:47" s="14" customFormat="1">
+      <c r="A40" s="12"/>
+      <c r="B40" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="15" t="e">
+        <f t="shared" ref="C40" si="2">(C26+C35+C38+C39)*3.5%</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D40" s="10" t="e">
+        <f>SUM(C40:C40)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="12"/>
+      <c r="R40" s="12"/>
+      <c r="S40" s="12"/>
+      <c r="T40" s="12"/>
+      <c r="U40" s="12"/>
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="12"/>
+      <c r="Y40" s="12"/>
+      <c r="Z40" s="12"/>
+      <c r="AA40" s="12"/>
+      <c r="AB40" s="12"/>
+      <c r="AC40" s="12"/>
+      <c r="AD40" s="12"/>
+      <c r="AE40" s="12"/>
+      <c r="AF40" s="12"/>
+      <c r="AG40" s="12"/>
+      <c r="AH40" s="12"/>
+      <c r="AI40" s="12"/>
+      <c r="AJ40" s="12"/>
+      <c r="AK40" s="12"/>
+      <c r="AL40" s="12"/>
+      <c r="AM40" s="12"/>
+    </row>
+    <row r="41" spans="1:47">
+      <c r="B41" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="20" t="e">
+        <f t="shared" ref="C41" si="3">SUM(C35:C40)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D41" s="18" t="e">
+        <f>SUM(C41:C41)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="AN41"/>
+      <c r="AO41"/>
+      <c r="AP41"/>
+      <c r="AQ41"/>
+      <c r="AR41"/>
+      <c r="AS41"/>
+      <c r="AT41"/>
+      <c r="AU41"/>
+    </row>
+    <row r="42" spans="1:47">
+      <c r="J42" s="1"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="1"/>
+      <c r="AS42"/>
+      <c r="AT42"/>
+      <c r="AU42"/>
+    </row>
+    <row r="43" spans="1:47">
+      <c r="O43" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="P40" s="24">
+      <c r="P43" s="24">
         <v>3.7</v>
       </c>
     </row>
-    <row r="42" spans="1:47">
-      <c r="B42" s="159" t="s">
+    <row r="45" spans="1:47">
+      <c r="B45" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="159"/>
-      <c r="D42" s="159"/>
-      <c r="E42" s="159"/>
-      <c r="F42" s="159"/>
-      <c r="G42" s="159"/>
-      <c r="H42" s="159"/>
-      <c r="I42" s="159"/>
-      <c r="J42" s="159"/>
-      <c r="K42" s="159"/>
-      <c r="L42" s="159"/>
-    </row>
-    <row r="44" spans="1:47">
-      <c r="C44" s="21">
+      <c r="C45" s="207"/>
+      <c r="D45" s="207"/>
+      <c r="E45" s="207"/>
+      <c r="F45" s="207"/>
+      <c r="G45" s="207"/>
+      <c r="H45" s="207"/>
+      <c r="I45" s="207"/>
+      <c r="J45" s="207"/>
+      <c r="K45" s="207"/>
+      <c r="L45" s="207"/>
+    </row>
+    <row r="47" spans="1:47">
+      <c r="C47" s="21">
         <f>+C20</f>
         <v>1</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D47" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="AN44"/>
-      <c r="AO44"/>
-      <c r="AP44"/>
-      <c r="AQ44"/>
-      <c r="AR44"/>
-      <c r="AS44"/>
-      <c r="AT44"/>
-      <c r="AU44"/>
-    </row>
-    <row r="45" spans="1:47">
-      <c r="B45" s="28" t="s">
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="AN47"/>
+      <c r="AO47"/>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47"/>
+      <c r="AS47"/>
+      <c r="AT47"/>
+      <c r="AU47"/>
+    </row>
+    <row r="48" spans="1:47">
+      <c r="B48" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="23" t="e">
-        <f>$D$45*C44</f>
+      <c r="C48" s="23" t="e">
+        <f>$D$48*C47</f>
         <v>#REF!</v>
       </c>
-      <c r="D45" s="29" t="e">
+      <c r="D48" s="29" t="e">
         <f>IF(#REF!=0,IF('1'!E11="NUEVO",'2'!#REF!*40%,IF('1'!E11="ANTIGUO",'2'!#REF!*40%,IF('1'!E11="SOCIO",40%*(250*'1'!I11),IF('1'!E11="PILOTO",40%*(250*'1'!I11),IF('2'!#REF!&gt;0,40%*(250*'1'!I11),IF('1'!E11="MANUAL",40%*(IF('1'!#REF!&gt;250,('1'!#REF!*'1'!I11),IF('1'!#REF!&lt;=250,(250*'1'!I11)))))))))),IF(#REF!&lt;=250,(250*'1'!I11)*40%,#REF!*40%))</f>
         <v>#REF!</v>
       </c>
-      <c r="E45" s="77"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="AN45"/>
-      <c r="AO45"/>
-      <c r="AP45"/>
-      <c r="AQ45"/>
-      <c r="AR45"/>
-      <c r="AS45"/>
-      <c r="AT45"/>
-      <c r="AU45"/>
-    </row>
-    <row r="46" spans="1:47" s="1" customFormat="1">
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-    </row>
-    <row r="48" spans="1:47">
-      <c r="B48" s="88" t="s">
+      <c r="E48" s="77"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="AN48"/>
+      <c r="AO48"/>
+      <c r="AP48"/>
+      <c r="AQ48"/>
+      <c r="AR48"/>
+      <c r="AS48"/>
+      <c r="AT48"/>
+      <c r="AU48"/>
+    </row>
+    <row r="49" spans="2:47" s="1" customFormat="1">
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="51" spans="2:47">
+      <c r="B51" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="88"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="88"/>
-      <c r="H48" s="88"/>
-      <c r="I48" s="88"/>
-      <c r="J48" s="88"/>
-      <c r="K48" s="88"/>
-      <c r="L48" s="88"/>
-    </row>
-    <row r="50" spans="2:47">
-      <c r="B50" s="27" t="s">
+      <c r="C51" s="88"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="88"/>
+      <c r="I51" s="88"/>
+      <c r="J51" s="88"/>
+      <c r="K51" s="88"/>
+      <c r="L51" s="88"/>
+    </row>
+    <row r="53" spans="2:47">
+      <c r="B53" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="7" t="str">
-        <f t="shared" ref="C50" si="4">C11</f>
+      <c r="C53" s="7" t="str">
+        <f t="shared" ref="C53" si="4">C11</f>
         <v>BASE DE LAMPARA LED</v>
-      </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="AN50"/>
-      <c r="AO50"/>
-      <c r="AP50"/>
-      <c r="AQ50"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50"/>
-    </row>
-    <row r="51" spans="2:47">
-      <c r="B51" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="23" t="e">
-        <f>C18+C38+C31+'2'!C20*('1'!$J$31)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D51" s="23" t="e">
-        <f>SUM(C51:C51)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="AN51"/>
-      <c r="AO51"/>
-      <c r="AP51"/>
-      <c r="AQ51"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51"/>
-    </row>
-    <row r="52" spans="2:47">
-      <c r="B52" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="25">
-        <f>+C17</f>
-        <v>100</v>
-      </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="AN52"/>
-      <c r="AO52"/>
-      <c r="AP52"/>
-      <c r="AQ52"/>
-      <c r="AR52"/>
-      <c r="AS52"/>
-      <c r="AT52"/>
-      <c r="AU52"/>
-    </row>
-    <row r="53" spans="2:47">
-      <c r="B53" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="23" t="e">
-        <f t="shared" ref="C53" si="5">C51/C52</f>
-        <v>#REF!</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -5367,11 +5921,15 @@
       <c r="AU53"/>
     </row>
     <row r="54" spans="2:47">
-      <c r="B54" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="26" t="e">
-        <f>C53*$P$40</f>
+      <c r="B54" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="23" t="e">
+        <f>C18+C41+C32+'2'!C20*('1'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D54" s="23" t="e">
+        <f>SUM(C54:C54)</f>
         <v>#REF!</v>
       </c>
       <c r="E54" s="1"/>
@@ -5391,19 +5949,94 @@
       <c r="AT54"/>
       <c r="AU54"/>
     </row>
+    <row r="55" spans="2:47">
+      <c r="B55" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="25">
+        <f>+C17</f>
+        <v>100</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="AN55"/>
+      <c r="AO55"/>
+      <c r="AP55"/>
+      <c r="AQ55"/>
+      <c r="AR55"/>
+      <c r="AS55"/>
+      <c r="AT55"/>
+      <c r="AU55"/>
+    </row>
+    <row r="56" spans="2:47">
+      <c r="B56" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="23" t="e">
+        <f t="shared" ref="C56" si="5">C54/C55</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="AN56"/>
+      <c r="AO56"/>
+      <c r="AP56"/>
+      <c r="AQ56"/>
+      <c r="AR56"/>
+      <c r="AS56"/>
+      <c r="AT56"/>
+      <c r="AU56"/>
+    </row>
+    <row r="57" spans="2:47">
+      <c r="B57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="26" t="e">
+        <f>C56*$P$43</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="AN57"/>
+      <c r="AO57"/>
+      <c r="AP57"/>
+      <c r="AQ57"/>
+      <c r="AR57"/>
+      <c r="AS57"/>
+      <c r="AT57"/>
+      <c r="AU57"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="H33:I34"/>
-    <mergeCell ref="B28:L28"/>
+    <mergeCell ref="B45:L45"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="H34:I35"/>
+    <mergeCell ref="B29:L29"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <cellWatches>
-    <cellWatch r="D38"/>
+    <cellWatch r="D41"/>
   </cellWatches>
 </worksheet>
 </file>
--- a/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
+++ b/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA268BBC-95BD-493B-AE8E-73390473A86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC1E803-77D6-4AD5-BE4B-C1F847FC6B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1921,20 +1921,77 @@
     <xf numFmtId="165" fontId="0" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1967,9 +2024,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1981,71 +2035,17 @@
     <xf numFmtId="0" fontId="40" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="45" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3244,36 +3244,36 @@
     <row r="1" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:17">
-      <c r="C3" s="185" t="s">
+      <c r="C3" s="164" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="164"/>
     </row>
     <row r="5" spans="1:17" ht="25.8">
-      <c r="C5" s="186" t="s">
+      <c r="C5" s="165" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
+      <c r="D5" s="165"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="165"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="D7" s="201" t="s">
+      <c r="D7" s="180" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="201"/>
-      <c r="F7" s="201"/>
+      <c r="E7" s="180"/>
+      <c r="F7" s="180"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="33" t="s">
@@ -3291,12 +3291,12 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="203">
+      <c r="I8" s="183">
         <f>+'2'!D5</f>
         <v>1</v>
       </c>
-      <c r="J8" s="203"/>
-      <c r="K8" s="203"/>
+      <c r="J8" s="183"/>
+      <c r="K8" s="183"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="33" t="s">
@@ -3306,21 +3306,21 @@
       <c r="D9" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="187">
+      <c r="E9" s="166">
         <f ca="1">+TODAY()</f>
         <v>46121</v>
       </c>
-      <c r="F9" s="188"/>
+      <c r="F9" s="167"/>
       <c r="G9" s="31"/>
       <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="165">
+      <c r="I9" s="184">
         <f>+'2'!D6</f>
         <v>23.2</v>
       </c>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="J9" s="184"/>
+      <c r="K9" s="184"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="33" t="s">
@@ -3361,21 +3361,21 @@
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="202">
+      <c r="I11" s="181">
         <f>+'2'!D8</f>
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J11" s="202"/>
-      <c r="K11" s="202"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="181"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="176" t="s">
+      <c r="A13" s="182" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="60"/>
@@ -3388,11 +3388,11 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="168" t="s">
+      <c r="A14" s="187" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="168"/>
-      <c r="C14" s="168"/>
+      <c r="B14" s="187"/>
+      <c r="C14" s="187"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -3431,11 +3431,11 @@
       <c r="Q15" s="117"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="167" t="s">
+      <c r="A16" s="186" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="167"/>
-      <c r="C16" s="167"/>
+      <c r="B16" s="186"/>
+      <c r="C16" s="186"/>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
       <c r="F16" s="38"/>
@@ -3483,13 +3483,13 @@
       <c r="K18" s="31"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="176" t="s">
+      <c r="A19" s="182" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="176"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="176"/>
+      <c r="B19" s="182"/>
+      <c r="C19" s="182"/>
+      <c r="D19" s="182"/>
+      <c r="E19" s="182"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
       <c r="H19" s="58"/>
@@ -3695,13 +3695,13 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="178" t="s">
+      <c r="A30" s="196" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="179"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
+      <c r="B30" s="197"/>
+      <c r="C30" s="197"/>
+      <c r="D30" s="197"/>
+      <c r="E30" s="197"/>
       <c r="F30" s="122"/>
       <c r="G30" s="123"/>
       <c r="H30" s="123"/>
@@ -3809,6 +3809,7 @@
       <c r="H34" s="125"/>
       <c r="I34" s="127"/>
       <c r="J34" s="118">
+        <f>SUM(J31:J33)</f>
         <v>0</v>
       </c>
       <c r="K34" s="119" t="s">
@@ -3872,16 +3873,16 @@
       <c r="Q37" s="117"/>
     </row>
     <row r="38" spans="1:19" customFormat="1">
-      <c r="A38" s="180" t="s">
+      <c r="A38" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="181"/>
-      <c r="C38" s="181"/>
-      <c r="D38" s="181"/>
-      <c r="E38" s="181"/>
-      <c r="F38" s="181"/>
-      <c r="G38" s="181"/>
-      <c r="H38" s="181"/>
+      <c r="B38" s="199"/>
+      <c r="C38" s="199"/>
+      <c r="D38" s="199"/>
+      <c r="E38" s="199"/>
+      <c r="F38" s="199"/>
+      <c r="G38" s="199"/>
+      <c r="H38" s="199"/>
       <c r="I38" s="146"/>
       <c r="J38" s="147">
         <f>SUM(J34+J36)-J37</f>
@@ -3917,13 +3918,13 @@
       <c r="Q39" s="117"/>
     </row>
     <row r="40" spans="1:19" ht="15.6">
-      <c r="A40" s="175" t="s">
+      <c r="A40" s="194" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="175"/>
-      <c r="C40" s="175"/>
-      <c r="D40" s="175"/>
-      <c r="E40" s="175"/>
+      <c r="B40" s="194"/>
+      <c r="C40" s="194"/>
+      <c r="D40" s="194"/>
+      <c r="E40" s="194"/>
       <c r="F40" s="78"/>
       <c r="G40" s="78"/>
       <c r="H40" s="79"/>
@@ -3995,13 +3996,13 @@
       <c r="K43" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M43" s="191" t="s">
+      <c r="M43" s="170" t="s">
         <v>87</v>
       </c>
-      <c r="N43" s="191"/>
-      <c r="O43" s="191"/>
-      <c r="P43" s="191"/>
-      <c r="Q43" s="191"/>
+      <c r="N43" s="170"/>
+      <c r="O43" s="170"/>
+      <c r="P43" s="170"/>
+      <c r="Q43" s="170"/>
     </row>
     <row r="44" spans="1:19" ht="20.25" customHeight="1">
       <c r="A44" s="33"/>
@@ -4015,39 +4016,39 @@
       <c r="I44" s="37"/>
       <c r="J44" s="37"/>
       <c r="K44" s="34"/>
-      <c r="M44" s="192"/>
-      <c r="N44" s="192"/>
-      <c r="O44" s="192"/>
-      <c r="P44" s="192"/>
-      <c r="Q44" s="192"/>
+      <c r="M44" s="171"/>
+      <c r="N44" s="171"/>
+      <c r="O44" s="171"/>
+      <c r="P44" s="171"/>
+      <c r="Q44" s="171"/>
     </row>
     <row r="45" spans="1:19" ht="15" customHeight="1">
-      <c r="A45" s="171" t="s">
+      <c r="A45" s="190" t="s">
         <v>73</v>
       </c>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
-      <c r="D45" s="172"/>
-      <c r="E45" s="172"/>
-      <c r="F45" s="172"/>
-      <c r="G45" s="172"/>
-      <c r="H45" s="172"/>
-      <c r="I45" s="172"/>
-      <c r="J45" s="172"/>
-      <c r="K45" s="173"/>
-      <c r="M45" s="199" t="s">
+      <c r="B45" s="191"/>
+      <c r="C45" s="191"/>
+      <c r="D45" s="191"/>
+      <c r="E45" s="191"/>
+      <c r="F45" s="191"/>
+      <c r="G45" s="191"/>
+      <c r="H45" s="191"/>
+      <c r="I45" s="191"/>
+      <c r="J45" s="191"/>
+      <c r="K45" s="192"/>
+      <c r="M45" s="178" t="s">
         <v>46</v>
       </c>
-      <c r="N45" s="197" t="s">
+      <c r="N45" s="176" t="s">
         <v>60</v>
       </c>
-      <c r="O45" s="193" t="s">
+      <c r="O45" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="195" t="s">
+      <c r="P45" s="174" t="s">
         <v>84</v>
       </c>
-      <c r="Q45" s="189" t="s">
+      <c r="Q45" s="168" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4055,33 +4056,33 @@
       <c r="A46" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="169" t="s">
+      <c r="B46" s="188" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="174"/>
-      <c r="D46" s="170"/>
+      <c r="C46" s="193"/>
+      <c r="D46" s="189"/>
       <c r="E46" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="169" t="s">
+      <c r="F46" s="188" t="s">
         <v>61</v>
       </c>
-      <c r="G46" s="170"/>
+      <c r="G46" s="189"/>
       <c r="H46" s="5" t="s">
         <v>58</v>
       </c>
       <c r="I46" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="177" t="s">
+      <c r="J46" s="195" t="s">
         <v>59</v>
       </c>
-      <c r="K46" s="177"/>
-      <c r="M46" s="200"/>
-      <c r="N46" s="198"/>
-      <c r="O46" s="194"/>
-      <c r="P46" s="196"/>
-      <c r="Q46" s="190"/>
+      <c r="K46" s="195"/>
+      <c r="M46" s="179"/>
+      <c r="N46" s="177"/>
+      <c r="O46" s="173"/>
+      <c r="P46" s="175"/>
+      <c r="Q46" s="169"/>
     </row>
     <row r="47" spans="1:19" s="106" customFormat="1" ht="15.6">
       <c r="A47" s="103" t="s">
@@ -4115,15 +4116,15 @@
       <c r="I48" s="83"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
-      <c r="M48" s="161" t="s">
+      <c r="M48" s="201" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="161"/>
-      <c r="O48" s="161"/>
-      <c r="P48" s="161"/>
-      <c r="Q48" s="161"/>
-      <c r="R48" s="161"/>
-      <c r="S48" s="161"/>
+      <c r="N48" s="201"/>
+      <c r="O48" s="201"/>
+      <c r="P48" s="201"/>
+      <c r="Q48" s="201"/>
+      <c r="R48" s="201"/>
+      <c r="S48" s="201"/>
     </row>
     <row r="49" spans="1:19" ht="18.75" customHeight="1">
       <c r="A49" s="81" t="s">
@@ -4138,13 +4139,13 @@
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
       <c r="J49" s="31"/>
-      <c r="M49" s="161"/>
-      <c r="N49" s="161"/>
-      <c r="O49" s="161"/>
-      <c r="P49" s="161"/>
-      <c r="Q49" s="161"/>
-      <c r="R49" s="161"/>
-      <c r="S49" s="161"/>
+      <c r="M49" s="201"/>
+      <c r="N49" s="201"/>
+      <c r="O49" s="201"/>
+      <c r="P49" s="201"/>
+      <c r="Q49" s="201"/>
+      <c r="R49" s="201"/>
+      <c r="S49" s="201"/>
     </row>
     <row r="50" spans="1:19" ht="18">
       <c r="A50" s="82" t="s">
@@ -4213,11 +4214,11 @@
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="31"/>
-      <c r="M53" s="162" t="s">
+      <c r="M53" s="202" t="s">
         <v>98</v>
       </c>
       <c r="N53" s="31"/>
-      <c r="O53" s="160">
+      <c r="O53" s="200">
         <f>J14</f>
         <v>1220</v>
       </c>
@@ -4241,9 +4242,9 @@
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="31"/>
-      <c r="M54" s="162"/>
+      <c r="M54" s="202"/>
       <c r="N54" s="112"/>
-      <c r="O54" s="160"/>
+      <c r="O54" s="200"/>
       <c r="P54" s="31"/>
       <c r="Q54" s="163"/>
       <c r="R54" s="163"/>
@@ -4282,11 +4283,11 @@
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="31"/>
-      <c r="M56" s="162" t="s">
+      <c r="M56" s="202" t="s">
         <v>100</v>
       </c>
       <c r="N56" s="31"/>
-      <c r="O56" s="160" t="e">
+      <c r="O56" s="200" t="e">
         <f>J41+#REF!-#REF!</f>
         <v>#REF!</v>
       </c>
@@ -4310,9 +4311,9 @@
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="31"/>
-      <c r="M57" s="162"/>
+      <c r="M57" s="202"/>
       <c r="N57" s="112"/>
-      <c r="O57" s="164"/>
+      <c r="O57" s="203"/>
       <c r="P57" s="31"/>
       <c r="Q57" s="163"/>
       <c r="R57" s="163"/>
@@ -4337,10 +4338,10 @@
       <c r="S58" s="2"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="M59" s="182" t="s">
+      <c r="M59" s="160" t="s">
         <v>102</v>
       </c>
-      <c r="O59" s="183" t="e">
+      <c r="O59" s="161" t="e">
         <f>J42</f>
         <v>#REF!</v>
       </c>
@@ -4355,8 +4356,8 @@
       <c r="I60" s="32"/>
       <c r="J60" s="32"/>
       <c r="K60" s="31"/>
-      <c r="M60" s="182"/>
-      <c r="O60" s="184"/>
+      <c r="M60" s="160"/>
+      <c r="O60" s="162"/>
       <c r="Q60" s="163"/>
       <c r="R60" s="163"/>
       <c r="S60" s="163"/>
@@ -4373,19 +4374,19 @@
       <c r="J63" s="40"/>
     </row>
     <row r="65" spans="1:11" ht="21">
-      <c r="A65" s="166" t="s">
+      <c r="A65" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="B65" s="166"/>
-      <c r="C65" s="166"/>
-      <c r="D65" s="166"/>
-      <c r="E65" s="166"/>
-      <c r="F65" s="166"/>
-      <c r="G65" s="166"/>
-      <c r="H65" s="166"/>
-      <c r="I65" s="166"/>
-      <c r="J65" s="166"/>
-      <c r="K65" s="166"/>
+      <c r="B65" s="185"/>
+      <c r="C65" s="185"/>
+      <c r="D65" s="185"/>
+      <c r="E65" s="185"/>
+      <c r="F65" s="185"/>
+      <c r="G65" s="185"/>
+      <c r="H65" s="185"/>
+      <c r="I65" s="185"/>
+      <c r="J65" s="185"/>
+      <c r="K65" s="185"/>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
@@ -4721,6 +4722,25 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="35">
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="M48:S49"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="Q53:S54"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="Q56:S57"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="M59:M60"/>
     <mergeCell ref="O59:O60"/>
     <mergeCell ref="Q59:S60"/>
@@ -4737,25 +4757,6 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="M48:S49"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="Q53:S54"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="O56:O57"/>
-    <mergeCell ref="Q56:S57"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="COMPROBAR CANTIDAD DE CAJAS" error="Se debe ingresar la cantidad de cajas" sqref="I11" xr:uid="{3C2F8455-5D0D-41B0-BE98-F91BBC4383D3}">

--- a/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
+++ b/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC1E803-77D6-4AD5-BE4B-C1F847FC6B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F376B55-DF9E-4577-BD4B-CC639B410F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -23,15 +23,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1552,7 +1543,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1814,9 +1805,6 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1874,15 +1862,10 @@
     <xf numFmtId="0" fontId="44" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="44" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="44" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1909,89 +1892,32 @@
     <xf numFmtId="165" fontId="0" fillId="13" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2024,6 +1950,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2035,17 +1964,71 @@
     <xf numFmtId="0" fontId="40" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="45" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3216,64 +3199,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:S118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="4" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.88671875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.44140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.44140625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="10.88671875" style="1"/>
+    <col min="8" max="8" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:17">
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="181" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="181"/>
+      <c r="F3" s="181"/>
+      <c r="G3" s="181"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="164"/>
-    </row>
-    <row r="5" spans="1:17" ht="25.8">
-      <c r="C5" s="165" t="s">
+      <c r="C4" s="181"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+    </row>
+    <row r="5" spans="1:17" ht="26.25">
+      <c r="C5" s="182" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="165"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="182"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="D7" s="180" t="s">
+      <c r="D7" s="197" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="180"/>
-      <c r="F7" s="180"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="33" t="s">
@@ -3291,12 +3274,12 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="183">
+      <c r="I8" s="199">
         <f>+'2'!D5</f>
         <v>1</v>
       </c>
-      <c r="J8" s="183"/>
-      <c r="K8" s="183"/>
+      <c r="J8" s="199"/>
+      <c r="K8" s="199"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="33" t="s">
@@ -3306,21 +3289,21 @@
       <c r="D9" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="166">
+      <c r="E9" s="183">
         <f ca="1">+TODAY()</f>
-        <v>46121</v>
-      </c>
-      <c r="F9" s="167"/>
+        <v>46122</v>
+      </c>
+      <c r="F9" s="184"/>
       <c r="G9" s="31"/>
       <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="184">
+      <c r="I9" s="161">
         <f>+'2'!D6</f>
         <v>23.2</v>
       </c>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
+      <c r="J9" s="161"/>
+      <c r="K9" s="161"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="33" t="s">
@@ -3361,21 +3344,21 @@
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="181">
+      <c r="I11" s="198">
         <f>+'2'!D8</f>
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J11" s="181"/>
-      <c r="K11" s="181"/>
+      <c r="J11" s="198"/>
+      <c r="K11" s="198"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="182" t="s">
+      <c r="A13" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="182"/>
-      <c r="C13" s="182"/>
-      <c r="D13" s="182"/>
-      <c r="E13" s="182"/>
+      <c r="B13" s="172"/>
+      <c r="C13" s="172"/>
+      <c r="D13" s="172"/>
+      <c r="E13" s="172"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="60"/>
@@ -3388,11 +3371,11 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="187" t="s">
+      <c r="A14" s="164" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="187"/>
-      <c r="C14" s="187"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="164"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -3406,36 +3389,36 @@
       </c>
     </row>
     <row r="15" spans="1:17" customFormat="1">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="118">
+      <c r="B15" s="114"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="117">
         <v>0</v>
       </c>
-      <c r="K15" s="119" t="s">
+      <c r="K15" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="117"/>
-      <c r="O15" s="117"/>
-      <c r="P15" s="117"/>
-      <c r="Q15" s="117"/>
+      <c r="L15" s="116"/>
+      <c r="M15" s="116"/>
+      <c r="N15" s="116"/>
+      <c r="O15" s="116"/>
+      <c r="P15" s="116"/>
+      <c r="Q15" s="116"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="186" t="s">
+      <c r="A16" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="186"/>
-      <c r="C16" s="186"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="163"/>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
       <c r="F16" s="38"/>
@@ -3457,7 +3440,7 @@
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="114"/>
+      <c r="F17" s="113"/>
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
@@ -3483,13 +3466,13 @@
       <c r="K18" s="31"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="182" t="s">
+      <c r="A19" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="182"/>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
+      <c r="B19" s="172"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="172"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
       <c r="H19" s="58"/>
@@ -3527,31 +3510,31 @@
       </c>
     </row>
     <row r="21" spans="1:17" customFormat="1">
-      <c r="A21" s="116" t="s">
+      <c r="A21" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="116"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="120">
+      <c r="B21" s="115"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="119">
         <v>0</v>
       </c>
-      <c r="J21" s="118">
+      <c r="J21" s="117">
         <v>0</v>
       </c>
-      <c r="K21" s="119" t="s">
+      <c r="K21" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="L21" s="117"/>
-      <c r="M21" s="117"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="117"/>
-      <c r="P21" s="117"/>
-      <c r="Q21" s="117"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="116"/>
+      <c r="N21" s="120"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="116"/>
+      <c r="Q21" s="116"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="31" t="s">
@@ -3695,236 +3678,235 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="196" t="s">
+      <c r="A30" s="174" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="197"/>
-      <c r="C30" s="197"/>
-      <c r="D30" s="197"/>
-      <c r="E30" s="197"/>
-      <c r="F30" s="122"/>
-      <c r="G30" s="123"/>
-      <c r="H30" s="123"/>
-      <c r="I30" s="124" t="s">
+      <c r="B30" s="175"/>
+      <c r="C30" s="175"/>
+      <c r="D30" s="175"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="122"/>
+      <c r="I30" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="124" t="s">
+      <c r="J30" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="124" t="s">
+      <c r="K30" s="123" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:17" customFormat="1">
-      <c r="A31" s="116" t="s">
+      <c r="A31" s="115" t="s">
         <v>129</v>
       </c>
-      <c r="B31" s="125"/>
-      <c r="C31" s="125"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="125"/>
-      <c r="F31" s="125"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="125"/>
-      <c r="I31" s="119" t="s">
+      <c r="B31" s="124"/>
+      <c r="C31" s="124"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="124"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="124"/>
+      <c r="I31" s="118" t="s">
         <v>132</v>
       </c>
-      <c r="J31" s="118">
+      <c r="J31" s="117">
         <v>0</v>
       </c>
-      <c r="K31" s="119" t="s">
+      <c r="K31" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="L31" s="117"/>
-      <c r="M31" s="117"/>
-      <c r="N31" s="117"/>
-      <c r="O31" s="117"/>
-      <c r="P31" s="117"/>
-      <c r="Q31" s="117"/>
+      <c r="L31" s="116"/>
+      <c r="M31" s="116"/>
+      <c r="N31" s="116"/>
+      <c r="O31" s="116"/>
+      <c r="P31" s="116"/>
+      <c r="Q31" s="116"/>
     </row>
     <row r="32" spans="1:17" customFormat="1">
-      <c r="A32" s="125" t="s">
+      <c r="A32" s="124" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="125"/>
-      <c r="C32" s="125"/>
-      <c r="D32" s="125"/>
-      <c r="E32" s="125"/>
-      <c r="F32" s="125"/>
-      <c r="G32" s="125"/>
-      <c r="H32" s="125"/>
-      <c r="I32" s="119" t="s">
+      <c r="B32" s="124"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="124"/>
+      <c r="H32" s="124"/>
+      <c r="I32" s="118" t="s">
         <v>134</v>
       </c>
-      <c r="J32" s="118">
+      <c r="J32" s="117">
         <v>0</v>
       </c>
-      <c r="K32" s="119" t="s">
+      <c r="K32" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="L32" s="117"/>
-      <c r="M32" s="117"/>
-      <c r="N32" s="117"/>
-      <c r="O32" s="117"/>
-      <c r="P32" s="117"/>
-      <c r="Q32" s="117"/>
+      <c r="L32" s="116"/>
+      <c r="M32" s="116"/>
+      <c r="N32" s="116"/>
+      <c r="O32" s="116"/>
+      <c r="P32" s="116"/>
+      <c r="Q32" s="116"/>
     </row>
     <row r="33" spans="1:19" customFormat="1">
-      <c r="A33" s="128" t="s">
+      <c r="A33" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="128"/>
-      <c r="C33" s="128"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="128"/>
-      <c r="F33" s="128"/>
-      <c r="G33" s="128"/>
-      <c r="H33" s="128"/>
-      <c r="I33" s="129" t="s">
+      <c r="B33" s="127"/>
+      <c r="C33" s="127"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="127"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="128" t="s">
         <v>132</v>
       </c>
-      <c r="J33" s="130">
+      <c r="J33" s="129">
         <v>0</v>
       </c>
-      <c r="K33" s="131" t="s">
+      <c r="K33" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="L33" s="117"/>
-      <c r="M33" s="117"/>
-      <c r="N33" s="117"/>
-      <c r="O33" s="117"/>
-      <c r="P33" s="117"/>
-      <c r="Q33" s="117"/>
+      <c r="L33" s="116"/>
+      <c r="M33" s="116"/>
+      <c r="N33" s="116"/>
+      <c r="O33" s="116"/>
+      <c r="P33" s="116"/>
+      <c r="Q33" s="116"/>
     </row>
     <row r="34" spans="1:19" customFormat="1">
-      <c r="A34" s="126" t="s">
+      <c r="A34" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="125"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
-      <c r="H34" s="125"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="118">
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="124"/>
+      <c r="G34" s="124"/>
+      <c r="H34" s="124"/>
+      <c r="I34" s="126"/>
+      <c r="J34" s="117">
         <f>SUM(J31:J33)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="119" t="s">
+      <c r="K34" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="L34" s="117"/>
-      <c r="M34" s="117"/>
-      <c r="N34" s="117"/>
-      <c r="O34" s="117"/>
-      <c r="P34" s="117"/>
-      <c r="Q34" s="117"/>
+      <c r="L34" s="116"/>
+      <c r="M34" s="116"/>
+      <c r="N34" s="116"/>
+      <c r="O34" s="116"/>
+      <c r="P34" s="116"/>
+      <c r="Q34" s="116"/>
     </row>
     <row r="36" spans="1:19" customFormat="1">
       <c r="A36" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="132"/>
-      <c r="C36" s="132"/>
-      <c r="D36" s="132"/>
-      <c r="E36" s="132"/>
-      <c r="F36" s="132"/>
-      <c r="G36" s="132"/>
-      <c r="H36" s="132"/>
-      <c r="I36" s="133"/>
-      <c r="J36" s="134">
+      <c r="B36" s="131"/>
+      <c r="C36" s="131"/>
+      <c r="D36" s="131"/>
+      <c r="E36" s="131"/>
+      <c r="F36" s="131"/>
+      <c r="G36" s="131"/>
+      <c r="H36" s="131"/>
+      <c r="I36" s="132"/>
+      <c r="J36" s="133">
         <v>0</v>
       </c>
-      <c r="K36" s="135" t="s">
+      <c r="K36" s="134" t="s">
         <v>35</v>
       </c>
-      <c r="L36" s="117"/>
-      <c r="M36" s="117"/>
-      <c r="N36" s="117"/>
-      <c r="O36" s="117"/>
-      <c r="P36" s="117"/>
-      <c r="Q36" s="117"/>
+      <c r="L36" s="116"/>
+      <c r="M36" s="116"/>
+      <c r="N36" s="116"/>
+      <c r="O36" s="116"/>
+      <c r="P36" s="116"/>
+      <c r="Q36" s="116"/>
     </row>
     <row r="37" spans="1:19" customFormat="1">
-      <c r="A37" s="136" t="s">
+      <c r="A37" s="135" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="137"/>
-      <c r="C37" s="137"/>
-      <c r="D37" s="137"/>
-      <c r="E37" s="137"/>
-      <c r="F37" s="137"/>
-      <c r="G37" s="137"/>
-      <c r="H37" s="137"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="139">
+      <c r="B37" s="136"/>
+      <c r="C37" s="136"/>
+      <c r="D37" s="136"/>
+      <c r="E37" s="136"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="136"/>
+      <c r="H37" s="136"/>
+      <c r="I37" s="137"/>
+      <c r="J37" s="138">
         <v>0</v>
       </c>
-      <c r="K37" s="140" t="s">
+      <c r="K37" s="139" t="s">
         <v>35</v>
       </c>
-      <c r="L37" s="117"/>
-      <c r="M37" s="117"/>
-      <c r="N37" s="117"/>
-      <c r="O37" s="117"/>
-      <c r="P37" s="117"/>
-      <c r="Q37" s="117"/>
+      <c r="L37" s="116"/>
+      <c r="M37" s="116"/>
+      <c r="N37" s="116"/>
+      <c r="O37" s="116"/>
+      <c r="P37" s="116"/>
+      <c r="Q37" s="116"/>
     </row>
     <row r="38" spans="1:19" customFormat="1">
-      <c r="A38" s="198" t="s">
+      <c r="A38" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="199"/>
-      <c r="C38" s="199"/>
-      <c r="D38" s="199"/>
-      <c r="E38" s="199"/>
-      <c r="F38" s="199"/>
-      <c r="G38" s="199"/>
-      <c r="H38" s="199"/>
-      <c r="I38" s="146"/>
-      <c r="J38" s="147">
+      <c r="B38" s="177"/>
+      <c r="C38" s="177"/>
+      <c r="D38" s="177"/>
+      <c r="E38" s="177"/>
+      <c r="F38" s="177"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="177"/>
+      <c r="I38" s="142"/>
+      <c r="J38" s="143">
         <f>SUM(J34+J36)-J37</f>
         <v>0</v>
       </c>
-      <c r="K38" s="148" t="s">
+      <c r="K38" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="L38" s="117"/>
-      <c r="M38" s="117"/>
-      <c r="N38" s="117"/>
-      <c r="O38" s="117"/>
-      <c r="P38" s="117"/>
-      <c r="Q38" s="117"/>
+      <c r="L38" s="116"/>
+      <c r="M38" s="116"/>
+      <c r="N38" s="116"/>
+      <c r="O38" s="116"/>
+      <c r="P38" s="116"/>
+      <c r="Q38" s="116"/>
     </row>
     <row r="39" spans="1:19" customFormat="1">
-      <c r="A39" s="141"/>
-      <c r="B39" s="142"/>
-      <c r="C39" s="142"/>
-      <c r="D39" s="142"/>
-      <c r="E39" s="142"/>
-      <c r="F39" s="142"/>
-      <c r="G39" s="142"/>
-      <c r="H39" s="142"/>
-      <c r="I39" s="143"/>
-      <c r="J39" s="144"/>
-      <c r="K39" s="145"/>
-      <c r="L39" s="117"/>
-      <c r="M39" s="117"/>
-      <c r="N39" s="117"/>
-      <c r="O39" s="117"/>
-      <c r="P39" s="117"/>
-      <c r="Q39" s="117"/>
-    </row>
-    <row r="40" spans="1:19" ht="15.6">
-      <c r="A40" s="194" t="s">
+      <c r="B39" s="131"/>
+      <c r="C39" s="131"/>
+      <c r="D39" s="131"/>
+      <c r="E39" s="131"/>
+      <c r="F39" s="131"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="131"/>
+      <c r="I39" s="132"/>
+      <c r="J39" s="140"/>
+      <c r="K39" s="141"/>
+      <c r="L39" s="116"/>
+      <c r="M39" s="116"/>
+      <c r="N39" s="116"/>
+      <c r="O39" s="116"/>
+      <c r="P39" s="116"/>
+      <c r="Q39" s="116"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75">
+      <c r="A40" s="171" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="194"/>
-      <c r="C40" s="194"/>
-      <c r="D40" s="194"/>
-      <c r="E40" s="194"/>
+      <c r="B40" s="171"/>
+      <c r="C40" s="171"/>
+      <c r="D40" s="171"/>
+      <c r="E40" s="171"/>
       <c r="F40" s="78"/>
       <c r="G40" s="78"/>
       <c r="H40" s="79"/>
@@ -3948,9 +3930,9 @@
       <c r="G41" s="31"/>
       <c r="H41" s="45"/>
       <c r="I41" s="45"/>
-      <c r="J41" s="45" t="e">
-        <f>+'2'!D48+'2'!D22</f>
-        <v>#REF!</v>
+      <c r="J41" s="45">
+        <f>J38</f>
+        <v>0</v>
       </c>
       <c r="K41" s="34" t="s">
         <v>35</v>
@@ -3996,13 +3978,13 @@
       <c r="K43" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M43" s="170" t="s">
+      <c r="M43" s="187" t="s">
         <v>87</v>
       </c>
-      <c r="N43" s="170"/>
-      <c r="O43" s="170"/>
-      <c r="P43" s="170"/>
-      <c r="Q43" s="170"/>
+      <c r="N43" s="187"/>
+      <c r="O43" s="187"/>
+      <c r="P43" s="187"/>
+      <c r="Q43" s="187"/>
     </row>
     <row r="44" spans="1:19" ht="20.25" customHeight="1">
       <c r="A44" s="33"/>
@@ -4016,39 +3998,39 @@
       <c r="I44" s="37"/>
       <c r="J44" s="37"/>
       <c r="K44" s="34"/>
-      <c r="M44" s="171"/>
-      <c r="N44" s="171"/>
-      <c r="O44" s="171"/>
-      <c r="P44" s="171"/>
-      <c r="Q44" s="171"/>
+      <c r="M44" s="188"/>
+      <c r="N44" s="188"/>
+      <c r="O44" s="188"/>
+      <c r="P44" s="188"/>
+      <c r="Q44" s="188"/>
     </row>
     <row r="45" spans="1:19" ht="15" customHeight="1">
-      <c r="A45" s="190" t="s">
+      <c r="A45" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="B45" s="191"/>
-      <c r="C45" s="191"/>
-      <c r="D45" s="191"/>
-      <c r="E45" s="191"/>
-      <c r="F45" s="191"/>
-      <c r="G45" s="191"/>
-      <c r="H45" s="191"/>
-      <c r="I45" s="191"/>
-      <c r="J45" s="191"/>
-      <c r="K45" s="192"/>
-      <c r="M45" s="178" t="s">
+      <c r="B45" s="168"/>
+      <c r="C45" s="168"/>
+      <c r="D45" s="168"/>
+      <c r="E45" s="168"/>
+      <c r="F45" s="168"/>
+      <c r="G45" s="168"/>
+      <c r="H45" s="168"/>
+      <c r="I45" s="168"/>
+      <c r="J45" s="168"/>
+      <c r="K45" s="169"/>
+      <c r="M45" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="N45" s="176" t="s">
+      <c r="N45" s="193" t="s">
         <v>60</v>
       </c>
-      <c r="O45" s="172" t="s">
+      <c r="O45" s="189" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="174" t="s">
+      <c r="P45" s="191" t="s">
         <v>84</v>
       </c>
-      <c r="Q45" s="168" t="s">
+      <c r="Q45" s="185" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4056,35 +4038,35 @@
       <c r="A46" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="188" t="s">
+      <c r="B46" s="165" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="193"/>
-      <c r="D46" s="189"/>
+      <c r="C46" s="170"/>
+      <c r="D46" s="166"/>
       <c r="E46" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="188" t="s">
+      <c r="F46" s="165" t="s">
         <v>61</v>
       </c>
-      <c r="G46" s="189"/>
+      <c r="G46" s="166"/>
       <c r="H46" s="5" t="s">
         <v>58</v>
       </c>
       <c r="I46" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="195" t="s">
+      <c r="J46" s="173" t="s">
         <v>59</v>
       </c>
-      <c r="K46" s="195"/>
-      <c r="M46" s="179"/>
-      <c r="N46" s="177"/>
-      <c r="O46" s="173"/>
-      <c r="P46" s="175"/>
-      <c r="Q46" s="169"/>
-    </row>
-    <row r="47" spans="1:19" s="106" customFormat="1" ht="15.6">
+      <c r="K46" s="173"/>
+      <c r="M46" s="196"/>
+      <c r="N46" s="194"/>
+      <c r="O46" s="190"/>
+      <c r="P46" s="192"/>
+      <c r="Q46" s="186"/>
+    </row>
+    <row r="47" spans="1:19" s="106" customFormat="1" ht="15.75">
       <c r="A47" s="103" t="s">
         <v>8</v>
       </c>
@@ -4116,15 +4098,15 @@
       <c r="I48" s="83"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
-      <c r="M48" s="201" t="s">
+      <c r="M48" s="157" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="201"/>
-      <c r="O48" s="201"/>
-      <c r="P48" s="201"/>
-      <c r="Q48" s="201"/>
-      <c r="R48" s="201"/>
-      <c r="S48" s="201"/>
+      <c r="N48" s="157"/>
+      <c r="O48" s="157"/>
+      <c r="P48" s="157"/>
+      <c r="Q48" s="157"/>
+      <c r="R48" s="157"/>
+      <c r="S48" s="157"/>
     </row>
     <row r="49" spans="1:19" ht="18.75" customHeight="1">
       <c r="A49" s="81" t="s">
@@ -4139,15 +4121,15 @@
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
       <c r="J49" s="31"/>
-      <c r="M49" s="201"/>
-      <c r="N49" s="201"/>
-      <c r="O49" s="201"/>
-      <c r="P49" s="201"/>
-      <c r="Q49" s="201"/>
-      <c r="R49" s="201"/>
-      <c r="S49" s="201"/>
-    </row>
-    <row r="50" spans="1:19" ht="18">
+      <c r="M49" s="157"/>
+      <c r="N49" s="157"/>
+      <c r="O49" s="157"/>
+      <c r="P49" s="157"/>
+      <c r="Q49" s="157"/>
+      <c r="R49" s="157"/>
+      <c r="S49" s="157"/>
+    </row>
+    <row r="50" spans="1:19" ht="18.75">
       <c r="A50" s="82" t="s">
         <v>65</v>
       </c>
@@ -4161,7 +4143,7 @@
       <c r="I50" s="31"/>
       <c r="J50" s="31"/>
     </row>
-    <row r="51" spans="1:19" ht="18">
+    <row r="51" spans="1:19" ht="18.75">
       <c r="A51" s="82" t="s">
         <v>66</v>
       </c>
@@ -4184,7 +4166,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="18">
+    <row r="52" spans="1:19" ht="18.75">
       <c r="A52" s="82" t="s">
         <v>76</v>
       </c>
@@ -4214,20 +4196,20 @@
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="31"/>
-      <c r="M53" s="202" t="s">
+      <c r="M53" s="158" t="s">
         <v>98</v>
       </c>
       <c r="N53" s="31"/>
-      <c r="O53" s="200">
+      <c r="O53" s="156">
         <f>J14</f>
         <v>1220</v>
       </c>
       <c r="P53" s="31"/>
-      <c r="Q53" s="163" t="s">
+      <c r="Q53" s="159" t="s">
         <v>99</v>
       </c>
-      <c r="R53" s="163"/>
-      <c r="S53" s="163"/>
+      <c r="R53" s="159"/>
+      <c r="S53" s="159"/>
     </row>
     <row r="54" spans="1:19" ht="18.75" customHeight="1">
       <c r="A54" s="82" t="s">
@@ -4242,13 +4224,13 @@
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="31"/>
-      <c r="M54" s="202"/>
+      <c r="M54" s="158"/>
       <c r="N54" s="112"/>
-      <c r="O54" s="200"/>
+      <c r="O54" s="156"/>
       <c r="P54" s="31"/>
-      <c r="Q54" s="163"/>
-      <c r="R54" s="163"/>
-      <c r="S54" s="163"/>
+      <c r="Q54" s="159"/>
+      <c r="R54" s="159"/>
+      <c r="S54" s="159"/>
     </row>
     <row r="55" spans="1:19" ht="18.75" customHeight="1">
       <c r="A55" s="82" t="s">
@@ -4270,7 +4252,7 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
     </row>
-    <row r="56" spans="1:19" ht="18">
+    <row r="56" spans="1:19" ht="18.75">
       <c r="A56" s="82" t="s">
         <v>79</v>
       </c>
@@ -4283,22 +4265,22 @@
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="31"/>
-      <c r="M56" s="202" t="s">
+      <c r="M56" s="158" t="s">
         <v>100</v>
       </c>
       <c r="N56" s="31"/>
-      <c r="O56" s="200" t="e">
-        <f>J41+#REF!-#REF!</f>
-        <v>#REF!</v>
+      <c r="O56" s="156">
+        <f>J41</f>
+        <v>0</v>
       </c>
       <c r="P56" s="31"/>
-      <c r="Q56" s="163" t="s">
+      <c r="Q56" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="R56" s="163"/>
-      <c r="S56" s="163"/>
-    </row>
-    <row r="57" spans="1:19" ht="18">
+      <c r="R56" s="159"/>
+      <c r="S56" s="159"/>
+    </row>
+    <row r="57" spans="1:19" ht="18.75">
       <c r="A57" s="82" t="s">
         <v>75</v>
       </c>
@@ -4311,13 +4293,13 @@
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="31"/>
-      <c r="M57" s="202"/>
+      <c r="M57" s="158"/>
       <c r="N57" s="112"/>
-      <c r="O57" s="203"/>
+      <c r="O57" s="160"/>
       <c r="P57" s="31"/>
-      <c r="Q57" s="163"/>
-      <c r="R57" s="163"/>
-      <c r="S57" s="163"/>
+      <c r="Q57" s="159"/>
+      <c r="R57" s="159"/>
+      <c r="S57" s="159"/>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" s="31"/>
@@ -4338,31 +4320,31 @@
       <c r="S58" s="2"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="M59" s="160" t="s">
+      <c r="M59" s="178" t="s">
         <v>102</v>
       </c>
-      <c r="O59" s="161" t="e">
+      <c r="O59" s="179" t="e">
         <f>J42</f>
         <v>#REF!</v>
       </c>
-      <c r="Q59" s="163" t="s">
+      <c r="Q59" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="R59" s="163"/>
-      <c r="S59" s="163"/>
-    </row>
-    <row r="60" spans="1:19" ht="18">
+      <c r="R59" s="159"/>
+      <c r="S59" s="159"/>
+    </row>
+    <row r="60" spans="1:19" ht="18.75">
       <c r="H60" s="32"/>
       <c r="I60" s="32"/>
       <c r="J60" s="32"/>
       <c r="K60" s="31"/>
-      <c r="M60" s="160"/>
-      <c r="O60" s="162"/>
-      <c r="Q60" s="163"/>
-      <c r="R60" s="163"/>
-      <c r="S60" s="163"/>
-    </row>
-    <row r="61" spans="1:19" ht="18">
+      <c r="M60" s="178"/>
+      <c r="O60" s="180"/>
+      <c r="Q60" s="159"/>
+      <c r="R60" s="159"/>
+      <c r="S60" s="159"/>
+    </row>
+    <row r="61" spans="1:19" ht="18.75">
       <c r="H61" s="32"/>
       <c r="I61" s="32"/>
       <c r="J61" s="32"/>
@@ -4374,19 +4356,19 @@
       <c r="J63" s="40"/>
     </row>
     <row r="65" spans="1:11" ht="21">
-      <c r="A65" s="185" t="s">
+      <c r="A65" s="162" t="s">
         <v>45</v>
       </c>
-      <c r="B65" s="185"/>
-      <c r="C65" s="185"/>
-      <c r="D65" s="185"/>
-      <c r="E65" s="185"/>
-      <c r="F65" s="185"/>
-      <c r="G65" s="185"/>
-      <c r="H65" s="185"/>
-      <c r="I65" s="185"/>
-      <c r="J65" s="185"/>
-      <c r="K65" s="185"/>
+      <c r="B65" s="162"/>
+      <c r="C65" s="162"/>
+      <c r="D65" s="162"/>
+      <c r="E65" s="162"/>
+      <c r="F65" s="162"/>
+      <c r="G65" s="162"/>
+      <c r="H65" s="162"/>
+      <c r="I65" s="162"/>
+      <c r="J65" s="162"/>
+      <c r="K65" s="162"/>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
@@ -4692,10 +4674,10 @@
     <row r="109" spans="1:4">
       <c r="B109" s="41"/>
     </row>
-    <row r="110" spans="1:4" ht="15.6">
+    <row r="110" spans="1:4" ht="15.75">
       <c r="B110" s="42"/>
     </row>
-    <row r="111" spans="1:4" ht="15.6">
+    <row r="111" spans="1:4" ht="15.75">
       <c r="B111" s="42"/>
     </row>
     <row r="113" spans="2:10">
@@ -4716,31 +4698,12 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
     </row>
-    <row r="118" spans="2:10" ht="15.6">
+    <row r="118" spans="2:10" ht="15.75">
       <c r="B118" s="44"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="35">
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="M48:S49"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="Q53:S54"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="O56:O57"/>
-    <mergeCell ref="Q56:S57"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="M59:M60"/>
     <mergeCell ref="O59:O60"/>
     <mergeCell ref="Q59:S60"/>
@@ -4757,6 +4720,25 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="M48:S49"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="Q53:S54"/>
+    <mergeCell ref="M56:M57"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="Q56:S57"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="COMPROBAR CANTIDAD DE CAJAS" error="Se debe ingresar la cantidad de cajas" sqref="I11" xr:uid="{3C2F8455-5D0D-41B0-BE98-F91BBC4383D3}">
@@ -4783,36 +4765,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AV57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="2"/>
-    <col min="6" max="6" width="11.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.44140625" style="2"/>
-    <col min="9" max="9" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="2"/>
+    <col min="6" max="6" width="11.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="2"/>
+    <col min="9" max="9" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="47" width="11.44140625" style="1"/>
+    <col min="12" max="12" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="47" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:47" ht="15" thickBot="1">
-      <c r="B1" s="204" t="s">
+    <row r="1" spans="2:47" ht="15.75" thickBot="1">
+      <c r="B1" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="206"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="201"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="201"/>
+      <c r="I1" s="201"/>
+      <c r="J1" s="201"/>
+      <c r="K1" s="201"/>
+      <c r="L1" s="202"/>
     </row>
     <row r="2" spans="2:47" s="1" customFormat="1" ht="35.1" customHeight="1">
       <c r="B2" s="43"/>
@@ -5200,20 +5182,16 @@
       <c r="AU20"/>
     </row>
     <row r="21" spans="2:48" ht="15" customHeight="1">
-      <c r="B21" s="149" t="s">
+      <c r="B21" s="145" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="150">
+      <c r="C21" s="146">
         <v>0</v>
       </c>
-      <c r="D21" s="150">
+      <c r="D21" s="146">
         <v>0</v>
       </c>
       <c r="E21" s="30"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -5244,7 +5222,7 @@
         <v>#REF!</v>
       </c>
       <c r="E22" s="77"/>
-      <c r="F22" s="208"/>
+      <c r="F22" s="204"/>
       <c r="G22" s="48"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5278,7 +5256,7 @@
         <v>#REF!</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="208"/>
+      <c r="F23" s="204"/>
       <c r="G23" s="48"/>
       <c r="H23" s="1"/>
       <c r="I23" s="76"/>
@@ -5413,19 +5391,19 @@
       <c r="G28" s="48"/>
     </row>
     <row r="29" spans="2:48">
-      <c r="B29" s="210" t="s">
+      <c r="B29" s="206" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="210"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
-      <c r="G29" s="210"/>
-      <c r="H29" s="210"/>
-      <c r="I29" s="210"/>
-      <c r="J29" s="210"/>
-      <c r="K29" s="210"/>
-      <c r="L29" s="210"/>
+      <c r="C29" s="206"/>
+      <c r="D29" s="206"/>
+      <c r="E29" s="206"/>
+      <c r="F29" s="206"/>
+      <c r="G29" s="206"/>
+      <c r="H29" s="206"/>
+      <c r="I29" s="206"/>
+      <c r="J29" s="206"/>
+      <c r="K29" s="206"/>
+      <c r="L29" s="206"/>
     </row>
     <row r="31" spans="2:48">
       <c r="C31" s="50"/>
@@ -5460,8 +5438,8 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="209"/>
-      <c r="I34" s="209"/>
+      <c r="H34" s="205"/>
+      <c r="I34" s="205"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -5489,8 +5467,8 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="209"/>
-      <c r="I35" s="209"/>
+      <c r="H35" s="205"/>
+      <c r="I35" s="205"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -5504,28 +5482,28 @@
       <c r="AU35"/>
     </row>
     <row r="36" spans="1:47">
-      <c r="A36" s="117"/>
-      <c r="B36" s="151"/>
-      <c r="C36" s="152">
+      <c r="A36" s="116"/>
+      <c r="B36" s="147"/>
+      <c r="C36" s="148">
         <v>0</v>
       </c>
-      <c r="D36" s="152">
+      <c r="D36" s="148">
         <v>0</v>
       </c>
-      <c r="E36" s="156"/>
-      <c r="F36" s="156"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="117"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="153"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="117"/>
-      <c r="N36" s="117"/>
-      <c r="O36" s="117"/>
-      <c r="P36" s="117"/>
-      <c r="Q36" s="117"/>
-      <c r="R36" s="117"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="152"/>
+      <c r="G36" s="116"/>
+      <c r="H36" s="116"/>
+      <c r="I36" s="116"/>
+      <c r="J36" s="149"/>
+      <c r="K36" s="149"/>
+      <c r="L36" s="116"/>
+      <c r="M36" s="116"/>
+      <c r="N36" s="116"/>
+      <c r="O36" s="116"/>
+      <c r="P36" s="116"/>
+      <c r="Q36" s="116"/>
+      <c r="R36" s="116"/>
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
@@ -5557,32 +5535,32 @@
       <c r="AU36"/>
     </row>
     <row r="37" spans="1:47">
-      <c r="A37" s="117"/>
-      <c r="B37" s="154" t="s">
+      <c r="A37" s="116"/>
+      <c r="B37" s="150" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="155" t="e">
+      <c r="C37" s="151" t="e">
         <f>ROUND((MAX(C26:C27)+C35)*C36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="D37" s="159" t="e">
+      <c r="D37" s="155" t="e">
         <f>ROUND((MAX(D26:D27)+D35)*D36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="E37" s="157"/>
-      <c r="F37" s="158"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="117"/>
-      <c r="J37" s="153"/>
-      <c r="K37" s="153"/>
-      <c r="L37" s="117"/>
-      <c r="M37" s="117"/>
-      <c r="N37" s="117"/>
-      <c r="O37" s="117"/>
-      <c r="P37" s="117"/>
-      <c r="Q37" s="117"/>
-      <c r="R37" s="117"/>
+      <c r="E37" s="153"/>
+      <c r="F37" s="154"/>
+      <c r="G37" s="116"/>
+      <c r="H37" s="116"/>
+      <c r="I37" s="116"/>
+      <c r="J37" s="149"/>
+      <c r="K37" s="149"/>
+      <c r="L37" s="116"/>
+      <c r="M37" s="116"/>
+      <c r="N37" s="116"/>
+      <c r="O37" s="116"/>
+      <c r="P37" s="116"/>
+      <c r="Q37" s="116"/>
+      <c r="R37" s="116"/>
       <c r="S37"/>
       <c r="T37"/>
       <c r="U37"/>
@@ -5806,19 +5784,19 @@
       </c>
     </row>
     <row r="45" spans="1:47">
-      <c r="B45" s="207" t="s">
+      <c r="B45" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="207"/>
-      <c r="D45" s="207"/>
-      <c r="E45" s="207"/>
-      <c r="F45" s="207"/>
-      <c r="G45" s="207"/>
-      <c r="H45" s="207"/>
-      <c r="I45" s="207"/>
-      <c r="J45" s="207"/>
-      <c r="K45" s="207"/>
-      <c r="L45" s="207"/>
+      <c r="C45" s="203"/>
+      <c r="D45" s="203"/>
+      <c r="E45" s="203"/>
+      <c r="F45" s="203"/>
+      <c r="G45" s="203"/>
+      <c r="H45" s="203"/>
+      <c r="I45" s="203"/>
+      <c r="J45" s="203"/>
+      <c r="K45" s="203"/>
+      <c r="L45" s="203"/>
     </row>
     <row r="47" spans="1:47">
       <c r="C47" s="21">

--- a/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
+++ b/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F376B55-DF9E-4577-BD4B-CC639B410F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D8E55D-9F98-45EF-93B3-BD939DB7A886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1543,7 +1552,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1804,7 +1813,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1904,20 +1912,65 @@
     <xf numFmtId="165" fontId="0" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1950,9 +2003,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1964,71 +2014,14 @@
     <xf numFmtId="0" fontId="40" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="45" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="26" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2050,6 +2043,40 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -3199,64 +3226,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:S118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="4" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="10.85546875" style="1"/>
+    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.88671875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="30.44140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.44140625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:17">
-      <c r="C3" s="181" t="s">
+      <c r="C3" s="155" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="181"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="181"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="181"/>
-      <c r="G4" s="181"/>
-    </row>
-    <row r="5" spans="1:17" ht="26.25">
-      <c r="C5" s="182" t="s">
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="155"/>
+    </row>
+    <row r="5" spans="1:17" ht="25.8">
+      <c r="C5" s="156" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="156"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="D7" s="197" t="s">
+      <c r="D7" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="197"/>
-      <c r="F7" s="197"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="171"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="33" t="s">
@@ -3274,12 +3301,12 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="199">
+      <c r="I8" s="174">
         <f>+'2'!D5</f>
         <v>1</v>
       </c>
-      <c r="J8" s="199"/>
-      <c r="K8" s="199"/>
+      <c r="J8" s="174"/>
+      <c r="K8" s="174"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="33" t="s">
@@ -3289,21 +3316,21 @@
       <c r="D9" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="183">
+      <c r="E9" s="157">
         <f ca="1">+TODAY()</f>
-        <v>46122</v>
-      </c>
-      <c r="F9" s="184"/>
+        <v>46253</v>
+      </c>
+      <c r="F9" s="158"/>
       <c r="G9" s="31"/>
       <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="161">
+      <c r="I9" s="175">
         <f>+'2'!D6</f>
         <v>23.2</v>
       </c>
-      <c r="J9" s="161"/>
-      <c r="K9" s="161"/>
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="33" t="s">
@@ -3344,21 +3371,21 @@
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="198">
+      <c r="I11" s="172">
         <f>+'2'!D8</f>
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J11" s="198"/>
-      <c r="K11" s="198"/>
+      <c r="J11" s="172"/>
+      <c r="K11" s="172"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="172" t="s">
+      <c r="A13" s="173" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="172"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="172"/>
-      <c r="E13" s="172"/>
+      <c r="B13" s="173"/>
+      <c r="C13" s="173"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="60"/>
@@ -3371,11 +3398,11 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="164" t="s">
+      <c r="A14" s="178" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="164"/>
-      <c r="C14" s="164"/>
+      <c r="B14" s="178"/>
+      <c r="C14" s="178"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -3389,36 +3416,36 @@
       </c>
     </row>
     <row r="15" spans="1:17" customFormat="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="117">
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="116">
         <v>0</v>
       </c>
-      <c r="K15" s="118" t="s">
+      <c r="K15" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="115"/>
+      <c r="P15" s="115"/>
+      <c r="Q15" s="115"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="163" t="s">
+      <c r="A16" s="177" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="163"/>
-      <c r="C16" s="163"/>
+      <c r="B16" s="177"/>
+      <c r="C16" s="177"/>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
       <c r="F16" s="38"/>
@@ -3440,7 +3467,7 @@
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="113"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
@@ -3466,13 +3493,13 @@
       <c r="K18" s="31"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="172" t="s">
+      <c r="A19" s="173" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="172"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="172"/>
-      <c r="E19" s="172"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
       <c r="H19" s="58"/>
@@ -3510,31 +3537,31 @@
       </c>
     </row>
     <row r="21" spans="1:17" customFormat="1">
-      <c r="A21" s="115" t="s">
+      <c r="A21" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="115"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="119">
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="118">
         <v>0</v>
       </c>
-      <c r="J21" s="117">
+      <c r="J21" s="116">
         <v>0</v>
       </c>
-      <c r="K21" s="118" t="s">
+      <c r="K21" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="L21" s="116"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="120"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="116"/>
-      <c r="Q21" s="116"/>
+      <c r="L21" s="115"/>
+      <c r="M21" s="115"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="115"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="31" t="s">
@@ -3678,235 +3705,235 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="174" t="s">
+      <c r="A30" s="187" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="175"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="121"/>
-      <c r="G30" s="122"/>
-      <c r="H30" s="122"/>
-      <c r="I30" s="123" t="s">
+      <c r="B30" s="188"/>
+      <c r="C30" s="188"/>
+      <c r="D30" s="188"/>
+      <c r="E30" s="188"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="121"/>
+      <c r="H30" s="121"/>
+      <c r="I30" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="123" t="s">
+      <c r="J30" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="123" t="s">
+      <c r="K30" s="122" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:17" customFormat="1">
-      <c r="A31" s="115" t="s">
+      <c r="A31" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="B31" s="124"/>
-      <c r="C31" s="124"/>
-      <c r="D31" s="124"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="124"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="124"/>
-      <c r="I31" s="118" t="s">
+      <c r="B31" s="123"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="123"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="123"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="123"/>
+      <c r="I31" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="J31" s="117">
+      <c r="J31" s="116">
         <v>0</v>
       </c>
-      <c r="K31" s="118" t="s">
+      <c r="K31" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="L31" s="116"/>
-      <c r="M31" s="116"/>
-      <c r="N31" s="116"/>
-      <c r="O31" s="116"/>
-      <c r="P31" s="116"/>
-      <c r="Q31" s="116"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="115"/>
+      <c r="N31" s="115"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="115"/>
+      <c r="Q31" s="115"/>
     </row>
     <row r="32" spans="1:17" customFormat="1">
-      <c r="A32" s="124" t="s">
+      <c r="A32" s="123" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="124"/>
-      <c r="C32" s="124"/>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="124"/>
-      <c r="H32" s="124"/>
-      <c r="I32" s="118" t="s">
+      <c r="B32" s="123"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="123"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="123"/>
+      <c r="H32" s="123"/>
+      <c r="I32" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="J32" s="117">
+      <c r="J32" s="116">
         <v>0</v>
       </c>
-      <c r="K32" s="118" t="s">
+      <c r="K32" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="L32" s="116"/>
-      <c r="M32" s="116"/>
-      <c r="N32" s="116"/>
-      <c r="O32" s="116"/>
-      <c r="P32" s="116"/>
-      <c r="Q32" s="116"/>
+      <c r="L32" s="115"/>
+      <c r="M32" s="115"/>
+      <c r="N32" s="115"/>
+      <c r="O32" s="115"/>
+      <c r="P32" s="115"/>
+      <c r="Q32" s="115"/>
     </row>
     <row r="33" spans="1:19" customFormat="1">
-      <c r="A33" s="127" t="s">
+      <c r="A33" s="126" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="128" t="s">
+      <c r="B33" s="126"/>
+      <c r="C33" s="126"/>
+      <c r="D33" s="126"/>
+      <c r="E33" s="126"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="126"/>
+      <c r="H33" s="126"/>
+      <c r="I33" s="127" t="s">
         <v>132</v>
       </c>
-      <c r="J33" s="129">
+      <c r="J33" s="128">
         <v>0</v>
       </c>
-      <c r="K33" s="130" t="s">
+      <c r="K33" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="L33" s="116"/>
-      <c r="M33" s="116"/>
-      <c r="N33" s="116"/>
-      <c r="O33" s="116"/>
-      <c r="P33" s="116"/>
-      <c r="Q33" s="116"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="115"/>
+      <c r="N33" s="115"/>
+      <c r="O33" s="115"/>
+      <c r="P33" s="115"/>
+      <c r="Q33" s="115"/>
     </row>
     <row r="34" spans="1:19" customFormat="1">
-      <c r="A34" s="125" t="s">
+      <c r="A34" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="124"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="124"/>
-      <c r="I34" s="126"/>
-      <c r="J34" s="117">
+      <c r="B34" s="123"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="123"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="123"/>
+      <c r="I34" s="125"/>
+      <c r="J34" s="116">
         <f>SUM(J31:J33)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="118" t="s">
+      <c r="K34" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="L34" s="116"/>
-      <c r="M34" s="116"/>
-      <c r="N34" s="116"/>
-      <c r="O34" s="116"/>
-      <c r="P34" s="116"/>
-      <c r="Q34" s="116"/>
+      <c r="L34" s="115"/>
+      <c r="M34" s="115"/>
+      <c r="N34" s="115"/>
+      <c r="O34" s="115"/>
+      <c r="P34" s="115"/>
+      <c r="Q34" s="115"/>
     </row>
     <row r="36" spans="1:19" customFormat="1">
       <c r="A36" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="131"/>
-      <c r="C36" s="131"/>
-      <c r="D36" s="131"/>
-      <c r="E36" s="131"/>
-      <c r="F36" s="131"/>
-      <c r="G36" s="131"/>
-      <c r="H36" s="131"/>
-      <c r="I36" s="132"/>
-      <c r="J36" s="133">
+      <c r="B36" s="130"/>
+      <c r="C36" s="130"/>
+      <c r="D36" s="130"/>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="130"/>
+      <c r="H36" s="130"/>
+      <c r="I36" s="131"/>
+      <c r="J36" s="132">
         <v>0</v>
       </c>
-      <c r="K36" s="134" t="s">
+      <c r="K36" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="L36" s="116"/>
-      <c r="M36" s="116"/>
-      <c r="N36" s="116"/>
-      <c r="O36" s="116"/>
-      <c r="P36" s="116"/>
-      <c r="Q36" s="116"/>
+      <c r="L36" s="115"/>
+      <c r="M36" s="115"/>
+      <c r="N36" s="115"/>
+      <c r="O36" s="115"/>
+      <c r="P36" s="115"/>
+      <c r="Q36" s="115"/>
     </row>
     <row r="37" spans="1:19" customFormat="1">
-      <c r="A37" s="135" t="s">
+      <c r="A37" s="134" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="136"/>
-      <c r="C37" s="136"/>
-      <c r="D37" s="136"/>
-      <c r="E37" s="136"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="136"/>
-      <c r="H37" s="136"/>
-      <c r="I37" s="137"/>
-      <c r="J37" s="138">
+      <c r="B37" s="135"/>
+      <c r="C37" s="135"/>
+      <c r="D37" s="135"/>
+      <c r="E37" s="135"/>
+      <c r="F37" s="135"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="135"/>
+      <c r="I37" s="136"/>
+      <c r="J37" s="137">
         <v>0</v>
       </c>
-      <c r="K37" s="139" t="s">
+      <c r="K37" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="L37" s="116"/>
-      <c r="M37" s="116"/>
-      <c r="N37" s="116"/>
-      <c r="O37" s="116"/>
-      <c r="P37" s="116"/>
-      <c r="Q37" s="116"/>
+      <c r="L37" s="115"/>
+      <c r="M37" s="115"/>
+      <c r="N37" s="115"/>
+      <c r="O37" s="115"/>
+      <c r="P37" s="115"/>
+      <c r="Q37" s="115"/>
     </row>
     <row r="38" spans="1:19" customFormat="1">
-      <c r="A38" s="176" t="s">
+      <c r="A38" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="177"/>
-      <c r="C38" s="177"/>
-      <c r="D38" s="177"/>
-      <c r="E38" s="177"/>
-      <c r="F38" s="177"/>
-      <c r="G38" s="177"/>
-      <c r="H38" s="177"/>
-      <c r="I38" s="142"/>
-      <c r="J38" s="143">
+      <c r="B38" s="190"/>
+      <c r="C38" s="190"/>
+      <c r="D38" s="190"/>
+      <c r="E38" s="190"/>
+      <c r="F38" s="190"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="141"/>
+      <c r="J38" s="142">
         <f>SUM(J34+J36)-J37</f>
         <v>0</v>
       </c>
-      <c r="K38" s="144" t="s">
+      <c r="K38" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="L38" s="116"/>
-      <c r="M38" s="116"/>
-      <c r="N38" s="116"/>
-      <c r="O38" s="116"/>
-      <c r="P38" s="116"/>
-      <c r="Q38" s="116"/>
+      <c r="L38" s="115"/>
+      <c r="M38" s="115"/>
+      <c r="N38" s="115"/>
+      <c r="O38" s="115"/>
+      <c r="P38" s="115"/>
+      <c r="Q38" s="115"/>
     </row>
     <row r="39" spans="1:19" customFormat="1">
-      <c r="B39" s="131"/>
-      <c r="C39" s="131"/>
-      <c r="D39" s="131"/>
-      <c r="E39" s="131"/>
-      <c r="F39" s="131"/>
-      <c r="G39" s="131"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="132"/>
-      <c r="J39" s="140"/>
-      <c r="K39" s="141"/>
-      <c r="L39" s="116"/>
-      <c r="M39" s="116"/>
-      <c r="N39" s="116"/>
-      <c r="O39" s="116"/>
-      <c r="P39" s="116"/>
-      <c r="Q39" s="116"/>
-    </row>
-    <row r="40" spans="1:19" ht="15.75">
-      <c r="A40" s="171" t="s">
+      <c r="B39" s="130"/>
+      <c r="C39" s="130"/>
+      <c r="D39" s="130"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="130"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="131"/>
+      <c r="J39" s="139"/>
+      <c r="K39" s="140"/>
+      <c r="L39" s="115"/>
+      <c r="M39" s="115"/>
+      <c r="N39" s="115"/>
+      <c r="O39" s="115"/>
+      <c r="P39" s="115"/>
+      <c r="Q39" s="115"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.6">
+      <c r="A40" s="185" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="171"/>
-      <c r="C40" s="171"/>
-      <c r="D40" s="171"/>
-      <c r="E40" s="171"/>
+      <c r="B40" s="185"/>
+      <c r="C40" s="185"/>
+      <c r="D40" s="185"/>
+      <c r="E40" s="185"/>
       <c r="F40" s="78"/>
       <c r="G40" s="78"/>
       <c r="H40" s="79"/>
@@ -3978,13 +4005,13 @@
       <c r="K43" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M43" s="187" t="s">
+      <c r="M43" s="161" t="s">
         <v>87</v>
       </c>
-      <c r="N43" s="187"/>
-      <c r="O43" s="187"/>
-      <c r="P43" s="187"/>
-      <c r="Q43" s="187"/>
+      <c r="N43" s="161"/>
+      <c r="O43" s="161"/>
+      <c r="P43" s="161"/>
+      <c r="Q43" s="161"/>
     </row>
     <row r="44" spans="1:19" ht="20.25" customHeight="1">
       <c r="A44" s="33"/>
@@ -3998,39 +4025,39 @@
       <c r="I44" s="37"/>
       <c r="J44" s="37"/>
       <c r="K44" s="34"/>
-      <c r="M44" s="188"/>
-      <c r="N44" s="188"/>
-      <c r="O44" s="188"/>
-      <c r="P44" s="188"/>
-      <c r="Q44" s="188"/>
+      <c r="M44" s="162"/>
+      <c r="N44" s="162"/>
+      <c r="O44" s="162"/>
+      <c r="P44" s="162"/>
+      <c r="Q44" s="162"/>
     </row>
     <row r="45" spans="1:19" ht="15" customHeight="1">
-      <c r="A45" s="167" t="s">
+      <c r="A45" s="181" t="s">
         <v>73</v>
       </c>
-      <c r="B45" s="168"/>
-      <c r="C45" s="168"/>
-      <c r="D45" s="168"/>
-      <c r="E45" s="168"/>
-      <c r="F45" s="168"/>
-      <c r="G45" s="168"/>
-      <c r="H45" s="168"/>
-      <c r="I45" s="168"/>
-      <c r="J45" s="168"/>
-      <c r="K45" s="169"/>
-      <c r="M45" s="195" t="s">
+      <c r="B45" s="182"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="182"/>
+      <c r="F45" s="182"/>
+      <c r="G45" s="182"/>
+      <c r="H45" s="182"/>
+      <c r="I45" s="182"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="183"/>
+      <c r="M45" s="169" t="s">
         <v>46</v>
       </c>
-      <c r="N45" s="193" t="s">
+      <c r="N45" s="167" t="s">
         <v>60</v>
       </c>
-      <c r="O45" s="189" t="s">
+      <c r="O45" s="163" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="191" t="s">
+      <c r="P45" s="165" t="s">
         <v>84</v>
       </c>
-      <c r="Q45" s="185" t="s">
+      <c r="Q45" s="159" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4038,35 +4065,35 @@
       <c r="A46" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="165" t="s">
+      <c r="B46" s="179" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="170"/>
-      <c r="D46" s="166"/>
+      <c r="C46" s="184"/>
+      <c r="D46" s="180"/>
       <c r="E46" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="165" t="s">
+      <c r="F46" s="179" t="s">
         <v>61</v>
       </c>
-      <c r="G46" s="166"/>
+      <c r="G46" s="180"/>
       <c r="H46" s="5" t="s">
         <v>58</v>
       </c>
       <c r="I46" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="173" t="s">
+      <c r="J46" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="K46" s="173"/>
-      <c r="M46" s="196"/>
-      <c r="N46" s="194"/>
-      <c r="O46" s="190"/>
-      <c r="P46" s="192"/>
-      <c r="Q46" s="186"/>
-    </row>
-    <row r="47" spans="1:19" s="106" customFormat="1" ht="15.75">
+      <c r="K46" s="186"/>
+      <c r="M46" s="170"/>
+      <c r="N46" s="168"/>
+      <c r="O46" s="164"/>
+      <c r="P46" s="166"/>
+      <c r="Q46" s="160"/>
+    </row>
+    <row r="47" spans="1:19" s="106" customFormat="1" ht="15.6">
       <c r="A47" s="103" t="s">
         <v>8</v>
       </c>
@@ -4098,15 +4125,15 @@
       <c r="I48" s="83"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
-      <c r="M48" s="157" t="s">
+      <c r="M48" s="192" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="157"/>
-      <c r="O48" s="157"/>
-      <c r="P48" s="157"/>
-      <c r="Q48" s="157"/>
-      <c r="R48" s="157"/>
-      <c r="S48" s="157"/>
+      <c r="N48" s="192"/>
+      <c r="O48" s="192"/>
+      <c r="P48" s="192"/>
+      <c r="Q48" s="192"/>
+      <c r="R48" s="192"/>
+      <c r="S48" s="192"/>
     </row>
     <row r="49" spans="1:19" ht="18.75" customHeight="1">
       <c r="A49" s="81" t="s">
@@ -4121,15 +4148,15 @@
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
       <c r="J49" s="31"/>
-      <c r="M49" s="157"/>
-      <c r="N49" s="157"/>
-      <c r="O49" s="157"/>
-      <c r="P49" s="157"/>
-      <c r="Q49" s="157"/>
-      <c r="R49" s="157"/>
-      <c r="S49" s="157"/>
-    </row>
-    <row r="50" spans="1:19" ht="18.75">
+      <c r="M49" s="192"/>
+      <c r="N49" s="192"/>
+      <c r="O49" s="192"/>
+      <c r="P49" s="192"/>
+      <c r="Q49" s="192"/>
+      <c r="R49" s="192"/>
+      <c r="S49" s="192"/>
+    </row>
+    <row r="50" spans="1:19" ht="18">
       <c r="A50" s="82" t="s">
         <v>65</v>
       </c>
@@ -4143,7 +4170,7 @@
       <c r="I50" s="31"/>
       <c r="J50" s="31"/>
     </row>
-    <row r="51" spans="1:19" ht="18.75">
+    <row r="51" spans="1:19" ht="18">
       <c r="A51" s="82" t="s">
         <v>66</v>
       </c>
@@ -4166,7 +4193,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="18.75">
+    <row r="52" spans="1:19" ht="18">
       <c r="A52" s="82" t="s">
         <v>76</v>
       </c>
@@ -4196,20 +4223,20 @@
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="31"/>
-      <c r="M53" s="158" t="s">
+      <c r="M53" s="203" t="s">
         <v>98</v>
       </c>
-      <c r="N53" s="31"/>
-      <c r="O53" s="156">
+      <c r="N53" s="204"/>
+      <c r="O53" s="191">
         <f>J14</f>
         <v>1220</v>
       </c>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="159" t="s">
+      <c r="P53" s="212" t="s">
         <v>99</v>
       </c>
-      <c r="R53" s="159"/>
-      <c r="S53" s="159"/>
+      <c r="Q53" s="210"/>
+      <c r="R53" s="210"/>
+      <c r="S53" s="210"/>
     </row>
     <row r="54" spans="1:19" ht="18.75" customHeight="1">
       <c r="A54" s="82" t="s">
@@ -4224,13 +4251,13 @@
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="31"/>
-      <c r="M54" s="158"/>
-      <c r="N54" s="112"/>
-      <c r="O54" s="156"/>
-      <c r="P54" s="31"/>
-      <c r="Q54" s="159"/>
-      <c r="R54" s="159"/>
-      <c r="S54" s="159"/>
+      <c r="M54" s="201"/>
+      <c r="N54" s="205"/>
+      <c r="O54" s="191"/>
+      <c r="P54" s="212"/>
+      <c r="Q54" s="210"/>
+      <c r="R54" s="210"/>
+      <c r="S54" s="210"/>
     </row>
     <row r="55" spans="1:19" ht="18.75" customHeight="1">
       <c r="A55" s="82" t="s">
@@ -4246,13 +4273,13 @@
       <c r="I55" s="31"/>
       <c r="J55" s="31"/>
       <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
+      <c r="O55" s="202"/>
       <c r="P55" s="31"/>
-      <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
-    </row>
-    <row r="56" spans="1:19" ht="18.75">
+      <c r="Q55" s="211"/>
+      <c r="R55" s="211"/>
+      <c r="S55" s="211"/>
+    </row>
+    <row r="56" spans="1:19" ht="18" customHeight="1">
       <c r="A56" s="82" t="s">
         <v>79</v>
       </c>
@@ -4265,22 +4292,22 @@
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="31"/>
-      <c r="M56" s="158" t="s">
+      <c r="M56" s="203" t="s">
         <v>100</v>
       </c>
-      <c r="N56" s="31"/>
-      <c r="O56" s="156">
+      <c r="N56" s="204"/>
+      <c r="O56" s="191">
         <f>J41</f>
         <v>0</v>
       </c>
-      <c r="P56" s="31"/>
-      <c r="Q56" s="159" t="s">
+      <c r="P56" s="212" t="s">
         <v>101</v>
       </c>
-      <c r="R56" s="159"/>
-      <c r="S56" s="159"/>
-    </row>
-    <row r="57" spans="1:19" ht="18.75">
+      <c r="Q56" s="210"/>
+      <c r="R56" s="210"/>
+      <c r="S56" s="210"/>
+    </row>
+    <row r="57" spans="1:19" ht="18">
       <c r="A57" s="82" t="s">
         <v>75</v>
       </c>
@@ -4293,13 +4320,13 @@
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="31"/>
-      <c r="M57" s="158"/>
-      <c r="N57" s="112"/>
-      <c r="O57" s="160"/>
-      <c r="P57" s="31"/>
-      <c r="Q57" s="159"/>
-      <c r="R57" s="159"/>
-      <c r="S57" s="159"/>
+      <c r="M57" s="201"/>
+      <c r="N57" s="205"/>
+      <c r="O57" s="193"/>
+      <c r="P57" s="212"/>
+      <c r="Q57" s="210"/>
+      <c r="R57" s="210"/>
+      <c r="S57" s="210"/>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" s="31"/>
@@ -4313,38 +4340,42 @@
       <c r="I58" s="31"/>
       <c r="J58" s="31"/>
       <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
+      <c r="O58" s="202"/>
       <c r="P58" s="31"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-    </row>
-    <row r="59" spans="1:19">
-      <c r="M59" s="178" t="s">
+      <c r="Q58" s="211"/>
+      <c r="R58" s="211"/>
+      <c r="S58" s="211"/>
+    </row>
+    <row r="59" spans="1:19" ht="14.4" customHeight="1">
+      <c r="M59" s="206" t="s">
         <v>102</v>
       </c>
-      <c r="O59" s="179" t="e">
+      <c r="N59" s="207"/>
+      <c r="O59" s="191" t="e">
         <f>J42</f>
         <v>#REF!</v>
       </c>
-      <c r="Q59" s="159" t="s">
+      <c r="P59" s="212" t="s">
         <v>103</v>
       </c>
-      <c r="R59" s="159"/>
-      <c r="S59" s="159"/>
-    </row>
-    <row r="60" spans="1:19" ht="18.75">
+      <c r="Q59" s="210"/>
+      <c r="R59" s="210"/>
+      <c r="S59" s="210"/>
+    </row>
+    <row r="60" spans="1:19" ht="18">
       <c r="H60" s="32"/>
       <c r="I60" s="32"/>
       <c r="J60" s="32"/>
       <c r="K60" s="31"/>
-      <c r="M60" s="178"/>
-      <c r="O60" s="180"/>
-      <c r="Q60" s="159"/>
-      <c r="R60" s="159"/>
-      <c r="S60" s="159"/>
-    </row>
-    <row r="61" spans="1:19" ht="18.75">
+      <c r="M60" s="208"/>
+      <c r="N60" s="209"/>
+      <c r="O60" s="191"/>
+      <c r="P60" s="212"/>
+      <c r="Q60" s="210"/>
+      <c r="R60" s="210"/>
+      <c r="S60" s="210"/>
+    </row>
+    <row r="61" spans="1:19" ht="18">
       <c r="H61" s="32"/>
       <c r="I61" s="32"/>
       <c r="J61" s="32"/>
@@ -4356,19 +4387,19 @@
       <c r="J63" s="40"/>
     </row>
     <row r="65" spans="1:11" ht="21">
-      <c r="A65" s="162" t="s">
+      <c r="A65" s="176" t="s">
         <v>45</v>
       </c>
-      <c r="B65" s="162"/>
-      <c r="C65" s="162"/>
-      <c r="D65" s="162"/>
-      <c r="E65" s="162"/>
-      <c r="F65" s="162"/>
-      <c r="G65" s="162"/>
-      <c r="H65" s="162"/>
-      <c r="I65" s="162"/>
-      <c r="J65" s="162"/>
-      <c r="K65" s="162"/>
+      <c r="B65" s="176"/>
+      <c r="C65" s="176"/>
+      <c r="D65" s="176"/>
+      <c r="E65" s="176"/>
+      <c r="F65" s="176"/>
+      <c r="G65" s="176"/>
+      <c r="H65" s="176"/>
+      <c r="I65" s="176"/>
+      <c r="J65" s="176"/>
+      <c r="K65" s="176"/>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
@@ -4674,10 +4705,10 @@
     <row r="109" spans="1:4">
       <c r="B109" s="41"/>
     </row>
-    <row r="110" spans="1:4" ht="15.75">
+    <row r="110" spans="1:4" ht="15.6">
       <c r="B110" s="42"/>
     </row>
-    <row r="111" spans="1:4" ht="15.75">
+    <row r="111" spans="1:4" ht="15.6">
       <c r="B111" s="42"/>
     </row>
     <row r="113" spans="2:10">
@@ -4698,15 +4729,34 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
     </row>
-    <row r="118" spans="2:10" ht="15.75">
+    <row r="118" spans="2:10" ht="15.6">
       <c r="B118" s="44"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="35">
-    <mergeCell ref="M59:M60"/>
+    <mergeCell ref="M59:N60"/>
+    <mergeCell ref="P53:S54"/>
+    <mergeCell ref="P56:S57"/>
+    <mergeCell ref="P59:S60"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="M48:S49"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="M53:N54"/>
+    <mergeCell ref="M56:N57"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="O59:O60"/>
-    <mergeCell ref="Q59:S60"/>
     <mergeCell ref="C3:G4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="E9:F9"/>
@@ -4720,25 +4770,6 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="M48:S49"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="Q53:S54"/>
-    <mergeCell ref="M56:M57"/>
-    <mergeCell ref="O56:O57"/>
-    <mergeCell ref="Q56:S57"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="COMPROBAR CANTIDAD DE CAJAS" error="Se debe ingresar la cantidad de cajas" sqref="I11" xr:uid="{3C2F8455-5D0D-41B0-BE98-F91BBC4383D3}">
@@ -4765,36 +4796,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AV57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="2"/>
-    <col min="6" max="6" width="11.28515625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="2"/>
-    <col min="9" max="9" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="2"/>
+    <col min="6" max="6" width="11.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" style="2"/>
+    <col min="9" max="9" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="47" width="11.42578125" style="1"/>
+    <col min="12" max="12" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="47" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:47" ht="15.75" thickBot="1">
-      <c r="B1" s="200" t="s">
+    <row r="1" spans="2:47" ht="15" thickBot="1">
+      <c r="B1" s="194" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="202"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="196"/>
     </row>
     <row r="2" spans="2:47" s="1" customFormat="1" ht="35.1" customHeight="1">
       <c r="B2" s="43"/>
@@ -5182,13 +5213,13 @@
       <c r="AU20"/>
     </row>
     <row r="21" spans="2:48" ht="15" customHeight="1">
-      <c r="B21" s="145" t="s">
+      <c r="B21" s="144" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="146">
+      <c r="C21" s="145">
         <v>0</v>
       </c>
-      <c r="D21" s="146">
+      <c r="D21" s="145">
         <v>0</v>
       </c>
       <c r="E21" s="30"/>
@@ -5222,7 +5253,7 @@
         <v>#REF!</v>
       </c>
       <c r="E22" s="77"/>
-      <c r="F22" s="204"/>
+      <c r="F22" s="198"/>
       <c r="G22" s="48"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5256,7 +5287,7 @@
         <v>#REF!</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="204"/>
+      <c r="F23" s="198"/>
       <c r="G23" s="48"/>
       <c r="H23" s="1"/>
       <c r="I23" s="76"/>
@@ -5391,19 +5422,19 @@
       <c r="G28" s="48"/>
     </row>
     <row r="29" spans="2:48">
-      <c r="B29" s="206" t="s">
+      <c r="B29" s="200" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="206"/>
-      <c r="D29" s="206"/>
-      <c r="E29" s="206"/>
-      <c r="F29" s="206"/>
-      <c r="G29" s="206"/>
-      <c r="H29" s="206"/>
-      <c r="I29" s="206"/>
-      <c r="J29" s="206"/>
-      <c r="K29" s="206"/>
-      <c r="L29" s="206"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="200"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="200"/>
+      <c r="I29" s="200"/>
+      <c r="J29" s="200"/>
+      <c r="K29" s="200"/>
+      <c r="L29" s="200"/>
     </row>
     <row r="31" spans="2:48">
       <c r="C31" s="50"/>
@@ -5438,8 +5469,8 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="205"/>
-      <c r="I34" s="205"/>
+      <c r="H34" s="199"/>
+      <c r="I34" s="199"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -5467,8 +5498,8 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="205"/>
-      <c r="I35" s="205"/>
+      <c r="H35" s="199"/>
+      <c r="I35" s="199"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -5482,28 +5513,28 @@
       <c r="AU35"/>
     </row>
     <row r="36" spans="1:47">
-      <c r="A36" s="116"/>
-      <c r="B36" s="147"/>
-      <c r="C36" s="148">
+      <c r="A36" s="115"/>
+      <c r="B36" s="146"/>
+      <c r="C36" s="147">
         <v>0</v>
       </c>
-      <c r="D36" s="148">
+      <c r="D36" s="147">
         <v>0</v>
       </c>
-      <c r="E36" s="152"/>
-      <c r="F36" s="152"/>
-      <c r="G36" s="116"/>
-      <c r="H36" s="116"/>
-      <c r="I36" s="116"/>
-      <c r="J36" s="149"/>
-      <c r="K36" s="149"/>
-      <c r="L36" s="116"/>
-      <c r="M36" s="116"/>
-      <c r="N36" s="116"/>
-      <c r="O36" s="116"/>
-      <c r="P36" s="116"/>
-      <c r="Q36" s="116"/>
-      <c r="R36" s="116"/>
+      <c r="E36" s="151"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="115"/>
+      <c r="H36" s="115"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="148"/>
+      <c r="K36" s="148"/>
+      <c r="L36" s="115"/>
+      <c r="M36" s="115"/>
+      <c r="N36" s="115"/>
+      <c r="O36" s="115"/>
+      <c r="P36" s="115"/>
+      <c r="Q36" s="115"/>
+      <c r="R36" s="115"/>
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
@@ -5535,32 +5566,32 @@
       <c r="AU36"/>
     </row>
     <row r="37" spans="1:47">
-      <c r="A37" s="116"/>
-      <c r="B37" s="150" t="s">
+      <c r="A37" s="115"/>
+      <c r="B37" s="149" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="151" t="e">
+      <c r="C37" s="150" t="e">
         <f>ROUND((MAX(C26:C27)+C35)*C36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="D37" s="155" t="e">
+      <c r="D37" s="154" t="e">
         <f>ROUND((MAX(D26:D27)+D35)*D36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="E37" s="153"/>
-      <c r="F37" s="154"/>
-      <c r="G37" s="116"/>
-      <c r="H37" s="116"/>
-      <c r="I37" s="116"/>
-      <c r="J37" s="149"/>
-      <c r="K37" s="149"/>
-      <c r="L37" s="116"/>
-      <c r="M37" s="116"/>
-      <c r="N37" s="116"/>
-      <c r="O37" s="116"/>
-      <c r="P37" s="116"/>
-      <c r="Q37" s="116"/>
-      <c r="R37" s="116"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="153"/>
+      <c r="G37" s="115"/>
+      <c r="H37" s="115"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="148"/>
+      <c r="K37" s="148"/>
+      <c r="L37" s="115"/>
+      <c r="M37" s="115"/>
+      <c r="N37" s="115"/>
+      <c r="O37" s="115"/>
+      <c r="P37" s="115"/>
+      <c r="Q37" s="115"/>
+      <c r="R37" s="115"/>
       <c r="S37"/>
       <c r="T37"/>
       <c r="U37"/>
@@ -5784,19 +5815,19 @@
       </c>
     </row>
     <row r="45" spans="1:47">
-      <c r="B45" s="203" t="s">
+      <c r="B45" s="197" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="203"/>
-      <c r="D45" s="203"/>
-      <c r="E45" s="203"/>
-      <c r="F45" s="203"/>
-      <c r="G45" s="203"/>
-      <c r="H45" s="203"/>
-      <c r="I45" s="203"/>
-      <c r="J45" s="203"/>
-      <c r="K45" s="203"/>
-      <c r="L45" s="203"/>
+      <c r="C45" s="197"/>
+      <c r="D45" s="197"/>
+      <c r="E45" s="197"/>
+      <c r="F45" s="197"/>
+      <c r="G45" s="197"/>
+      <c r="H45" s="197"/>
+      <c r="I45" s="197"/>
+      <c r="J45" s="197"/>
+      <c r="K45" s="197"/>
+      <c r="L45" s="197"/>
     </row>
     <row r="47" spans="1:47">
       <c r="C47" s="21">

--- a/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
+++ b/public/assets/templates/PLANTILLA_COTIZACION_INICIAL_CALCULADORA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ea0715c3b27ff88/Desktop/Proyectos/Probusiness/probusiness_intranetv2_back/public/assets/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D8E55D-9F98-45EF-93B3-BD939DB7A886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{51D8E55D-9F98-45EF-93B3-BD939DB7A886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E444773E-73D6-416B-94E7-5A48D954D6B3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -23,15 +23,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -958,16 +949,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1045,6 +1026,15 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1809,48 +1799,62 @@
     <xf numFmtId="2" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="39" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="38" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="39" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="42" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="43" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="43" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1859,59 +1863,129 @@
     <xf numFmtId="0" fontId="43" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="13" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="44" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="44" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="43" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="42" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="46" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="45" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="13" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="45" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="45" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1966,62 +2040,8 @@
     <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2044,39 +2064,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -3226,64 +3218,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:S118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="4" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.88671875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.44140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="30.44140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.44140625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="10.88671875" style="1"/>
+    <col min="8" max="8" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="30.42578125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:17" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:17">
-      <c r="C3" s="155" t="s">
+      <c r="C3" s="185" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="155"/>
-    </row>
-    <row r="5" spans="1:17" ht="25.8">
-      <c r="C5" s="156" t="s">
+      <c r="C4" s="185"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
+    </row>
+    <row r="5" spans="1:17" ht="26.25">
+      <c r="C5" s="186" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="156"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="D7" s="171" t="s">
+      <c r="D7" s="201" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="171"/>
-      <c r="F7" s="171"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="33" t="s">
@@ -3301,12 +3293,12 @@
       <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="174">
+      <c r="I8" s="203">
         <f>+'2'!D5</f>
         <v>1</v>
       </c>
-      <c r="J8" s="174"/>
-      <c r="K8" s="174"/>
+      <c r="J8" s="203"/>
+      <c r="K8" s="203"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="33" t="s">
@@ -3316,21 +3308,21 @@
       <c r="D9" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="157">
+      <c r="E9" s="187">
         <f ca="1">+TODAY()</f>
-        <v>46253</v>
-      </c>
-      <c r="F9" s="158"/>
+        <v>46255</v>
+      </c>
+      <c r="F9" s="188"/>
       <c r="G9" s="31"/>
       <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="175">
+      <c r="I9" s="168">
         <f>+'2'!D6</f>
         <v>23.2</v>
       </c>
-      <c r="J9" s="175"/>
-      <c r="K9" s="175"/>
+      <c r="J9" s="168"/>
+      <c r="K9" s="168"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="33" t="s">
@@ -3371,21 +3363,21 @@
       <c r="H11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="172">
+      <c r="I11" s="202">
         <f>+'2'!D8</f>
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J11" s="172"/>
-      <c r="K11" s="172"/>
+      <c r="J11" s="202"/>
+      <c r="K11" s="202"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="173" t="s">
+      <c r="A13" s="179" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="173"/>
-      <c r="C13" s="173"/>
-      <c r="D13" s="173"/>
-      <c r="E13" s="173"/>
+      <c r="B13" s="179"/>
+      <c r="C13" s="179"/>
+      <c r="D13" s="179"/>
+      <c r="E13" s="179"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
       <c r="H13" s="60"/>
@@ -3398,11 +3390,11 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="178" t="s">
+      <c r="A14" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="178"/>
-      <c r="C14" s="178"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="171"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -3416,36 +3408,36 @@
       </c>
     </row>
     <row r="15" spans="1:17" customFormat="1">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="112" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="113"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="116">
+      <c r="B15" s="112"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="115">
         <v>0</v>
       </c>
-      <c r="K15" s="117" t="s">
+      <c r="K15" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="115"/>
-      <c r="M15" s="115"/>
-      <c r="N15" s="115"/>
-      <c r="O15" s="115"/>
-      <c r="P15" s="115"/>
-      <c r="Q15" s="115"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="177" t="s">
+      <c r="A16" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="177"/>
-      <c r="C16" s="177"/>
+      <c r="B16" s="170"/>
+      <c r="C16" s="170"/>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
       <c r="F16" s="38"/>
@@ -3467,7 +3459,7 @@
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="112"/>
+      <c r="F17" s="111"/>
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
@@ -3493,13 +3485,13 @@
       <c r="K18" s="31"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="173" t="s">
+      <c r="A19" s="179" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="173"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
+      <c r="B19" s="179"/>
+      <c r="C19" s="179"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="179"/>
       <c r="F19" s="58"/>
       <c r="G19" s="58"/>
       <c r="H19" s="58"/>
@@ -3537,31 +3529,31 @@
       </c>
     </row>
     <row r="21" spans="1:17" customFormat="1">
-      <c r="A21" s="114" t="s">
+      <c r="A21" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="118">
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="117">
         <v>0</v>
       </c>
-      <c r="J21" s="116">
+      <c r="J21" s="115">
         <v>0</v>
       </c>
-      <c r="K21" s="117" t="s">
+      <c r="K21" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="L21" s="115"/>
-      <c r="M21" s="115"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="115"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="114"/>
+      <c r="Q21" s="114"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="31" t="s">
@@ -3705,235 +3697,235 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="187" t="s">
+      <c r="A30" s="181" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="188"/>
-      <c r="C30" s="188"/>
-      <c r="D30" s="188"/>
-      <c r="E30" s="188"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="121"/>
-      <c r="H30" s="121"/>
-      <c r="I30" s="122" t="s">
+      <c r="B30" s="182"/>
+      <c r="C30" s="182"/>
+      <c r="D30" s="182"/>
+      <c r="E30" s="182"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="120"/>
+      <c r="I30" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="J30" s="122" t="s">
+      <c r="J30" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="122" t="s">
+      <c r="K30" s="121" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:17" customFormat="1">
-      <c r="A31" s="114" t="s">
+      <c r="A31" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="B31" s="123"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="123"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="123"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="123"/>
-      <c r="I31" s="117" t="s">
+      <c r="B31" s="122"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="122"/>
+      <c r="E31" s="122"/>
+      <c r="F31" s="122"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="122"/>
+      <c r="I31" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="J31" s="116">
+      <c r="J31" s="115">
         <v>0</v>
       </c>
-      <c r="K31" s="117" t="s">
+      <c r="K31" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="L31" s="115"/>
-      <c r="M31" s="115"/>
-      <c r="N31" s="115"/>
-      <c r="O31" s="115"/>
-      <c r="P31" s="115"/>
-      <c r="Q31" s="115"/>
+      <c r="L31" s="114"/>
+      <c r="M31" s="114"/>
+      <c r="N31" s="114"/>
+      <c r="O31" s="114"/>
+      <c r="P31" s="114"/>
+      <c r="Q31" s="114"/>
     </row>
     <row r="32" spans="1:17" customFormat="1">
-      <c r="A32" s="123" t="s">
+      <c r="A32" s="122" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="123"/>
-      <c r="C32" s="123"/>
-      <c r="D32" s="123"/>
-      <c r="E32" s="123"/>
-      <c r="F32" s="123"/>
-      <c r="G32" s="123"/>
-      <c r="H32" s="123"/>
-      <c r="I32" s="117" t="s">
+      <c r="B32" s="122"/>
+      <c r="C32" s="122"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="122"/>
+      <c r="I32" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="J32" s="116">
+      <c r="J32" s="115">
         <v>0</v>
       </c>
-      <c r="K32" s="117" t="s">
+      <c r="K32" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="L32" s="115"/>
-      <c r="M32" s="115"/>
-      <c r="N32" s="115"/>
-      <c r="O32" s="115"/>
-      <c r="P32" s="115"/>
-      <c r="Q32" s="115"/>
+      <c r="L32" s="114"/>
+      <c r="M32" s="114"/>
+      <c r="N32" s="114"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="114"/>
+      <c r="Q32" s="114"/>
     </row>
     <row r="33" spans="1:19" customFormat="1">
-      <c r="A33" s="126" t="s">
+      <c r="A33" s="125" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="126"/>
-      <c r="C33" s="126"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="126"/>
-      <c r="F33" s="126"/>
-      <c r="G33" s="126"/>
-      <c r="H33" s="126"/>
-      <c r="I33" s="127" t="s">
+      <c r="B33" s="125"/>
+      <c r="C33" s="125"/>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="125"/>
+      <c r="G33" s="125"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="126" t="s">
         <v>132</v>
       </c>
-      <c r="J33" s="128">
+      <c r="J33" s="127">
         <v>0</v>
       </c>
-      <c r="K33" s="129" t="s">
+      <c r="K33" s="128" t="s">
         <v>35</v>
       </c>
-      <c r="L33" s="115"/>
-      <c r="M33" s="115"/>
-      <c r="N33" s="115"/>
-      <c r="O33" s="115"/>
-      <c r="P33" s="115"/>
-      <c r="Q33" s="115"/>
+      <c r="L33" s="114"/>
+      <c r="M33" s="114"/>
+      <c r="N33" s="114"/>
+      <c r="O33" s="114"/>
+      <c r="P33" s="114"/>
+      <c r="Q33" s="114"/>
     </row>
     <row r="34" spans="1:19" customFormat="1">
-      <c r="A34" s="124" t="s">
+      <c r="A34" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="123"/>
-      <c r="C34" s="123"/>
-      <c r="D34" s="123"/>
-      <c r="E34" s="123"/>
-      <c r="F34" s="123"/>
-      <c r="G34" s="123"/>
-      <c r="H34" s="123"/>
-      <c r="I34" s="125"/>
-      <c r="J34" s="116">
+      <c r="B34" s="122"/>
+      <c r="C34" s="122"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="122"/>
+      <c r="F34" s="122"/>
+      <c r="G34" s="122"/>
+      <c r="H34" s="122"/>
+      <c r="I34" s="124"/>
+      <c r="J34" s="115">
         <f>SUM(J31:J33)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="117" t="s">
+      <c r="K34" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="L34" s="115"/>
-      <c r="M34" s="115"/>
-      <c r="N34" s="115"/>
-      <c r="O34" s="115"/>
-      <c r="P34" s="115"/>
-      <c r="Q34" s="115"/>
+      <c r="L34" s="114"/>
+      <c r="M34" s="114"/>
+      <c r="N34" s="114"/>
+      <c r="O34" s="114"/>
+      <c r="P34" s="114"/>
+      <c r="Q34" s="114"/>
     </row>
     <row r="36" spans="1:19" customFormat="1">
       <c r="A36" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="130"/>
-      <c r="C36" s="130"/>
-      <c r="D36" s="130"/>
-      <c r="E36" s="130"/>
-      <c r="F36" s="130"/>
-      <c r="G36" s="130"/>
-      <c r="H36" s="130"/>
-      <c r="I36" s="131"/>
-      <c r="J36" s="132">
+      <c r="B36" s="129"/>
+      <c r="C36" s="129"/>
+      <c r="D36" s="129"/>
+      <c r="E36" s="129"/>
+      <c r="F36" s="129"/>
+      <c r="G36" s="129"/>
+      <c r="H36" s="129"/>
+      <c r="I36" s="130"/>
+      <c r="J36" s="131">
         <v>0</v>
       </c>
-      <c r="K36" s="133" t="s">
+      <c r="K36" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="L36" s="115"/>
-      <c r="M36" s="115"/>
-      <c r="N36" s="115"/>
-      <c r="O36" s="115"/>
-      <c r="P36" s="115"/>
-      <c r="Q36" s="115"/>
+      <c r="L36" s="114"/>
+      <c r="M36" s="114"/>
+      <c r="N36" s="114"/>
+      <c r="O36" s="114"/>
+      <c r="P36" s="114"/>
+      <c r="Q36" s="114"/>
     </row>
     <row r="37" spans="1:19" customFormat="1">
-      <c r="A37" s="134" t="s">
+      <c r="A37" s="133" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="135"/>
-      <c r="C37" s="135"/>
-      <c r="D37" s="135"/>
-      <c r="E37" s="135"/>
-      <c r="F37" s="135"/>
-      <c r="G37" s="135"/>
-      <c r="H37" s="135"/>
-      <c r="I37" s="136"/>
-      <c r="J37" s="137">
+      <c r="B37" s="134"/>
+      <c r="C37" s="134"/>
+      <c r="D37" s="134"/>
+      <c r="E37" s="134"/>
+      <c r="F37" s="134"/>
+      <c r="G37" s="134"/>
+      <c r="H37" s="134"/>
+      <c r="I37" s="135"/>
+      <c r="J37" s="136">
         <v>0</v>
       </c>
-      <c r="K37" s="138" t="s">
+      <c r="K37" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="L37" s="115"/>
-      <c r="M37" s="115"/>
-      <c r="N37" s="115"/>
-      <c r="O37" s="115"/>
-      <c r="P37" s="115"/>
-      <c r="Q37" s="115"/>
+      <c r="L37" s="114"/>
+      <c r="M37" s="114"/>
+      <c r="N37" s="114"/>
+      <c r="O37" s="114"/>
+      <c r="P37" s="114"/>
+      <c r="Q37" s="114"/>
     </row>
     <row r="38" spans="1:19" customFormat="1">
-      <c r="A38" s="189" t="s">
+      <c r="A38" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="190"/>
-      <c r="C38" s="190"/>
-      <c r="D38" s="190"/>
-      <c r="E38" s="190"/>
-      <c r="F38" s="190"/>
-      <c r="G38" s="190"/>
-      <c r="H38" s="190"/>
-      <c r="I38" s="141"/>
-      <c r="J38" s="142">
+      <c r="B38" s="184"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="184"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="140"/>
+      <c r="J38" s="141">
         <f>SUM(J34+J36)-J37</f>
         <v>0</v>
       </c>
-      <c r="K38" s="143" t="s">
+      <c r="K38" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="L38" s="115"/>
-      <c r="M38" s="115"/>
-      <c r="N38" s="115"/>
-      <c r="O38" s="115"/>
-      <c r="P38" s="115"/>
-      <c r="Q38" s="115"/>
+      <c r="L38" s="114"/>
+      <c r="M38" s="114"/>
+      <c r="N38" s="114"/>
+      <c r="O38" s="114"/>
+      <c r="P38" s="114"/>
+      <c r="Q38" s="114"/>
     </row>
     <row r="39" spans="1:19" customFormat="1">
-      <c r="B39" s="130"/>
-      <c r="C39" s="130"/>
-      <c r="D39" s="130"/>
-      <c r="E39" s="130"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="130"/>
-      <c r="H39" s="130"/>
-      <c r="I39" s="131"/>
-      <c r="J39" s="139"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="115"/>
-      <c r="M39" s="115"/>
-      <c r="N39" s="115"/>
-      <c r="O39" s="115"/>
-      <c r="P39" s="115"/>
-      <c r="Q39" s="115"/>
-    </row>
-    <row r="40" spans="1:19" ht="15.6">
-      <c r="A40" s="185" t="s">
+      <c r="B39" s="129"/>
+      <c r="C39" s="129"/>
+      <c r="D39" s="129"/>
+      <c r="E39" s="129"/>
+      <c r="F39" s="129"/>
+      <c r="G39" s="129"/>
+      <c r="H39" s="129"/>
+      <c r="I39" s="130"/>
+      <c r="J39" s="138"/>
+      <c r="K39" s="139"/>
+      <c r="L39" s="114"/>
+      <c r="M39" s="114"/>
+      <c r="N39" s="114"/>
+      <c r="O39" s="114"/>
+      <c r="P39" s="114"/>
+      <c r="Q39" s="114"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75">
+      <c r="A40" s="178" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="185"/>
-      <c r="C40" s="185"/>
-      <c r="D40" s="185"/>
-      <c r="E40" s="185"/>
+      <c r="B40" s="178"/>
+      <c r="C40" s="178"/>
+      <c r="D40" s="178"/>
+      <c r="E40" s="178"/>
       <c r="F40" s="78"/>
       <c r="G40" s="78"/>
       <c r="H40" s="79"/>
@@ -4005,13 +3997,13 @@
       <c r="K43" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="M43" s="161" t="s">
+      <c r="M43" s="191" t="s">
         <v>87</v>
       </c>
-      <c r="N43" s="161"/>
-      <c r="O43" s="161"/>
-      <c r="P43" s="161"/>
-      <c r="Q43" s="161"/>
+      <c r="N43" s="191"/>
+      <c r="O43" s="191"/>
+      <c r="P43" s="191"/>
+      <c r="Q43" s="191"/>
     </row>
     <row r="44" spans="1:19" ht="20.25" customHeight="1">
       <c r="A44" s="33"/>
@@ -4025,39 +4017,39 @@
       <c r="I44" s="37"/>
       <c r="J44" s="37"/>
       <c r="K44" s="34"/>
-      <c r="M44" s="162"/>
-      <c r="N44" s="162"/>
-      <c r="O44" s="162"/>
-      <c r="P44" s="162"/>
-      <c r="Q44" s="162"/>
+      <c r="M44" s="192"/>
+      <c r="N44" s="192"/>
+      <c r="O44" s="192"/>
+      <c r="P44" s="192"/>
+      <c r="Q44" s="192"/>
     </row>
     <row r="45" spans="1:19" ht="15" customHeight="1">
-      <c r="A45" s="181" t="s">
+      <c r="A45" s="174" t="s">
         <v>73</v>
       </c>
-      <c r="B45" s="182"/>
-      <c r="C45" s="182"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="182"/>
-      <c r="F45" s="182"/>
-      <c r="G45" s="182"/>
-      <c r="H45" s="182"/>
-      <c r="I45" s="182"/>
-      <c r="J45" s="182"/>
-      <c r="K45" s="183"/>
-      <c r="M45" s="169" t="s">
+      <c r="B45" s="175"/>
+      <c r="C45" s="175"/>
+      <c r="D45" s="175"/>
+      <c r="E45" s="175"/>
+      <c r="F45" s="175"/>
+      <c r="G45" s="175"/>
+      <c r="H45" s="175"/>
+      <c r="I45" s="175"/>
+      <c r="J45" s="175"/>
+      <c r="K45" s="176"/>
+      <c r="M45" s="199" t="s">
         <v>46</v>
       </c>
-      <c r="N45" s="167" t="s">
+      <c r="N45" s="197" t="s">
         <v>60</v>
       </c>
-      <c r="O45" s="163" t="s">
+      <c r="O45" s="193" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="165" t="s">
+      <c r="P45" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="Q45" s="159" t="s">
+      <c r="Q45" s="189" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4065,35 +4057,35 @@
       <c r="A46" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="179" t="s">
+      <c r="B46" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="184"/>
-      <c r="D46" s="180"/>
+      <c r="C46" s="177"/>
+      <c r="D46" s="173"/>
       <c r="E46" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="179" t="s">
+      <c r="F46" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="G46" s="180"/>
+      <c r="G46" s="173"/>
       <c r="H46" s="5" t="s">
         <v>58</v>
       </c>
       <c r="I46" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="186" t="s">
+      <c r="J46" s="180" t="s">
         <v>59</v>
       </c>
-      <c r="K46" s="186"/>
-      <c r="M46" s="170"/>
-      <c r="N46" s="168"/>
-      <c r="O46" s="164"/>
-      <c r="P46" s="166"/>
-      <c r="Q46" s="160"/>
-    </row>
-    <row r="47" spans="1:19" s="106" customFormat="1" ht="15.6">
+      <c r="K46" s="180"/>
+      <c r="M46" s="200"/>
+      <c r="N46" s="198"/>
+      <c r="O46" s="194"/>
+      <c r="P46" s="196"/>
+      <c r="Q46" s="190"/>
+    </row>
+    <row r="47" spans="1:19" s="106" customFormat="1" ht="15.75">
       <c r="A47" s="103" t="s">
         <v>8</v>
       </c>
@@ -4125,15 +4117,15 @@
       <c r="I48" s="83"/>
       <c r="J48" s="71"/>
       <c r="K48" s="72"/>
-      <c r="M48" s="192" t="s">
+      <c r="M48" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="N48" s="192"/>
-      <c r="O48" s="192"/>
-      <c r="P48" s="192"/>
-      <c r="Q48" s="192"/>
-      <c r="R48" s="192"/>
-      <c r="S48" s="192"/>
+      <c r="N48" s="162"/>
+      <c r="O48" s="162"/>
+      <c r="P48" s="162"/>
+      <c r="Q48" s="162"/>
+      <c r="R48" s="162"/>
+      <c r="S48" s="162"/>
     </row>
     <row r="49" spans="1:19" ht="18.75" customHeight="1">
       <c r="A49" s="81" t="s">
@@ -4148,15 +4140,15 @@
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
       <c r="J49" s="31"/>
-      <c r="M49" s="192"/>
-      <c r="N49" s="192"/>
-      <c r="O49" s="192"/>
-      <c r="P49" s="192"/>
-      <c r="Q49" s="192"/>
-      <c r="R49" s="192"/>
-      <c r="S49" s="192"/>
-    </row>
-    <row r="50" spans="1:19" ht="18">
+      <c r="M49" s="162"/>
+      <c r="N49" s="162"/>
+      <c r="O49" s="162"/>
+      <c r="P49" s="162"/>
+      <c r="Q49" s="162"/>
+      <c r="R49" s="162"/>
+      <c r="S49" s="162"/>
+    </row>
+    <row r="50" spans="1:19" ht="18.75">
       <c r="A50" s="82" t="s">
         <v>65</v>
       </c>
@@ -4170,7 +4162,7 @@
       <c r="I50" s="31"/>
       <c r="J50" s="31"/>
     </row>
-    <row r="51" spans="1:19" ht="18">
+    <row r="51" spans="1:19" ht="18.75">
       <c r="A51" s="82" t="s">
         <v>66</v>
       </c>
@@ -4183,17 +4175,21 @@
       <c r="H51" s="31"/>
       <c r="I51" s="31"/>
       <c r="J51" s="31"/>
-      <c r="M51" s="110" t="s">
+      <c r="M51" s="211" t="s">
         <v>96</v>
       </c>
-      <c r="O51" s="110" t="s">
+      <c r="N51" s="211"/>
+      <c r="O51" s="212" t="s">
         <v>34</v>
       </c>
-      <c r="R51" s="110" t="s">
+      <c r="P51" s="211" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" ht="18">
+      <c r="Q51" s="211"/>
+      <c r="R51" s="211"/>
+      <c r="S51" s="211"/>
+    </row>
+    <row r="52" spans="1:19" ht="18.75">
       <c r="A52" s="82" t="s">
         <v>76</v>
       </c>
@@ -4206,9 +4202,9 @@
       <c r="H52" s="31"/>
       <c r="I52" s="31"/>
       <c r="J52" s="31"/>
-      <c r="N52" s="111"/>
-      <c r="O52" s="111"/>
-      <c r="P52" s="111"/>
+      <c r="N52" s="110"/>
+      <c r="O52" s="110"/>
+      <c r="P52" s="110"/>
     </row>
     <row r="53" spans="1:19" ht="18.75" customHeight="1">
       <c r="A53" s="82" t="s">
@@ -4223,20 +4219,20 @@
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="31"/>
-      <c r="M53" s="203" t="s">
+      <c r="M53" s="164" t="s">
         <v>98</v>
       </c>
-      <c r="N53" s="204"/>
-      <c r="O53" s="191">
+      <c r="N53" s="165"/>
+      <c r="O53" s="161">
         <f>J14</f>
         <v>1220</v>
       </c>
-      <c r="P53" s="212" t="s">
+      <c r="P53" s="159" t="s">
         <v>99</v>
       </c>
-      <c r="Q53" s="210"/>
-      <c r="R53" s="210"/>
-      <c r="S53" s="210"/>
+      <c r="Q53" s="160"/>
+      <c r="R53" s="160"/>
+      <c r="S53" s="160"/>
     </row>
     <row r="54" spans="1:19" ht="18.75" customHeight="1">
       <c r="A54" s="82" t="s">
@@ -4251,13 +4247,13 @@
       <c r="H54" s="31"/>
       <c r="I54" s="31"/>
       <c r="J54" s="31"/>
-      <c r="M54" s="201"/>
-      <c r="N54" s="205"/>
-      <c r="O54" s="191"/>
-      <c r="P54" s="212"/>
-      <c r="Q54" s="210"/>
-      <c r="R54" s="210"/>
-      <c r="S54" s="210"/>
+      <c r="M54" s="166"/>
+      <c r="N54" s="167"/>
+      <c r="O54" s="161"/>
+      <c r="P54" s="159"/>
+      <c r="Q54" s="160"/>
+      <c r="R54" s="160"/>
+      <c r="S54" s="160"/>
     </row>
     <row r="55" spans="1:19" ht="18.75" customHeight="1">
       <c r="A55" s="82" t="s">
@@ -4273,11 +4269,11 @@
       <c r="I55" s="31"/>
       <c r="J55" s="31"/>
       <c r="N55" s="31"/>
-      <c r="O55" s="202"/>
+      <c r="O55" s="31"/>
       <c r="P55" s="31"/>
-      <c r="Q55" s="211"/>
-      <c r="R55" s="211"/>
-      <c r="S55" s="211"/>
+      <c r="Q55" s="154"/>
+      <c r="R55" s="154"/>
+      <c r="S55" s="154"/>
     </row>
     <row r="56" spans="1:19" ht="18" customHeight="1">
       <c r="A56" s="82" t="s">
@@ -4292,22 +4288,22 @@
       <c r="H56" s="31"/>
       <c r="I56" s="31"/>
       <c r="J56" s="31"/>
-      <c r="M56" s="203" t="s">
+      <c r="M56" s="164" t="s">
         <v>100</v>
       </c>
-      <c r="N56" s="204"/>
-      <c r="O56" s="191">
+      <c r="N56" s="165"/>
+      <c r="O56" s="161">
         <f>J41</f>
         <v>0</v>
       </c>
-      <c r="P56" s="212" t="s">
+      <c r="P56" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="Q56" s="210"/>
-      <c r="R56" s="210"/>
-      <c r="S56" s="210"/>
-    </row>
-    <row r="57" spans="1:19" ht="18">
+      <c r="Q56" s="160"/>
+      <c r="R56" s="160"/>
+      <c r="S56" s="160"/>
+    </row>
+    <row r="57" spans="1:19" ht="18.75">
       <c r="A57" s="82" t="s">
         <v>75</v>
       </c>
@@ -4320,13 +4316,13 @@
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
       <c r="J57" s="31"/>
-      <c r="M57" s="201"/>
-      <c r="N57" s="205"/>
-      <c r="O57" s="193"/>
-      <c r="P57" s="212"/>
-      <c r="Q57" s="210"/>
-      <c r="R57" s="210"/>
-      <c r="S57" s="210"/>
+      <c r="M57" s="166"/>
+      <c r="N57" s="167"/>
+      <c r="O57" s="163"/>
+      <c r="P57" s="159"/>
+      <c r="Q57" s="160"/>
+      <c r="R57" s="160"/>
+      <c r="S57" s="160"/>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" s="31"/>
@@ -4340,42 +4336,42 @@
       <c r="I58" s="31"/>
       <c r="J58" s="31"/>
       <c r="N58" s="31"/>
-      <c r="O58" s="202"/>
+      <c r="O58" s="31"/>
       <c r="P58" s="31"/>
-      <c r="Q58" s="211"/>
-      <c r="R58" s="211"/>
-      <c r="S58" s="211"/>
-    </row>
-    <row r="59" spans="1:19" ht="14.4" customHeight="1">
-      <c r="M59" s="206" t="s">
+      <c r="Q58" s="154"/>
+      <c r="R58" s="154"/>
+      <c r="S58" s="154"/>
+    </row>
+    <row r="59" spans="1:19" ht="14.45" customHeight="1">
+      <c r="M59" s="155" t="s">
         <v>102</v>
       </c>
-      <c r="N59" s="207"/>
-      <c r="O59" s="191" t="e">
+      <c r="N59" s="156"/>
+      <c r="O59" s="161" t="e">
         <f>J42</f>
         <v>#REF!</v>
       </c>
-      <c r="P59" s="212" t="s">
+      <c r="P59" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="Q59" s="210"/>
-      <c r="R59" s="210"/>
-      <c r="S59" s="210"/>
-    </row>
-    <row r="60" spans="1:19" ht="18">
+      <c r="Q59" s="160"/>
+      <c r="R59" s="160"/>
+      <c r="S59" s="160"/>
+    </row>
+    <row r="60" spans="1:19" ht="18.75">
       <c r="H60" s="32"/>
       <c r="I60" s="32"/>
       <c r="J60" s="32"/>
       <c r="K60" s="31"/>
-      <c r="M60" s="208"/>
-      <c r="N60" s="209"/>
-      <c r="O60" s="191"/>
-      <c r="P60" s="212"/>
-      <c r="Q60" s="210"/>
-      <c r="R60" s="210"/>
-      <c r="S60" s="210"/>
-    </row>
-    <row r="61" spans="1:19" ht="18">
+      <c r="M60" s="157"/>
+      <c r="N60" s="158"/>
+      <c r="O60" s="161"/>
+      <c r="P60" s="159"/>
+      <c r="Q60" s="160"/>
+      <c r="R60" s="160"/>
+      <c r="S60" s="160"/>
+    </row>
+    <row r="61" spans="1:19" ht="18.75">
       <c r="H61" s="32"/>
       <c r="I61" s="32"/>
       <c r="J61" s="32"/>
@@ -4387,19 +4383,19 @@
       <c r="J63" s="40"/>
     </row>
     <row r="65" spans="1:11" ht="21">
-      <c r="A65" s="176" t="s">
+      <c r="A65" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="B65" s="176"/>
-      <c r="C65" s="176"/>
-      <c r="D65" s="176"/>
-      <c r="E65" s="176"/>
-      <c r="F65" s="176"/>
-      <c r="G65" s="176"/>
-      <c r="H65" s="176"/>
-      <c r="I65" s="176"/>
-      <c r="J65" s="176"/>
-      <c r="K65" s="176"/>
+      <c r="B65" s="169"/>
+      <c r="C65" s="169"/>
+      <c r="D65" s="169"/>
+      <c r="E65" s="169"/>
+      <c r="F65" s="169"/>
+      <c r="G65" s="169"/>
+      <c r="H65" s="169"/>
+      <c r="I65" s="169"/>
+      <c r="J65" s="169"/>
+      <c r="K65" s="169"/>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
@@ -4705,10 +4701,10 @@
     <row r="109" spans="1:4">
       <c r="B109" s="41"/>
     </row>
-    <row r="110" spans="1:4" ht="15.6">
+    <row r="110" spans="1:4" ht="15.75">
       <c r="B110" s="42"/>
     </row>
-    <row r="111" spans="1:4" ht="15.6">
+    <row r="111" spans="1:4" ht="15.75">
       <c r="B111" s="42"/>
     </row>
     <row r="113" spans="2:10">
@@ -4729,34 +4725,12 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
     </row>
-    <row r="118" spans="2:10" ht="15.6">
+    <row r="118" spans="2:10" ht="15.75">
       <c r="B118" s="44"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="35">
-    <mergeCell ref="M59:N60"/>
-    <mergeCell ref="P53:S54"/>
-    <mergeCell ref="P56:S57"/>
-    <mergeCell ref="P59:S60"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="M48:S49"/>
-    <mergeCell ref="O56:O57"/>
-    <mergeCell ref="M53:N54"/>
-    <mergeCell ref="M56:N57"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="O59:O60"/>
+  <mergeCells count="37">
     <mergeCell ref="C3:G4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="E9:F9"/>
@@ -4770,6 +4744,30 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="M48:S49"/>
+    <mergeCell ref="O56:O57"/>
+    <mergeCell ref="M53:N54"/>
+    <mergeCell ref="M56:N57"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="P51:S51"/>
+    <mergeCell ref="M59:N60"/>
+    <mergeCell ref="P53:S54"/>
+    <mergeCell ref="P56:S57"/>
+    <mergeCell ref="P59:S60"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="O59:O60"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="COMPROBAR CANTIDAD DE CAJAS" error="Se debe ingresar la cantidad de cajas" sqref="I11" xr:uid="{3C2F8455-5D0D-41B0-BE98-F91BBC4383D3}">
@@ -4796,36 +4794,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AV57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="2"/>
-    <col min="6" max="6" width="11.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.44140625" style="2"/>
-    <col min="9" max="9" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="2"/>
+    <col min="6" max="6" width="11.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="2"/>
+    <col min="9" max="9" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="47" width="11.44140625" style="1"/>
+    <col min="12" max="12" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="47" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:47" ht="15" thickBot="1">
-      <c r="B1" s="194" t="s">
+    <row r="1" spans="2:47" ht="15.75" thickBot="1">
+      <c r="B1" s="204" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="196"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="206"/>
     </row>
     <row r="2" spans="2:47" s="1" customFormat="1" ht="35.1" customHeight="1">
       <c r="B2" s="43"/>
@@ -5213,13 +5211,13 @@
       <c r="AU20"/>
     </row>
     <row r="21" spans="2:48" ht="15" customHeight="1">
-      <c r="B21" s="144" t="s">
+      <c r="B21" s="143" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="145">
+      <c r="C21" s="144">
         <v>0</v>
       </c>
-      <c r="D21" s="145">
+      <c r="D21" s="144">
         <v>0</v>
       </c>
       <c r="E21" s="30"/>
@@ -5253,7 +5251,7 @@
         <v>#REF!</v>
       </c>
       <c r="E22" s="77"/>
-      <c r="F22" s="198"/>
+      <c r="F22" s="208"/>
       <c r="G22" s="48"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5287,7 +5285,7 @@
         <v>#REF!</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="198"/>
+      <c r="F23" s="208"/>
       <c r="G23" s="48"/>
       <c r="H23" s="1"/>
       <c r="I23" s="76"/>
@@ -5422,19 +5420,19 @@
       <c r="G28" s="48"/>
     </row>
     <row r="29" spans="2:48">
-      <c r="B29" s="200" t="s">
+      <c r="B29" s="210" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="200"/>
-      <c r="D29" s="200"/>
-      <c r="E29" s="200"/>
-      <c r="F29" s="200"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="200"/>
-      <c r="I29" s="200"/>
-      <c r="J29" s="200"/>
-      <c r="K29" s="200"/>
-      <c r="L29" s="200"/>
+      <c r="C29" s="210"/>
+      <c r="D29" s="210"/>
+      <c r="E29" s="210"/>
+      <c r="F29" s="210"/>
+      <c r="G29" s="210"/>
+      <c r="H29" s="210"/>
+      <c r="I29" s="210"/>
+      <c r="J29" s="210"/>
+      <c r="K29" s="210"/>
+      <c r="L29" s="210"/>
     </row>
     <row r="31" spans="2:48">
       <c r="C31" s="50"/>
@@ -5469,8 +5467,8 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="199"/>
-      <c r="I34" s="199"/>
+      <c r="H34" s="209"/>
+      <c r="I34" s="209"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -5498,8 +5496,8 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="199"/>
-      <c r="I35" s="199"/>
+      <c r="H35" s="209"/>
+      <c r="I35" s="209"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -5513,28 +5511,28 @@
       <c r="AU35"/>
     </row>
     <row r="36" spans="1:47">
-      <c r="A36" s="115"/>
-      <c r="B36" s="146"/>
-      <c r="C36" s="147">
+      <c r="A36" s="114"/>
+      <c r="B36" s="145"/>
+      <c r="C36" s="146">
         <v>0</v>
       </c>
-      <c r="D36" s="147">
+      <c r="D36" s="146">
         <v>0</v>
       </c>
-      <c r="E36" s="151"/>
-      <c r="F36" s="151"/>
-      <c r="G36" s="115"/>
-      <c r="H36" s="115"/>
-      <c r="I36" s="115"/>
-      <c r="J36" s="148"/>
-      <c r="K36" s="148"/>
-      <c r="L36" s="115"/>
-      <c r="M36" s="115"/>
-      <c r="N36" s="115"/>
-      <c r="O36" s="115"/>
-      <c r="P36" s="115"/>
-      <c r="Q36" s="115"/>
-      <c r="R36" s="115"/>
+      <c r="E36" s="150"/>
+      <c r="F36" s="150"/>
+      <c r="G36" s="114"/>
+      <c r="H36" s="114"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="147"/>
+      <c r="K36" s="147"/>
+      <c r="L36" s="114"/>
+      <c r="M36" s="114"/>
+      <c r="N36" s="114"/>
+      <c r="O36" s="114"/>
+      <c r="P36" s="114"/>
+      <c r="Q36" s="114"/>
+      <c r="R36" s="114"/>
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
@@ -5566,32 +5564,32 @@
       <c r="AU36"/>
     </row>
     <row r="37" spans="1:47">
-      <c r="A37" s="115"/>
-      <c r="B37" s="149" t="s">
+      <c r="A37" s="114"/>
+      <c r="B37" s="148" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="150" t="e">
+      <c r="C37" s="149" t="e">
         <f>ROUND((MAX(C26:C27)+C35)*C36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="D37" s="154" t="e">
+      <c r="D37" s="153" t="e">
         <f>ROUND((MAX(D26:D27)+D35)*D36,10)</f>
         <v>#REF!</v>
       </c>
-      <c r="E37" s="152"/>
-      <c r="F37" s="153"/>
-      <c r="G37" s="115"/>
-      <c r="H37" s="115"/>
-      <c r="I37" s="115"/>
-      <c r="J37" s="148"/>
-      <c r="K37" s="148"/>
-      <c r="L37" s="115"/>
-      <c r="M37" s="115"/>
-      <c r="N37" s="115"/>
-      <c r="O37" s="115"/>
-      <c r="P37" s="115"/>
-      <c r="Q37" s="115"/>
-      <c r="R37" s="115"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="114"/>
+      <c r="H37" s="114"/>
+      <c r="I37" s="114"/>
+      <c r="J37" s="147"/>
+      <c r="K37" s="147"/>
+      <c r="L37" s="114"/>
+      <c r="M37" s="114"/>
+      <c r="N37" s="114"/>
+      <c r="O37" s="114"/>
+      <c r="P37" s="114"/>
+      <c r="Q37" s="114"/>
+      <c r="R37" s="114"/>
       <c r="S37"/>
       <c r="T37"/>
       <c r="U37"/>
@@ -5815,19 +5813,19 @@
       </c>
     </row>
     <row r="45" spans="1:47">
-      <c r="B45" s="197" t="s">
+      <c r="B45" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="197"/>
-      <c r="D45" s="197"/>
-      <c r="E45" s="197"/>
-      <c r="F45" s="197"/>
-      <c r="G45" s="197"/>
-      <c r="H45" s="197"/>
-      <c r="I45" s="197"/>
-      <c r="J45" s="197"/>
-      <c r="K45" s="197"/>
-      <c r="L45" s="197"/>
+      <c r="C45" s="207"/>
+      <c r="D45" s="207"/>
+      <c r="E45" s="207"/>
+      <c r="F45" s="207"/>
+      <c r="G45" s="207"/>
+      <c r="H45" s="207"/>
+      <c r="I45" s="207"/>
+      <c r="J45" s="207"/>
+      <c r="K45" s="207"/>
+      <c r="L45" s="207"/>
     </row>
     <row r="47" spans="1:47">
       <c r="C47" s="21">
